--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CfgID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,7 +463,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -706,644 +710,2633 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_2</t>
+          <t>ActvSoccer_preset_name_5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中路任意球</t>
+          <t>左路单刀</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2</t>
+          <t>SlicePresetCfg/5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_3</t>
+          <t>ActvSoccer_preset_name_6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>标准点球</t>
+          <t>中路突破</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3</t>
+          <t>SlicePresetCfg/6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_4</t>
+          <t>ActvSoccer_preset_name_16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>基础守门</t>
+          <t>中路吊射</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4</t>
+          <t>SlicePresetCfg/16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_1</t>
+          <t>ActvSoccer_preset_name_2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>业余球员</t>
+          <t>中路任意球</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GrowthLevelCfg/101</t>
+          <t>SlicePresetCfg/2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_2</t>
+          <t>ActvSoccer_preset_name_7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>专业球员</t>
+          <t>左侧任意球</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GrowthLevelCfg/102</t>
+          <t>SlicePresetCfg/7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_3</t>
+          <t>ActvSoccer_preset_name_8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>大师</t>
+          <t>右侧任意球</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GrowthLevelCfg/103</t>
+          <t>SlicePresetCfg/8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_101</t>
+          <t>ActvSoccer_preset_name_17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>红星联</t>
+          <t>弧线任意球</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TeamCfg/101</t>
+          <t>SlicePresetCfg/17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_102</t>
+          <t>ActvSoccer_preset_name_3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>莱茵青年</t>
+          <t>标准点球</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TeamCfg/102</t>
+          <t>SlicePresetCfg/3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_103</t>
+          <t>ActvSoccer_preset_name_9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>桑巴之星</t>
+          <t>加压点球</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TeamCfg/103</t>
+          <t>SlicePresetCfg/9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_104</t>
+          <t>ActvSoccer_preset_name_10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>蓝白雄鹰</t>
+          <t>左角球</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TeamCfg/104</t>
+          <t>SlicePresetCfg/10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_201</t>
+          <t>ActvSoccer_preset_name_11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>海港FC</t>
+          <t>右角球</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TeamCfg/201</t>
+          <t>SlicePresetCfg/11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_202</t>
+          <t>ActvSoccer_preset_name_18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>东方之鹰</t>
+          <t>后点包抄</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TeamCfg/202</t>
+          <t>SlicePresetCfg/18</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_203</t>
+          <t>ActvSoccer_preset_name_12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>北欧狼</t>
+          <t>左界外球</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TeamCfg/203</t>
+          <t>SlicePresetCfg/12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_204</t>
+          <t>ActvSoccer_preset_name_13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>阿根廷神鹰</t>
+          <t>右界外球</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TeamCfg/204</t>
+          <t>SlicePresetCfg/13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_205</t>
+          <t>ActvSoccer_preset_name_4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>桑巴红魔</t>
+          <t>基础守门</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TeamCfg/205</t>
+          <t>SlicePresetCfg/4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_206</t>
+          <t>ActvSoccer_preset_name_14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南美风暴</t>
+          <t>大范围守门</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TeamCfg/206</t>
+          <t>SlicePresetCfg/14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_207</t>
+          <t>ActvSoccer_preset_name_15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>潘帕斯之翼</t>
+          <t>近距扑点</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TeamCfg/207</t>
+          <t>SlicePresetCfg/15</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_208</t>
+          <t>ActvSoccer_growth_fame_title_1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>高卢雄鸡</t>
+          <t>业余球员</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TeamCfg/208</t>
+          <t>FameGrowthLevelCfg/1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_1</t>
+          <t>ActvSoccer_growth_fame_title_2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>地区预选赛</t>
+          <t>新秀</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SeasonCfg/1</t>
+          <t>FameGrowthLevelCfg/2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_team_build</t>
+          <t>ActvSoccer_growth_fame_title_3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>组队期</t>
+          <t>专业球员</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>FameGrowthLevelCfg/3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_1</t>
+          <t>ActvSoccer_growth_fame_title_4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>发起/加入组队、命名队名队标、审批</t>
+          <t>明星</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>FameGrowthLevelCfg/4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_2</t>
+          <t>ActvSoccer_growth_fame_title_5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>组队结束补位</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>FameGrowthLevelCfg/5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
+          <t>ActvSoccer_growth_fame_title_6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>海选</t>
+          <t>世界级</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>FameGrowthLevelCfg/6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
+          <t>ActvSoccer_growth_fame_title_7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1天内筛出64强</t>
+          <t>传奇</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>FameGrowthLevelCfg/7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
+          <t>ActvSoccer_team_name_101</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>正赛第1轮</t>
+          <t>红星联</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>TeamCfg/101</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
+          <t>ActvSoccer_team_name_102</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8组各一轮(64强)</t>
+          <t>莱茵青年</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>TeamCfg/102</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
+          <t>ActvSoccer_team_name_103</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>正赛第2轮</t>
+          <t>桑巴之星</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>TeamCfg/103</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
+          <t>ActvSoccer_team_name_104</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8组各一轮(32强)</t>
+          <t>蓝白雄鹰</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>TeamCfg/104</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
+          <t>ActvSoccer_team_name_201</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>正赛第3轮</t>
+          <t>海港FC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>TeamCfg/201</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
+          <t>ActvSoccer_team_name_202</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8组各一轮(16强)</t>
+          <t>东方之鹰</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>TeamCfg/202</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
+          <t>ActvSoccer_team_name_203</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>正赛第4轮</t>
+          <t>北欧狼</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>TeamCfg/203</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
+          <t>ActvSoccer_team_name_204</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8组决出组冠军→8强</t>
+          <t>阿根廷神鹰</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>TeamCfg/204</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
+          <t>ActvSoccer_team_name_205</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>正赛第5轮</t>
+          <t>桑巴红魔</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>TeamCfg/205</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
+          <t>ActvSoccer_team_name_206</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8强淘汰赛(4强)</t>
+          <t>南美风暴</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>TeamCfg/206</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
+          <t>ActvSoccer_team_name_207</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>决赛</t>
+          <t>潘帕斯之翼</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/9</t>
+          <t>TeamCfg/207</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
+          <t>ActvSoccer_team_name_208</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>冠亚军决赛</t>
+          <t>高卢雄鸡</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/9</t>
+          <t>TeamCfg/208</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
+          <t>ActvSoccer_team_name_3001</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>展示期</t>
+          <t>社区杯·联</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/10</t>
+          <t>TeamCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>ActvSoccer_team_name_3002</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>社区杯·FC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TeamCfg/3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3003</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>社区杯·竞技</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TeamCfg/3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3004</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>社区杯·联合</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TeamCfg/3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3005</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>社区杯·勇士</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TeamCfg/3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3006</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>城市联赛·联</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TeamCfg/3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3007</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>城市联赛·FC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TeamCfg/3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3008</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>城市联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TeamCfg/3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3009</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>城市联赛·联合</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TeamCfg/3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3010</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>城市联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TeamCfg/3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3011</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>省级联赛·联</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TeamCfg/3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3012</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>省级联赛·FC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TeamCfg/3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3013</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>省级联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TeamCfg/3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3014</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>省级联赛·联合</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TeamCfg/3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3015</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>省级联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TeamCfg/3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3016</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>大区联赛·联</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TeamCfg/3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3017</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>大区联赛·FC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TeamCfg/3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3018</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>大区联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TeamCfg/3018</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3019</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>大区联赛·联合</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TeamCfg/3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3020</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>大区联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TeamCfg/3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3021</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>全国联赛·联</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TeamCfg/3021</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3022</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>全国联赛·FC</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TeamCfg/3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3023</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>全国联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TeamCfg/3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>全国联赛·联合</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TeamCfg/3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3025</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>全国联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TeamCfg/3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>洲际资格赛·联</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TeamCfg/3026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3027</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>洲际资格赛·FC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TeamCfg/3027</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3028</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>洲际资格赛·竞技</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TeamCfg/3028</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3029</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>洲际资格赛·联合</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TeamCfg/3029</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3030</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>洲际资格赛·勇士</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TeamCfg/3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3031</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>洲际联赛·联</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TeamCfg/3031</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3032</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>洲际联赛·FC</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TeamCfg/3032</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3033</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>洲际联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TeamCfg/3033</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3034</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>洲际联赛·联合</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TeamCfg/3034</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3035</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>洲际联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TeamCfg/3035</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3036</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>国际邀请赛·联</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TeamCfg/3036</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3037</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>国际邀请赛·FC</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TeamCfg/3037</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3038</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>国际邀请赛·竞技</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TeamCfg/3038</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3039</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>国际邀请赛·联合</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TeamCfg/3039</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3040</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>国际邀请赛·勇士</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TeamCfg/3040</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3041</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>世界精英赛·联</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TeamCfg/3041</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3042</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>世界精英赛·FC</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TeamCfg/3042</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3043</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>世界精英赛·竞技</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TeamCfg/3043</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3044</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>世界精英赛·联合</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TeamCfg/3044</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3045</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>世界精英赛·勇士</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TeamCfg/3045</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3046</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·联</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TeamCfg/3046</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3047</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·FC</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TeamCfg/3047</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3048</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·竞技</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TeamCfg/3048</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3049</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·联合</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TeamCfg/3049</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3050</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·勇士</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TeamCfg/3050</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_1</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>社区杯 第1/50轮</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SeasonCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>社区杯 第2/50轮</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SeasonCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_3</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>社区杯 第3/50轮</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SeasonCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_4</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>社区杯 第4/50轮</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SeasonCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_5</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>社区杯 第5/50轮</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SeasonCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_6</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>城市联赛 第6/50轮</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SeasonCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_7</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>城市联赛 第7/50轮</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SeasonCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_8</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>城市联赛 第8/50轮</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SeasonCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_9</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>城市联赛 第9/50轮</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SeasonCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>城市联赛 第10/50轮</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SeasonCfg/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_11</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>省级联赛 第11/50轮</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SeasonCfg/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>省级联赛 第12/50轮</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SeasonCfg/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_13</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>省级联赛 第13/50轮</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SeasonCfg/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_14</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>省级联赛 第14/50轮</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SeasonCfg/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_15</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>省级联赛 第15/50轮</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SeasonCfg/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_16</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>大区联赛 第16/50轮</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SeasonCfg/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_17</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>大区联赛 第17/50轮</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SeasonCfg/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>大区联赛 第18/50轮</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SeasonCfg/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_19</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>大区联赛 第19/50轮</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SeasonCfg/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_20</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>大区联赛 第20/50轮</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SeasonCfg/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_21</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>全国联赛 第21/50轮</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SeasonCfg/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_22</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>全国联赛 第22/50轮</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SeasonCfg/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_23</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>全国联赛 第23/50轮</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SeasonCfg/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_24</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>全国联赛 第24/50轮</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SeasonCfg/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_25</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>全国联赛 第25/50轮</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SeasonCfg/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第26/50轮</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SeasonCfg/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第27/50轮</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SeasonCfg/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_28</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第28/50轮</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SeasonCfg/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_29</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第29/50轮</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SeasonCfg/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_30</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第30/50轮</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SeasonCfg/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_31</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>洲际联赛 第31/50轮</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SeasonCfg/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_32</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>洲际联赛 第32/50轮</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SeasonCfg/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_33</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>洲际联赛 第33/50轮</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SeasonCfg/33</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_34</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>洲际联赛 第34/50轮</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SeasonCfg/34</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_35</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>洲际联赛 第35/50轮</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SeasonCfg/35</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_36</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第36/50轮</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SeasonCfg/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_37</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第37/50轮</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SeasonCfg/37</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_38</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第38/50轮</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SeasonCfg/38</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_39</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第39/50轮</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SeasonCfg/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_40</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第40/50轮</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SeasonCfg/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_41</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>世界精英赛 第41/50轮</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SeasonCfg/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_42</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>世界精英赛 第42/50轮</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SeasonCfg/42</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_43</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>世界精英赛 第43/50轮</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SeasonCfg/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_44</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>世界精英赛 第44/50轮</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SeasonCfg/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_45</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>世界精英赛 第45/50轮</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SeasonCfg/45</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_46</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第46/50轮</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SeasonCfg/46</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_47</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第47/50轮</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SeasonCfg/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_48</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第48/50轮</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SeasonCfg/48</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_49</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第49/50轮</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SeasonCfg/49</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_50</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第50/50轮</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SeasonCfg/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_team_build</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>组队期</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>发起/加入组队、命名队名队标、审批</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>组队结束补位</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_3</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>海选</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_3</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1天内筛出64强</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_4</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>正赛第1轮</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_4</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>8组各一轮(64强)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_5</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>正赛第2轮</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_5</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>8组各一轮(32强)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_6</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>正赛第3轮</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_6</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>8组各一轮(16强)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_7</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>正赛第4轮</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_7</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>8组决出组冠军→8强</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_8</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>正赛第5轮</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_8</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>8强淘汰赛(4强)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_9</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>决赛</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_9</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>冠亚军决赛</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_10</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>展示期</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>KnockoutPhaseCfg/10</t>
         </is>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C175"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3056,12 +3056,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_2</t>
+          <t>ActvSoccer_knockout_phase_name_3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>组队结束补位</t>
+          <t>海选</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3073,29 +3073,29 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
+          <t>ActvSoccer_knockout_day_content_3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>海选</t>
+          <t>1天内筛出64强</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>KnockoutPhaseCfg/2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
+          <t>ActvSoccer_knockout_phase_name_4</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1天内筛出64强</t>
+          <t>正赛第1轮</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3107,29 +3107,29 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
+          <t>ActvSoccer_knockout_day_content_4</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>正赛第1轮</t>
+          <t>8组各一轮(64强)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>KnockoutPhaseCfg/3</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
+          <t>ActvSoccer_knockout_phase_name_5</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>8组各一轮(64强)</t>
+          <t>正赛第2轮</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3141,29 +3141,29 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
+          <t>ActvSoccer_knockout_day_content_5</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>正赛第2轮</t>
+          <t>8组各一轮(32强)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>KnockoutPhaseCfg/4</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
+          <t>ActvSoccer_knockout_phase_name_6</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>8组各一轮(32强)</t>
+          <t>正赛第3轮</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3175,29 +3175,29 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
+          <t>ActvSoccer_knockout_day_content_6</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>正赛第3轮</t>
+          <t>8组各一轮(16强)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>KnockoutPhaseCfg/5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
+          <t>ActvSoccer_knockout_phase_name_7</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>8组各一轮(16强)</t>
+          <t>正赛第4轮</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3209,29 +3209,29 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
+          <t>ActvSoccer_knockout_day_content_7</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>正赛第4轮</t>
+          <t>8组决出组冠军→8强</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>KnockoutPhaseCfg/6</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
+          <t>ActvSoccer_knockout_phase_name_8</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8组决出组冠军→8强</t>
+          <t>正赛第5轮</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3243,29 +3243,29 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
+          <t>ActvSoccer_knockout_day_content_8</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>正赛第5轮</t>
+          <t>8强淘汰赛(4强)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>KnockoutPhaseCfg/7</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
+          <t>ActvSoccer_knockout_phase_name_9</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8强淘汰赛(4强)</t>
+          <t>决赛</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3277,29 +3277,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
+          <t>ActvSoccer_knockout_day_content_9</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>决赛</t>
+          <t>冠亚军决赛</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/9</t>
+          <t>KnockoutPhaseCfg/8</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
+          <t>ActvSoccer_knockout_phase_name_10</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>冠亚军决赛</t>
+          <t>展示期</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3311,34 +3311,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
+          <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>展示期</t>
+          <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_10</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>冠军展示+兑换商店可用</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/10</t>
+          <t>KnockoutPhaseCfg/9</t>
         </is>
       </c>
     </row>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,2327 +999,2871 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_1</t>
+          <t>ActvSoccer_preset_name_19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>业余球员</t>
+          <t>右肋斜插</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/1</t>
+          <t>SlicePresetCfg/19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_2</t>
+          <t>ActvSoccer_preset_name_20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>新秀</t>
+          <t>左肋斜插</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/2</t>
+          <t>SlicePresetCfg/20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_3</t>
+          <t>ActvSoccer_preset_name_21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>专业球员</t>
+          <t>禁区弧顶远射</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/3</t>
+          <t>SlicePresetCfg/21</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_4</t>
+          <t>ActvSoccer_preset_name_22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>明星</t>
+          <t>右路内切射门</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/4</t>
+          <t>SlicePresetCfg/22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_5</t>
+          <t>ActvSoccer_preset_name_23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>大师</t>
+          <t>左路内切射门</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/5</t>
+          <t>SlicePresetCfg/23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_6</t>
+          <t>ActvSoccer_preset_name_24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>世界级</t>
+          <t>倒三角回做</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/6</t>
+          <t>SlicePresetCfg/24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_7</t>
+          <t>ActvSoccer_preset_name_25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>传奇</t>
+          <t>门前抢点</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/7</t>
+          <t>SlicePresetCfg/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_101</t>
+          <t>ActvSoccer_preset_name_26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>红星联</t>
+          <t>禁区外吊射</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TeamCfg/101</t>
+          <t>SlicePresetCfg/26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_102</t>
+          <t>ActvSoccer_preset_name_27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>莱茵青年</t>
+          <t>二点补射</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TeamCfg/102</t>
+          <t>SlicePresetCfg/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_103</t>
+          <t>ActvSoccer_preset_name_28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>桑巴之星</t>
+          <t>横向摆脱射门</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamCfg/103</t>
+          <t>SlicePresetCfg/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_104</t>
+          <t>ActvSoccer_preset_name_29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>蓝白雄鹰</t>
+          <t>近距中路任意球</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TeamCfg/104</t>
+          <t>SlicePresetCfg/29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_201</t>
+          <t>ActvSoccer_preset_name_30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>海港FC</t>
+          <t>远距中路任意球</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TeamCfg/201</t>
+          <t>SlicePresetCfg/30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_202</t>
+          <t>ActvSoccer_preset_name_31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>东方之鹰</t>
+          <t>右侧绕墙低射</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TeamCfg/202</t>
+          <t>SlicePresetCfg/31</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_203</t>
+          <t>ActvSoccer_preset_name_32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>北欧狼</t>
+          <t>左侧绕墙低射</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TeamCfg/203</t>
+          <t>SlicePresetCfg/32</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_204</t>
+          <t>ActvSoccer_preset_name_33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>阿根廷神鹰</t>
+          <t>传中任意球</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TeamCfg/204</t>
+          <t>SlicePresetCfg/33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_205</t>
+          <t>ActvSoccer_preset_name_34</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>桑巴红魔</t>
+          <t>左下角点球</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TeamCfg/205</t>
+          <t>SlicePresetCfg/34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_206</t>
+          <t>ActvSoccer_preset_name_35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>南美风暴</t>
+          <t>右下角点球</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TeamCfg/206</t>
+          <t>SlicePresetCfg/35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_207</t>
+          <t>ActvSoccer_preset_name_36</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>潘帕斯之翼</t>
+          <t>半高点球</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TeamCfg/207</t>
+          <t>SlicePresetCfg/36</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_208</t>
+          <t>ActvSoccer_preset_name_37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>高卢雄鸡</t>
+          <t>左前点角球</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TeamCfg/208</t>
+          <t>SlicePresetCfg/37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3001</t>
+          <t>ActvSoccer_preset_name_38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>社区杯·联</t>
+          <t>右前点角球</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TeamCfg/3001</t>
+          <t>SlicePresetCfg/38</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3002</t>
+          <t>ActvSoccer_preset_name_39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>社区杯·FC</t>
+          <t>左后点高球</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TeamCfg/3002</t>
+          <t>SlicePresetCfg/39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3003</t>
+          <t>ActvSoccer_preset_name_40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>社区杯·竞技</t>
+          <t>右后点高球</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TeamCfg/3003</t>
+          <t>SlicePresetCfg/40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3004</t>
+          <t>ActvSoccer_preset_name_41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>社区杯·联合</t>
+          <t>短角球配合</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TeamCfg/3004</t>
+          <t>SlicePresetCfg/41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3005</t>
+          <t>ActvSoccer_preset_name_42</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>社区杯·勇士</t>
+          <t>低平扫门前</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TeamCfg/3005</t>
+          <t>SlicePresetCfg/42</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3006</t>
+          <t>ActvSoccer_preset_name_43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>城市联赛·联</t>
+          <t>禁区混战二点</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TeamCfg/3006</t>
+          <t>SlicePresetCfg/43</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3007</t>
+          <t>ActvSoccer_preset_name_44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>城市联赛·FC</t>
+          <t>左侧近端接应</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TeamCfg/3007</t>
+          <t>SlicePresetCfg/44</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3008</t>
+          <t>ActvSoccer_preset_name_45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>城市联赛·竞技</t>
+          <t>右侧近端接应</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TeamCfg/3008</t>
+          <t>SlicePresetCfg/45</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3009</t>
+          <t>ActvSoccer_preset_name_46</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>城市联赛·联合</t>
+          <t>左侧远端转移</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TeamCfg/3009</t>
+          <t>SlicePresetCfg/46</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3010</t>
+          <t>ActvSoccer_preset_name_47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>城市联赛·勇士</t>
+          <t>右侧远端转移</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TeamCfg/3010</t>
+          <t>SlicePresetCfg/47</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3011</t>
+          <t>ActvSoccer_preset_name_48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>省级联赛·联</t>
+          <t>左路快速反击</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TeamCfg/3011</t>
+          <t>SlicePresetCfg/48</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3012</t>
+          <t>ActvSoccer_preset_name_49</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>省级联赛·FC</t>
+          <t>右路快速反击</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TeamCfg/3012</t>
+          <t>SlicePresetCfg/49</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3013</t>
+          <t>ActvSoccer_preset_name_50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>省级联赛·竞技</t>
+          <t>左侧低球扑救</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TeamCfg/3013</t>
+          <t>SlicePresetCfg/50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3014</t>
+          <t>ActvSoccer_growth_fame_title_1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>省级联赛·联合</t>
+          <t>业余球员</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TeamCfg/3014</t>
+          <t>FameGrowthLevelCfg/1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3015</t>
+          <t>ActvSoccer_growth_fame_title_2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>省级联赛·勇士</t>
+          <t>新秀</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TeamCfg/3015</t>
+          <t>FameGrowthLevelCfg/2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3016</t>
+          <t>ActvSoccer_growth_fame_title_3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>大区联赛·联</t>
+          <t>专业球员</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TeamCfg/3016</t>
+          <t>FameGrowthLevelCfg/3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3017</t>
+          <t>ActvSoccer_growth_fame_title_4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>大区联赛·FC</t>
+          <t>明星</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TeamCfg/3017</t>
+          <t>FameGrowthLevelCfg/4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3018</t>
+          <t>ActvSoccer_growth_fame_title_5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>大区联赛·竞技</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TeamCfg/3018</t>
+          <t>FameGrowthLevelCfg/5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3019</t>
+          <t>ActvSoccer_growth_fame_title_6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>大区联赛·联合</t>
+          <t>世界级</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TeamCfg/3019</t>
+          <t>FameGrowthLevelCfg/6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3020</t>
+          <t>ActvSoccer_growth_fame_title_7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>大区联赛·勇士</t>
+          <t>传奇</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TeamCfg/3020</t>
+          <t>FameGrowthLevelCfg/7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3021</t>
+          <t>ActvSoccer_team_name_101</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>全国联赛·联</t>
+          <t>红星联</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TeamCfg/3021</t>
+          <t>TeamCfg/101</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3022</t>
+          <t>ActvSoccer_team_name_102</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>全国联赛·FC</t>
+          <t>莱茵青年</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TeamCfg/3022</t>
+          <t>TeamCfg/102</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3023</t>
+          <t>ActvSoccer_team_name_103</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>全国联赛·竞技</t>
+          <t>桑巴之星</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TeamCfg/3023</t>
+          <t>TeamCfg/103</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3024</t>
+          <t>ActvSoccer_team_name_104</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>全国联赛·联合</t>
+          <t>蓝白雄鹰</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TeamCfg/3024</t>
+          <t>TeamCfg/104</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3025</t>
+          <t>ActvSoccer_team_name_201</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>全国联赛·勇士</t>
+          <t>海港FC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TeamCfg/3025</t>
+          <t>TeamCfg/201</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3026</t>
+          <t>ActvSoccer_team_name_202</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>洲际资格赛·联</t>
+          <t>东方之鹰</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TeamCfg/3026</t>
+          <t>TeamCfg/202</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3027</t>
+          <t>ActvSoccer_team_name_203</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>洲际资格赛·FC</t>
+          <t>北欧狼</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TeamCfg/3027</t>
+          <t>TeamCfg/203</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3028</t>
+          <t>ActvSoccer_team_name_204</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>洲际资格赛·竞技</t>
+          <t>阿根廷神鹰</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TeamCfg/3028</t>
+          <t>TeamCfg/204</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3029</t>
+          <t>ActvSoccer_team_name_205</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>洲际资格赛·联合</t>
+          <t>桑巴红魔</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TeamCfg/3029</t>
+          <t>TeamCfg/205</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3030</t>
+          <t>ActvSoccer_team_name_206</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>洲际资格赛·勇士</t>
+          <t>南美风暴</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TeamCfg/3030</t>
+          <t>TeamCfg/206</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3031</t>
+          <t>ActvSoccer_team_name_207</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>洲际联赛·联</t>
+          <t>潘帕斯之翼</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TeamCfg/3031</t>
+          <t>TeamCfg/207</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3032</t>
+          <t>ActvSoccer_team_name_208</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>洲际联赛·FC</t>
+          <t>高卢雄鸡</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TeamCfg/3032</t>
+          <t>TeamCfg/208</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3033</t>
+          <t>ActvSoccer_team_name_3001</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>洲际联赛·竞技</t>
+          <t>社区杯·联</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TeamCfg/3033</t>
+          <t>TeamCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3034</t>
+          <t>ActvSoccer_team_name_3002</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>洲际联赛·联合</t>
+          <t>社区杯·FC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TeamCfg/3034</t>
+          <t>TeamCfg/3002</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3035</t>
+          <t>ActvSoccer_team_name_3003</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>洲际联赛·勇士</t>
+          <t>社区杯·竞技</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TeamCfg/3035</t>
+          <t>TeamCfg/3003</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3036</t>
+          <t>ActvSoccer_team_name_3004</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>国际邀请赛·联</t>
+          <t>社区杯·联合</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TeamCfg/3036</t>
+          <t>TeamCfg/3004</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3037</t>
+          <t>ActvSoccer_team_name_3005</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>国际邀请赛·FC</t>
+          <t>社区杯·勇士</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TeamCfg/3037</t>
+          <t>TeamCfg/3005</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3038</t>
+          <t>ActvSoccer_team_name_3006</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>国际邀请赛·竞技</t>
+          <t>城市联赛·联</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TeamCfg/3038</t>
+          <t>TeamCfg/3006</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3039</t>
+          <t>ActvSoccer_team_name_3007</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>国际邀请赛·联合</t>
+          <t>城市联赛·FC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TeamCfg/3039</t>
+          <t>TeamCfg/3007</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3040</t>
+          <t>ActvSoccer_team_name_3008</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>国际邀请赛·勇士</t>
+          <t>城市联赛·竞技</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TeamCfg/3040</t>
+          <t>TeamCfg/3008</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3041</t>
+          <t>ActvSoccer_team_name_3009</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>世界精英赛·联</t>
+          <t>城市联赛·联合</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TeamCfg/3041</t>
+          <t>TeamCfg/3009</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3042</t>
+          <t>ActvSoccer_team_name_3010</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>世界精英赛·FC</t>
+          <t>城市联赛·勇士</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TeamCfg/3042</t>
+          <t>TeamCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3043</t>
+          <t>ActvSoccer_team_name_3011</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>世界精英赛·竞技</t>
+          <t>省级联赛·联</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TeamCfg/3043</t>
+          <t>TeamCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3044</t>
+          <t>ActvSoccer_team_name_3012</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>世界精英赛·联合</t>
+          <t>省级联赛·FC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TeamCfg/3044</t>
+          <t>TeamCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3045</t>
+          <t>ActvSoccer_team_name_3013</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>世界精英赛·勇士</t>
+          <t>省级联赛·竞技</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TeamCfg/3045</t>
+          <t>TeamCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3046</t>
+          <t>ActvSoccer_team_name_3014</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联</t>
+          <t>省级联赛·联合</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TeamCfg/3046</t>
+          <t>TeamCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3047</t>
+          <t>ActvSoccer_team_name_3015</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>世界杯总决赛·FC</t>
+          <t>省级联赛·勇士</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TeamCfg/3047</t>
+          <t>TeamCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3048</t>
+          <t>ActvSoccer_team_name_3016</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>世界杯总决赛·竞技</t>
+          <t>大区联赛·联</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TeamCfg/3048</t>
+          <t>TeamCfg/3016</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3049</t>
+          <t>ActvSoccer_team_name_3017</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联合</t>
+          <t>大区联赛·FC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TeamCfg/3049</t>
+          <t>TeamCfg/3017</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3050</t>
+          <t>ActvSoccer_team_name_3018</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>世界杯总决赛·勇士</t>
+          <t>大区联赛·竞技</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TeamCfg/3050</t>
+          <t>TeamCfg/3018</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_1</t>
+          <t>ActvSoccer_team_name_3019</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>社区杯 第1/50轮</t>
+          <t>大区联赛·联合</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SeasonCfg/1</t>
+          <t>TeamCfg/3019</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_2</t>
+          <t>ActvSoccer_team_name_3020</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>社区杯 第2/50轮</t>
+          <t>大区联赛·勇士</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SeasonCfg/2</t>
+          <t>TeamCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_3</t>
+          <t>ActvSoccer_team_name_3021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>社区杯 第3/50轮</t>
+          <t>全国联赛·联</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SeasonCfg/3</t>
+          <t>TeamCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_4</t>
+          <t>ActvSoccer_team_name_3022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>社区杯 第4/50轮</t>
+          <t>全国联赛·FC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SeasonCfg/4</t>
+          <t>TeamCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_5</t>
+          <t>ActvSoccer_team_name_3023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>社区杯 第5/50轮</t>
+          <t>全国联赛·竞技</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SeasonCfg/5</t>
+          <t>TeamCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_6</t>
+          <t>ActvSoccer_team_name_3024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>城市联赛 第6/50轮</t>
+          <t>全国联赛·联合</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SeasonCfg/6</t>
+          <t>TeamCfg/3024</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_7</t>
+          <t>ActvSoccer_team_name_3025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>城市联赛 第7/50轮</t>
+          <t>全国联赛·勇士</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SeasonCfg/7</t>
+          <t>TeamCfg/3025</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_8</t>
+          <t>ActvSoccer_team_name_3026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>城市联赛 第8/50轮</t>
+          <t>洲际资格赛·联</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SeasonCfg/8</t>
+          <t>TeamCfg/3026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_9</t>
+          <t>ActvSoccer_team_name_3027</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>城市联赛 第9/50轮</t>
+          <t>洲际资格赛·FC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SeasonCfg/9</t>
+          <t>TeamCfg/3027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_10</t>
+          <t>ActvSoccer_team_name_3028</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>城市联赛 第10/50轮</t>
+          <t>洲际资格赛·竞技</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SeasonCfg/10</t>
+          <t>TeamCfg/3028</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_11</t>
+          <t>ActvSoccer_team_name_3029</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>省级联赛 第11/50轮</t>
+          <t>洲际资格赛·联合</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SeasonCfg/11</t>
+          <t>TeamCfg/3029</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_12</t>
+          <t>ActvSoccer_team_name_3030</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>省级联赛 第12/50轮</t>
+          <t>洲际资格赛·勇士</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SeasonCfg/12</t>
+          <t>TeamCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_13</t>
+          <t>ActvSoccer_team_name_3031</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>省级联赛 第13/50轮</t>
+          <t>洲际联赛·联</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SeasonCfg/13</t>
+          <t>TeamCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_14</t>
+          <t>ActvSoccer_team_name_3032</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>省级联赛 第14/50轮</t>
+          <t>洲际联赛·FC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SeasonCfg/14</t>
+          <t>TeamCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_15</t>
+          <t>ActvSoccer_team_name_3033</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>省级联赛 第15/50轮</t>
+          <t>洲际联赛·竞技</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SeasonCfg/15</t>
+          <t>TeamCfg/3033</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_16</t>
+          <t>ActvSoccer_team_name_3034</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>大区联赛 第16/50轮</t>
+          <t>洲际联赛·联合</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SeasonCfg/16</t>
+          <t>TeamCfg/3034</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_17</t>
+          <t>ActvSoccer_team_name_3035</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>大区联赛 第17/50轮</t>
+          <t>洲际联赛·勇士</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SeasonCfg/17</t>
+          <t>TeamCfg/3035</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_18</t>
+          <t>ActvSoccer_team_name_3036</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>大区联赛 第18/50轮</t>
+          <t>国际邀请赛·联</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SeasonCfg/18</t>
+          <t>TeamCfg/3036</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_19</t>
+          <t>ActvSoccer_team_name_3037</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>大区联赛 第19/50轮</t>
+          <t>国际邀请赛·FC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SeasonCfg/19</t>
+          <t>TeamCfg/3037</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_20</t>
+          <t>ActvSoccer_team_name_3038</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>大区联赛 第20/50轮</t>
+          <t>国际邀请赛·竞技</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SeasonCfg/20</t>
+          <t>TeamCfg/3038</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_21</t>
+          <t>ActvSoccer_team_name_3039</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>全国联赛 第21/50轮</t>
+          <t>国际邀请赛·联合</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SeasonCfg/21</t>
+          <t>TeamCfg/3039</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_22</t>
+          <t>ActvSoccer_team_name_3040</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>全国联赛 第22/50轮</t>
+          <t>国际邀请赛·勇士</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SeasonCfg/22</t>
+          <t>TeamCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_23</t>
+          <t>ActvSoccer_team_name_3041</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>全国联赛 第23/50轮</t>
+          <t>世界精英赛·联</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SeasonCfg/23</t>
+          <t>TeamCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_24</t>
+          <t>ActvSoccer_team_name_3042</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>全国联赛 第24/50轮</t>
+          <t>世界精英赛·FC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SeasonCfg/24</t>
+          <t>TeamCfg/3042</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_25</t>
+          <t>ActvSoccer_team_name_3043</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>全国联赛 第25/50轮</t>
+          <t>世界精英赛·竞技</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SeasonCfg/25</t>
+          <t>TeamCfg/3043</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_26</t>
+          <t>ActvSoccer_team_name_3044</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>洲际资格赛 第26/50轮</t>
+          <t>世界精英赛·联合</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SeasonCfg/26</t>
+          <t>TeamCfg/3044</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_27</t>
+          <t>ActvSoccer_team_name_3045</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>洲际资格赛 第27/50轮</t>
+          <t>世界精英赛·勇士</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SeasonCfg/27</t>
+          <t>TeamCfg/3045</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_28</t>
+          <t>ActvSoccer_team_name_3046</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>洲际资格赛 第28/50轮</t>
+          <t>世界杯总决赛·联</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SeasonCfg/28</t>
+          <t>TeamCfg/3046</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_29</t>
+          <t>ActvSoccer_team_name_3047</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>洲际资格赛 第29/50轮</t>
+          <t>世界杯总决赛·FC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SeasonCfg/29</t>
+          <t>TeamCfg/3047</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_30</t>
+          <t>ActvSoccer_team_name_3048</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>洲际资格赛 第30/50轮</t>
+          <t>世界杯总决赛·竞技</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SeasonCfg/30</t>
+          <t>TeamCfg/3048</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_31</t>
+          <t>ActvSoccer_team_name_3049</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>洲际联赛 第31/50轮</t>
+          <t>世界杯总决赛·联合</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SeasonCfg/31</t>
+          <t>TeamCfg/3049</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_32</t>
+          <t>ActvSoccer_team_name_3050</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>洲际联赛 第32/50轮</t>
+          <t>世界杯总决赛·勇士</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SeasonCfg/32</t>
+          <t>TeamCfg/3050</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_33</t>
+          <t>ActvSoccer_season_league_name_1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>洲际联赛 第33/50轮</t>
+          <t>社区杯 第1/50轮</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SeasonCfg/33</t>
+          <t>SeasonCfg/1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_34</t>
+          <t>ActvSoccer_season_league_name_2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>洲际联赛 第34/50轮</t>
+          <t>社区杯 第2/50轮</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SeasonCfg/34</t>
+          <t>SeasonCfg/2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_35</t>
+          <t>ActvSoccer_season_league_name_3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>洲际联赛 第35/50轮</t>
+          <t>社区杯 第3/50轮</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SeasonCfg/35</t>
+          <t>SeasonCfg/3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_36</t>
+          <t>ActvSoccer_season_league_name_4</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>国际邀请赛 第36/50轮</t>
+          <t>社区杯 第4/50轮</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SeasonCfg/36</t>
+          <t>SeasonCfg/4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_37</t>
+          <t>ActvSoccer_season_league_name_5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>国际邀请赛 第37/50轮</t>
+          <t>社区杯 第5/50轮</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SeasonCfg/37</t>
+          <t>SeasonCfg/5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_38</t>
+          <t>ActvSoccer_season_league_name_6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>国际邀请赛 第38/50轮</t>
+          <t>城市联赛 第6/50轮</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SeasonCfg/38</t>
+          <t>SeasonCfg/6</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_39</t>
+          <t>ActvSoccer_season_league_name_7</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>国际邀请赛 第39/50轮</t>
+          <t>城市联赛 第7/50轮</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SeasonCfg/39</t>
+          <t>SeasonCfg/7</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_40</t>
+          <t>ActvSoccer_season_league_name_8</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>国际邀请赛 第40/50轮</t>
+          <t>城市联赛 第8/50轮</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SeasonCfg/40</t>
+          <t>SeasonCfg/8</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_41</t>
+          <t>ActvSoccer_season_league_name_9</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>世界精英赛 第41/50轮</t>
+          <t>城市联赛 第9/50轮</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SeasonCfg/41</t>
+          <t>SeasonCfg/9</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_42</t>
+          <t>ActvSoccer_season_league_name_10</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>世界精英赛 第42/50轮</t>
+          <t>城市联赛 第10/50轮</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SeasonCfg/42</t>
+          <t>SeasonCfg/10</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_43</t>
+          <t>ActvSoccer_season_league_name_11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>世界精英赛 第43/50轮</t>
+          <t>省级联赛 第11/50轮</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SeasonCfg/43</t>
+          <t>SeasonCfg/11</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_44</t>
+          <t>ActvSoccer_season_league_name_12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>世界精英赛 第44/50轮</t>
+          <t>省级联赛 第12/50轮</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SeasonCfg/44</t>
+          <t>SeasonCfg/12</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_45</t>
+          <t>ActvSoccer_season_league_name_13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>世界精英赛 第45/50轮</t>
+          <t>省级联赛 第13/50轮</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SeasonCfg/45</t>
+          <t>SeasonCfg/13</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_46</t>
+          <t>ActvSoccer_season_league_name_14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第46/50轮</t>
+          <t>省级联赛 第14/50轮</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SeasonCfg/46</t>
+          <t>SeasonCfg/14</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_47</t>
+          <t>ActvSoccer_season_league_name_15</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第47/50轮</t>
+          <t>省级联赛 第15/50轮</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SeasonCfg/47</t>
+          <t>SeasonCfg/15</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_48</t>
+          <t>ActvSoccer_season_league_name_16</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第48/50轮</t>
+          <t>大区联赛 第16/50轮</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SeasonCfg/48</t>
+          <t>SeasonCfg/16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_49</t>
+          <t>ActvSoccer_season_league_name_17</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第49/50轮</t>
+          <t>大区联赛 第17/50轮</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SeasonCfg/49</t>
+          <t>SeasonCfg/17</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_50</t>
+          <t>ActvSoccer_season_league_name_18</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第50/50轮</t>
+          <t>大区联赛 第18/50轮</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SeasonCfg/50</t>
+          <t>SeasonCfg/18</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_team_build</t>
+          <t>ActvSoccer_season_league_name_19</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>组队期</t>
+          <t>大区联赛 第19/50轮</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>SeasonCfg/19</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_1</t>
+          <t>ActvSoccer_season_league_name_20</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>发起/加入组队、命名队名队标、审批</t>
+          <t>大区联赛 第20/50轮</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>SeasonCfg/20</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
+          <t>ActvSoccer_season_league_name_21</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>海选</t>
+          <t>全国联赛 第21/50轮</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>SeasonCfg/21</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
+          <t>ActvSoccer_season_league_name_22</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1天内筛出64强</t>
+          <t>全国联赛 第22/50轮</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>SeasonCfg/22</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
+          <t>ActvSoccer_season_league_name_23</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>正赛第1轮</t>
+          <t>全国联赛 第23/50轮</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>SeasonCfg/23</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
+          <t>ActvSoccer_season_league_name_24</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>8组各一轮(64强)</t>
+          <t>全国联赛 第24/50轮</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>SeasonCfg/24</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
+          <t>ActvSoccer_season_league_name_25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>正赛第2轮</t>
+          <t>全国联赛 第25/50轮</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>SeasonCfg/25</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
+          <t>ActvSoccer_season_league_name_26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8组各一轮(32强)</t>
+          <t>洲际资格赛 第26/50轮</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>SeasonCfg/26</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
+          <t>ActvSoccer_season_league_name_27</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>正赛第3轮</t>
+          <t>洲际资格赛 第27/50轮</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>SeasonCfg/27</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
+          <t>ActvSoccer_season_league_name_28</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>8组各一轮(16强)</t>
+          <t>洲际资格赛 第28/50轮</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>SeasonCfg/28</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
+          <t>ActvSoccer_season_league_name_29</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>正赛第4轮</t>
+          <t>洲际资格赛 第29/50轮</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>SeasonCfg/29</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
+          <t>ActvSoccer_season_league_name_30</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>8组决出组冠军→8强</t>
+          <t>洲际资格赛 第30/50轮</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>SeasonCfg/30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
+          <t>ActvSoccer_season_league_name_31</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>正赛第5轮</t>
+          <t>洲际联赛 第31/50轮</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>SeasonCfg/31</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
+          <t>ActvSoccer_season_league_name_32</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8强淘汰赛(4强)</t>
+          <t>洲际联赛 第32/50轮</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>SeasonCfg/32</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
+          <t>ActvSoccer_season_league_name_33</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>决赛</t>
+          <t>洲际联赛 第33/50轮</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>SeasonCfg/33</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
+          <t>ActvSoccer_season_league_name_34</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>冠亚军决赛</t>
+          <t>洲际联赛 第34/50轮</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>SeasonCfg/34</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
+          <t>ActvSoccer_season_league_name_35</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>展示期</t>
+          <t>洲际联赛 第35/50轮</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/9</t>
+          <t>SeasonCfg/35</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>ActvSoccer_season_league_name_36</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第36/50轮</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SeasonCfg/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_37</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第37/50轮</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SeasonCfg/37</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_38</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第38/50轮</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SeasonCfg/38</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_39</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第39/50轮</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SeasonCfg/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_40</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第40/50轮</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SeasonCfg/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_41</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>世界精英赛 第41/50轮</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SeasonCfg/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_42</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>世界精英赛 第42/50轮</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SeasonCfg/42</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_43</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>世界精英赛 第43/50轮</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SeasonCfg/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_44</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>世界精英赛 第44/50轮</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SeasonCfg/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_45</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>世界精英赛 第45/50轮</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SeasonCfg/45</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_46</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第46/50轮</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SeasonCfg/46</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_47</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第47/50轮</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SeasonCfg/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_48</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第48/50轮</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SeasonCfg/48</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_49</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第49/50轮</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SeasonCfg/49</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_50</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第50/50轮</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SeasonCfg/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_team_build</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>组队期</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_1</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>发起/加入组队、命名队名队标、审批</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_3</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>海选</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_3</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1天内筛出64强</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_4</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>正赛第1轮</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_4</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>8组各一轮(64强)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_5</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>正赛第2轮</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_5</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>8组各一轮(32强)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_6</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>正赛第3轮</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_6</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>8组各一轮(16强)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_7</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>正赛第4轮</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_7</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>8组决出组冠军→8强</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_8</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>正赛第5轮</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_8</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>8强淘汰赛(4强)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_9</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>决赛</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_9</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>冠亚军决赛</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_10</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>展示期</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
           <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>KnockoutPhaseCfg/9</t>
         </is>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C206"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,3177 +693,4826 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_1</t>
+          <t>ActvSoccer_guide_chapter_1001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>右路单刀</t>
+          <t>试训入口</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1</t>
+          <t>GuideStepCfg/1001</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_5</t>
+          <t>ActvSoccer_guide_dialogue_1001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>左路单刀</t>
+          <t>先完成一次试训，熟悉比赛中的射门操作。</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5</t>
+          <t>GuideStepCfg/1001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_6</t>
+          <t>ActvSoccer_guide_chapter_1010</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中路突破</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6</t>
+          <t>GuideStepCfg/1010</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_16</t>
+          <t>ActvSoccer_guide_dialogue_1010</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中路吊射</t>
+          <t>按住球员脚下区域，画出你想踢出的路线。</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/16</t>
+          <t>GuideStepCfg/1010</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_2</t>
+          <t>ActvSoccer_guide_gesture_1010</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中路任意球</t>
+          <t>白色手指从球员脚下按住，沿推荐轨迹拖向白色目标框，轨迹线循环播放。</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2</t>
+          <t>GuideStepCfg/1010</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_7</t>
+          <t>ActvSoccer_guide_chapter_1011</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>左侧任意球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/7</t>
+          <t>GuideStepCfg/1011</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_8</t>
+          <t>ActvSoccer_guide_dialogue_1011</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>右侧任意球</t>
+          <t>松手后，球会沿着轨迹飞出。</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/8</t>
+          <t>GuideStepCfg/1011</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_17</t>
+          <t>ActvSoccer_guide_gesture_1011</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>弧线任意球</t>
+          <t>手指沿轨迹到达目标框后松开，展示释放射门。</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/17</t>
+          <t>GuideStepCfg/1011</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_3</t>
+          <t>ActvSoccer_guide_chapter_1012</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>标准点球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3</t>
+          <t>GuideStepCfg/1012</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_9</t>
+          <t>ActvSoccer_guide_dialogue_1012</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>加压点球</t>
+          <t>做得好！继续下一项训练。</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9</t>
+          <t>GuideStepCfg/1012</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_10</t>
+          <t>ActvSoccer_guide_chapter_1013</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>左角球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/10</t>
+          <t>GuideStepCfg/1013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_11</t>
+          <t>ActvSoccer_guide_dialogue_1013</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>右角球</t>
+          <t>再试一次，把路线画向白色目标框。</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/11</t>
+          <t>GuideStepCfg/1013</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_18</t>
+          <t>ActvSoccer_guide_gesture_1013</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>后点包抄</t>
+          <t>重复播放从球员脚下划向目标框的轨迹手势。</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/18</t>
+          <t>GuideStepCfg/1013</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_12</t>
+          <t>ActvSoccer_guide_chapter_1020</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>左界外球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/12</t>
+          <t>GuideStepCfg/1020</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_13</t>
+          <t>ActvSoccer_guide_dialogue_1020</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>右界外球</t>
+          <t>任意球需要避开人墙。拖动来选择方向和力量。</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/13</t>
+          <t>GuideStepCfg/1020</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_4</t>
+          <t>ActvSoccer_guide_gesture_1020</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>基础守门</t>
+          <t>手指从球向后拖拽，出现弹弓方向线和力度百分比。</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4</t>
+          <t>GuideStepCfg/1020</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_14</t>
+          <t>ActvSoccer_guide_chapter_1021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>大范围守门</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/14</t>
+          <t>GuideStepCfg/1021</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_15</t>
+          <t>ActvSoccer_guide_dialogue_1021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>近距扑点</t>
+          <t>力量控制在65%左右，更容易命中目标。</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/15</t>
+          <t>GuideStepCfg/1021</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_19</t>
+          <t>ActvSoccer_guide_gesture_1021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>右肋斜插</t>
+          <t>手指拖动到推荐力度点，力度数值从49%动到65%附近。</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/19</t>
+          <t>GuideStepCfg/1021</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_20</t>
+          <t>ActvSoccer_guide_chapter_1022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>左肋斜插</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/20</t>
+          <t>GuideStepCfg/1022</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_21</t>
+          <t>ActvSoccer_guide_dialogue_1022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>禁区弧顶远射</t>
+          <t>很好，任意球训练完成。</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/21</t>
+          <t>GuideStepCfg/1022</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_22</t>
+          <t>ActvSoccer_guide_chapter_1023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>右路内切射门</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/22</t>
+          <t>GuideStepCfg/1023</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_23</t>
+          <t>ActvSoccer_guide_dialogue_1023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>左路内切射门</t>
+          <t>力量太小了，再向后拖动一些。</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/23</t>
+          <t>GuideStepCfg/1023</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_24</t>
+          <t>ActvSoccer_guide_gesture_1023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>倒三角回做</t>
+          <t>重复播放向后拖拽至65%附近的力度手势。</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/24</t>
+          <t>GuideStepCfg/1023</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_25</t>
+          <t>ActvSoccer_guide_chapter_1024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>门前抢点</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/25</t>
+          <t>GuideStepCfg/1024</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_26</t>
+          <t>ActvSoccer_guide_dialogue_1024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>禁区外吊射</t>
+          <t>力量太大了，稍微收一点力。</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/26</t>
+          <t>GuideStepCfg/1024</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_27</t>
+          <t>ActvSoccer_guide_gesture_1024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>二点补射</t>
+          <t>重复播放力度回收到65%附近的手势。</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/27</t>
+          <t>GuideStepCfg/1024</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_28</t>
+          <t>ActvSoccer_guide_chapter_1025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>横向摆脱射门</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/28</t>
+          <t>GuideStepCfg/1025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_29</t>
+          <t>ActvSoccer_guide_dialogue_1025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>近距中路任意球</t>
+          <t>角度偏离目标，再调整射门方向。</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/29</t>
+          <t>GuideStepCfg/1025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_30</t>
+          <t>ActvSoccer_guide_gesture_1025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>远距中路任意球</t>
+          <t>重复播放拖动方向线进入黄色允许角度范围的手势。</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/30</t>
+          <t>GuideStepCfg/1025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_31</t>
+          <t>ActvSoccer_guide_chapter_1030</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>右侧绕墙低射</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/31</t>
+          <t>GuideStepCfg/1030</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_32</t>
+          <t>ActvSoccer_guide_dialogue_1030</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>左侧绕墙低射</t>
+          <t>试训中可以自由切换操作方式，选择你更顺手的模式。</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/32</t>
+          <t>GuideStepCfg/1030</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_33</t>
+          <t>ActvSoccer_guide_gesture_1030</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>传中任意球</t>
+          <t>点击手指点按模式切换按钮，按钮在划线/弹弓之间切换。</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/33</t>
+          <t>GuideStepCfg/1030</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_34</t>
+          <t>ActvSoccer_guide_chapter_1031</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>左下角点球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/34</t>
+          <t>GuideStepCfg/1031</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_35</t>
+          <t>ActvSoccer_guide_dialogue_1031</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>右下角点球</t>
+          <t>现在把球踢向高亮区域。</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/35</t>
+          <t>GuideStepCfg/1031</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_36</t>
+          <t>ActvSoccer_guide_gesture_1031</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>半高点球</t>
+          <t>按玩家当前模式播放对应手势：划线轨迹或弹弓拖拽。</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/36</t>
+          <t>GuideStepCfg/1031</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_37</t>
+          <t>ActvSoccer_guide_chapter_1032</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>左前点角球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/37</t>
+          <t>GuideStepCfg/1032</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_38</t>
+          <t>ActvSoccer_guide_dialogue_1032</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>右前点角球</t>
+          <t>点球训练完成。</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/38</t>
+          <t>GuideStepCfg/1032</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_39</t>
+          <t>ActvSoccer_guide_chapter_1033</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>左后点高球</t>
+          <t>试训关卡</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/39</t>
+          <t>GuideStepCfg/1033</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_40</t>
+          <t>ActvSoccer_guide_dialogue_1033</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>右后点高球</t>
+          <t>再试一次，瞄准高亮区域射门。</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/40</t>
+          <t>GuideStepCfg/1033</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_41</t>
+          <t>ActvSoccer_guide_gesture_1033</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>短角球配合</t>
+          <t>按当前操作模式重复播放点球射门手势。</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/41</t>
+          <t>GuideStepCfg/1033</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_42</t>
+          <t>ActvSoccer_guide_chapter_1040</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>低平扫门前</t>
+          <t>试训完成</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/42</t>
+          <t>GuideStepCfg/1040</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_43</t>
+          <t>ActvSoccer_guide_dialogue_1040</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>禁区混战二点</t>
+          <t>试训完成。球队给你发来了邀请，挑选一支作为职业生涯起点。</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/43</t>
+          <t>GuideStepCfg/1040</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_44</t>
+          <t>ActvSoccer_guide_gesture_1040</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>左侧近端接应</t>
+          <t>点击手指循环点按确认按钮。</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/44</t>
+          <t>GuideStepCfg/1040</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_45</t>
+          <t>ActvSoccer_guide_chapter_2001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>右侧近端接应</t>
+          <t>主界面强引导</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/45</t>
+          <t>GuideStepCfg/2001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_46</t>
+          <t>ActvSoccer_guide_dialogue_2001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>左侧远端转移</t>
+          <t>第一场比赛已经准备好了，先从基础比赛开始。</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/46</t>
+          <t>GuideStepCfg/2001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_47</t>
+          <t>ActvSoccer_guide_gesture_2001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>右侧远端转移</t>
+          <t>点击手指点按主界面下一场比赛按钮。</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/47</t>
+          <t>GuideStepCfg/2001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_48</t>
+          <t>ActvSoccer_guide_chapter_2010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>左路快速反击</t>
+          <t>战前页引导</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/48</t>
+          <t>GuideStepCfg/2010</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_49</t>
+          <t>ActvSoccer_guide_dialogue_2010</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>右路快速反击</t>
+          <t>这里可以看到本场比赛目标。</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/49</t>
+          <t>GuideStepCfg/2010</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_50</t>
+          <t>ActvSoccer_guide_chapter_2011</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>左侧低球扑救</t>
+          <t>战前页引导</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/50</t>
+          <t>GuideStepCfg/2011</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_1</t>
+          <t>ActvSoccer_guide_dialogue_2011</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>业余球员</t>
+          <t>点击开球，开始你的第一场比赛。</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/1</t>
+          <t>GuideStepCfg/2011</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_2</t>
+          <t>ActvSoccer_guide_gesture_2011</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>新秀</t>
+          <t>点击手指点按黄色开球按钮。</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/2</t>
+          <t>GuideStepCfg/2011</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_3</t>
+          <t>ActvSoccer_guide_chapter_3001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>专业球员</t>
+          <t>第一关入场</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/3</t>
+          <t>GuideStepCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_4</t>
+          <t>ActvSoccer_guide_dialogue_3001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>明星</t>
+          <t>比赛即将开始。</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/4</t>
+          <t>GuideStepCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_5</t>
+          <t>ActvSoccer_guide_chapter_3010</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>大师</t>
+          <t>第一关切片201</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/5</t>
+          <t>GuideStepCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_6</t>
+          <t>ActvSoccer_guide_dialogue_3010</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>世界级</t>
+          <t>黄色光圈表示当前由你操作的球员。</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/6</t>
+          <t>GuideStepCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_7</t>
+          <t>ActvSoccer_guide_chapter_3011</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>传奇</t>
+          <t>第一关切片201</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/7</t>
+          <t>GuideStepCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_101</t>
+          <t>ActvSoccer_guide_dialogue_3011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>红星联</t>
+          <t>这个标志表示这个方向上有你的队友。</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TeamCfg/101</t>
+          <t>GuideStepCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_102</t>
+          <t>ActvSoccer_guide_gesture_3011</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>莱茵青年</t>
+          <t>点击手指点按明白了按钮。</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TeamCfg/102</t>
+          <t>GuideStepCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_103</t>
+          <t>ActvSoccer_guide_chapter_3012</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>桑巴之星</t>
+          <t>第一关切片201</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TeamCfg/103</t>
+          <t>GuideStepCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_104</t>
+          <t>ActvSoccer_guide_dialogue_3012</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>蓝白雄鹰</t>
+          <t>在屏幕上半部分左右滑动，可以移动相机观察场上情况。</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TeamCfg/104</t>
+          <t>GuideStepCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_201</t>
+          <t>ActvSoccer_guide_gesture_3012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>海港FC</t>
+          <t>手指在上半屏左右滑动一次，循环播放。</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TeamCfg/201</t>
+          <t>GuideStepCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_202</t>
+          <t>ActvSoccer_guide_chapter_3013</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>东方之鹰</t>
+          <t>第一关切片201</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TeamCfg/202</t>
+          <t>GuideStepCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_203</t>
+          <t>ActvSoccer_guide_dialogue_3013</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>北欧狼</t>
+          <t>现在把球踢向白色目标区域。</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TeamCfg/203</t>
+          <t>GuideStepCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_204</t>
+          <t>ActvSoccer_guide_gesture_3013</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>阿根廷神鹰</t>
+          <t>按当前锁定前模式播放射门手势：划线或弹弓。</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TeamCfg/204</t>
+          <t>GuideStepCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_205</t>
+          <t>ActvSoccer_guide_chapter_3014</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>桑巴红魔</t>
+          <t>第一关切片201</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TeamCfg/205</t>
+          <t>GuideStepCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_206</t>
+          <t>ActvSoccer_guide_dialogue_3014</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>南美风暴</t>
+          <t>进攻完成，点击继续。</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TeamCfg/206</t>
+          <t>GuideStepCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_207</t>
+          <t>ActvSoccer_guide_gesture_3014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>潘帕斯之翼</t>
+          <t>点击手指点按继续按钮。</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TeamCfg/207</t>
+          <t>GuideStepCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_208</t>
+          <t>ActvSoccer_guide_chapter_3015</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>高卢雄鸡</t>
+          <t>第一关切片201</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TeamCfg/208</t>
+          <t>GuideStepCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3001</t>
+          <t>ActvSoccer_guide_dialogue_3015</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>社区杯·联</t>
+          <t>错过这次机会可能会影响比赛结果，可以使用回溯重试。</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TeamCfg/3001</t>
+          <t>GuideStepCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3002</t>
+          <t>ActvSoccer_guide_gesture_3015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>社区杯·FC</t>
+          <t>点击手指点按免费回溯按钮。</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TeamCfg/3002</t>
+          <t>GuideStepCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3003</t>
+          <t>ActvSoccer_guide_chapter_3020</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>社区杯·竞技</t>
+          <t>第一关切片202</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TeamCfg/3003</t>
+          <t>GuideStepCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3004</t>
+          <t>ActvSoccer_guide_dialogue_3020</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>社区杯·联合</t>
+          <t>有些机会需要先传给队友。把球传到队友脚下。</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TeamCfg/3004</t>
+          <t>GuideStepCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3005</t>
+          <t>ActvSoccer_guide_gesture_3020</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>社区杯·勇士</t>
+          <t>手指从主角脚下拖向队友目标区域。</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TeamCfg/3005</t>
+          <t>GuideStepCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3006</t>
+          <t>ActvSoccer_guide_chapter_3021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>城市联赛·联</t>
+          <t>第一关切片202</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TeamCfg/3006</t>
+          <t>GuideStepCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3007</t>
+          <t>ActvSoccer_guide_dialogue_3021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>城市联赛·FC</t>
+          <t>传球成功后，队友会完成射门，这会计为你的助攻。</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TeamCfg/3007</t>
+          <t>GuideStepCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3008</t>
+          <t>ActvSoccer_guide_chapter_3022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>城市联赛·竞技</t>
+          <t>第一关切片202</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TeamCfg/3008</t>
+          <t>GuideStepCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3009</t>
+          <t>ActvSoccer_guide_dialogue_3022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>城市联赛·联合</t>
+          <t>助攻完成，点击继续。</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TeamCfg/3009</t>
+          <t>GuideStepCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3010</t>
+          <t>ActvSoccer_guide_gesture_3022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>城市联赛·勇士</t>
+          <t>点击手指点按继续按钮。</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TeamCfg/3010</t>
+          <t>GuideStepCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3011</t>
+          <t>ActvSoccer_guide_chapter_3023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>省级联赛·联</t>
+          <t>第一关切片202</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TeamCfg/3011</t>
+          <t>GuideStepCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3012</t>
+          <t>ActvSoccer_guide_dialogue_3023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>省级联赛·FC</t>
+          <t>传球没有到位，可以回溯后再试一次。</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TeamCfg/3012</t>
+          <t>GuideStepCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3013</t>
+          <t>ActvSoccer_guide_gesture_3023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>省级联赛·竞技</t>
+          <t>点击手指点按回溯按钮；若玩家放弃则按失败继续。</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TeamCfg/3013</t>
+          <t>GuideStepCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3014</t>
+          <t>ActvSoccer_guide_chapter_3030</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>省级联赛·联合</t>
+          <t>第一关切片203</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TeamCfg/3014</t>
+          <t>GuideStepCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3015</t>
+          <t>ActvSoccer_guide_dialogue_3030</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>省级联赛·勇士</t>
+          <t>现在轮到你防守。看准射门方向，划线完成扑救。</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TeamCfg/3015</t>
+          <t>GuideStepCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3016</t>
+          <t>ActvSoccer_guide_gesture_3030</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>大区联赛·联</t>
+          <t>手指从门将位置滑向来球方向。</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TeamCfg/3016</t>
+          <t>GuideStepCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3017</t>
+          <t>ActvSoccer_guide_chapter_3031</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>大区联赛·FC</t>
+          <t>第一关切片203</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TeamCfg/3017</t>
+          <t>GuideStepCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3018</t>
+          <t>ActvSoccer_guide_dialogue_3031</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>大区联赛·竞技</t>
+          <t>扑救完成，点击继续。</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TeamCfg/3018</t>
+          <t>GuideStepCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3019</t>
+          <t>ActvSoccer_guide_gesture_3031</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>大区联赛·联合</t>
+          <t>点击手指点按继续按钮。</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TeamCfg/3019</t>
+          <t>GuideStepCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3020</t>
+          <t>ActvSoccer_guide_chapter_3032</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>大区联赛·勇士</t>
+          <t>第一关切片203</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TeamCfg/3020</t>
+          <t>GuideStepCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3021</t>
+          <t>ActvSoccer_guide_dialogue_3032</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>全国联赛·联</t>
+          <t>再试一次，沿着来球方向滑动。</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TeamCfg/3021</t>
+          <t>GuideStepCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3022</t>
+          <t>ActvSoccer_guide_gesture_3032</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>全国联赛·FC</t>
+          <t>重复播放门将滑向来球方向的手势；若玩家放弃则按失败继续。</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TeamCfg/3022</t>
+          <t>GuideStepCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3023</t>
+          <t>ActvSoccer_guide_chapter_3040</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>全国联赛·竞技</t>
+          <t>第一关结算</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TeamCfg/3023</t>
+          <t>GuideStepCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3024</t>
+          <t>ActvSoccer_guide_dialogue_3040</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>全国联赛·联合</t>
+          <t>比赛结束，查看本场奖励。</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TeamCfg/3024</t>
+          <t>GuideStepCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3025</t>
+          <t>ActvSoccer_guide_gesture_3040</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>全国联赛·勇士</t>
+          <t>点击手指点按结算确认按钮。</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TeamCfg/3025</t>
+          <t>GuideStepCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3026</t>
+          <t>ActvSoccer_guide_chapter_3041</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>洲际资格赛·联</t>
+          <t>第一关结算</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TeamCfg/3026</t>
+          <t>GuideStepCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3027</t>
+          <t>ActvSoccer_guide_dialogue_3041</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>洲际资格赛·FC</t>
+          <t>这里会展示本轮后的排名变化。</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TeamCfg/3027</t>
+          <t>GuideStepCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3028</t>
+          <t>ActvSoccer_guide_gesture_3041</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>洲际资格赛·竞技</t>
+          <t>点击手指点按排名结算确认按钮。</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TeamCfg/3028</t>
+          <t>GuideStepCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3029</t>
+          <t>ActvSoccer_preset_name_1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>洲际资格赛·联合</t>
+          <t>右路单刀</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TeamCfg/3029</t>
+          <t>SlicePresetCfg/1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3030</t>
+          <t>ActvSoccer_preset_name_5</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>洲际资格赛·勇士</t>
+          <t>左路单刀</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TeamCfg/3030</t>
+          <t>SlicePresetCfg/5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3031</t>
+          <t>ActvSoccer_preset_name_6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>洲际联赛·联</t>
+          <t>中路突破</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TeamCfg/3031</t>
+          <t>SlicePresetCfg/6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3032</t>
+          <t>ActvSoccer_preset_name_16</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>洲际联赛·FC</t>
+          <t>中路吊射</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TeamCfg/3032</t>
+          <t>SlicePresetCfg/16</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3033</t>
+          <t>ActvSoccer_preset_name_2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>洲际联赛·竞技</t>
+          <t>中路任意球</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TeamCfg/3033</t>
+          <t>SlicePresetCfg/2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3034</t>
+          <t>ActvSoccer_preset_name_7</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>洲际联赛·联合</t>
+          <t>左侧任意球</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TeamCfg/3034</t>
+          <t>SlicePresetCfg/7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3035</t>
+          <t>ActvSoccer_preset_name_8</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>洲际联赛·勇士</t>
+          <t>右侧任意球</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TeamCfg/3035</t>
+          <t>SlicePresetCfg/8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3036</t>
+          <t>ActvSoccer_preset_name_17</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>国际邀请赛·联</t>
+          <t>弧线任意球</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TeamCfg/3036</t>
+          <t>SlicePresetCfg/17</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3037</t>
+          <t>ActvSoccer_preset_name_3</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>国际邀请赛·FC</t>
+          <t>标准点球</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TeamCfg/3037</t>
+          <t>SlicePresetCfg/3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3038</t>
+          <t>ActvSoccer_preset_name_9</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>国际邀请赛·竞技</t>
+          <t>加压点球</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TeamCfg/3038</t>
+          <t>SlicePresetCfg/9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3039</t>
+          <t>ActvSoccer_preset_name_10</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>国际邀请赛·联合</t>
+          <t>左角球</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TeamCfg/3039</t>
+          <t>SlicePresetCfg/10</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3040</t>
+          <t>ActvSoccer_preset_name_11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>国际邀请赛·勇士</t>
+          <t>右角球</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TeamCfg/3040</t>
+          <t>SlicePresetCfg/11</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3041</t>
+          <t>ActvSoccer_preset_name_18</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>世界精英赛·联</t>
+          <t>后点包抄</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TeamCfg/3041</t>
+          <t>SlicePresetCfg/18</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3042</t>
+          <t>ActvSoccer_preset_name_12</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>世界精英赛·FC</t>
+          <t>左界外球</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TeamCfg/3042</t>
+          <t>SlicePresetCfg/12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3043</t>
+          <t>ActvSoccer_preset_name_13</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>世界精英赛·竞技</t>
+          <t>右界外球</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TeamCfg/3043</t>
+          <t>SlicePresetCfg/13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3044</t>
+          <t>ActvSoccer_preset_name_4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>世界精英赛·联合</t>
+          <t>基础守门</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TeamCfg/3044</t>
+          <t>SlicePresetCfg/4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3045</t>
+          <t>ActvSoccer_preset_name_14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>世界精英赛·勇士</t>
+          <t>大范围守门</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TeamCfg/3045</t>
+          <t>SlicePresetCfg/14</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3046</t>
+          <t>ActvSoccer_preset_name_15</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联</t>
+          <t>近距扑点</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TeamCfg/3046</t>
+          <t>SlicePresetCfg/15</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3047</t>
+          <t>ActvSoccer_preset_name_19</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>世界杯总决赛·FC</t>
+          <t>右肋斜插</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TeamCfg/3047</t>
+          <t>SlicePresetCfg/19</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3048</t>
+          <t>ActvSoccer_preset_name_20</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>世界杯总决赛·竞技</t>
+          <t>左肋斜插</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TeamCfg/3048</t>
+          <t>SlicePresetCfg/20</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3049</t>
+          <t>ActvSoccer_preset_name_21</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联合</t>
+          <t>禁区弧顶远射</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TeamCfg/3049</t>
+          <t>SlicePresetCfg/21</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3050</t>
+          <t>ActvSoccer_preset_name_22</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>世界杯总决赛·勇士</t>
+          <t>右路内切射门</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TeamCfg/3050</t>
+          <t>SlicePresetCfg/22</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_1</t>
+          <t>ActvSoccer_preset_name_23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>社区杯 第1/50轮</t>
+          <t>左路内切射门</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SeasonCfg/1</t>
+          <t>SlicePresetCfg/23</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_2</t>
+          <t>ActvSoccer_preset_name_24</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>社区杯 第2/50轮</t>
+          <t>倒三角回做</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SeasonCfg/2</t>
+          <t>SlicePresetCfg/24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_3</t>
+          <t>ActvSoccer_preset_name_25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>社区杯 第3/50轮</t>
+          <t>门前抢点</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SeasonCfg/3</t>
+          <t>SlicePresetCfg/25</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_4</t>
+          <t>ActvSoccer_preset_name_26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>社区杯 第4/50轮</t>
+          <t>禁区外吊射</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SeasonCfg/4</t>
+          <t>SlicePresetCfg/26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_5</t>
+          <t>ActvSoccer_preset_name_27</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>社区杯 第5/50轮</t>
+          <t>二点补射</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SeasonCfg/5</t>
+          <t>SlicePresetCfg/27</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_6</t>
+          <t>ActvSoccer_preset_name_28</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>城市联赛 第6/50轮</t>
+          <t>横向摆脱射门</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SeasonCfg/6</t>
+          <t>SlicePresetCfg/28</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_7</t>
+          <t>ActvSoccer_preset_name_29</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>城市联赛 第7/50轮</t>
+          <t>近距中路任意球</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SeasonCfg/7</t>
+          <t>SlicePresetCfg/29</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_8</t>
+          <t>ActvSoccer_preset_name_30</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>城市联赛 第8/50轮</t>
+          <t>远距中路任意球</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SeasonCfg/8</t>
+          <t>SlicePresetCfg/30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_9</t>
+          <t>ActvSoccer_preset_name_31</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>城市联赛 第9/50轮</t>
+          <t>右侧绕墙低射</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SeasonCfg/9</t>
+          <t>SlicePresetCfg/31</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_10</t>
+          <t>ActvSoccer_preset_name_32</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>城市联赛 第10/50轮</t>
+          <t>左侧绕墙低射</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SeasonCfg/10</t>
+          <t>SlicePresetCfg/32</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_11</t>
+          <t>ActvSoccer_preset_name_33</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>省级联赛 第11/50轮</t>
+          <t>传中任意球</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SeasonCfg/11</t>
+          <t>SlicePresetCfg/33</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_12</t>
+          <t>ActvSoccer_preset_name_34</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>省级联赛 第12/50轮</t>
+          <t>左下角点球</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SeasonCfg/12</t>
+          <t>SlicePresetCfg/34</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_13</t>
+          <t>ActvSoccer_preset_name_35</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>省级联赛 第13/50轮</t>
+          <t>右下角点球</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SeasonCfg/13</t>
+          <t>SlicePresetCfg/35</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_14</t>
+          <t>ActvSoccer_preset_name_36</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>省级联赛 第14/50轮</t>
+          <t>半高点球</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SeasonCfg/14</t>
+          <t>SlicePresetCfg/36</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_15</t>
+          <t>ActvSoccer_preset_name_37</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>省级联赛 第15/50轮</t>
+          <t>左前点角球</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SeasonCfg/15</t>
+          <t>SlicePresetCfg/37</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_16</t>
+          <t>ActvSoccer_preset_name_38</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>大区联赛 第16/50轮</t>
+          <t>右前点角球</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SeasonCfg/16</t>
+          <t>SlicePresetCfg/38</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_17</t>
+          <t>ActvSoccer_preset_name_39</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>大区联赛 第17/50轮</t>
+          <t>左后点高球</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SeasonCfg/17</t>
+          <t>SlicePresetCfg/39</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_18</t>
+          <t>ActvSoccer_preset_name_40</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>大区联赛 第18/50轮</t>
+          <t>右后点高球</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SeasonCfg/18</t>
+          <t>SlicePresetCfg/40</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_19</t>
+          <t>ActvSoccer_preset_name_41</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>大区联赛 第19/50轮</t>
+          <t>短角球配合</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SeasonCfg/19</t>
+          <t>SlicePresetCfg/41</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_20</t>
+          <t>ActvSoccer_preset_name_42</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>大区联赛 第20/50轮</t>
+          <t>低平扫门前</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SeasonCfg/20</t>
+          <t>SlicePresetCfg/42</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_21</t>
+          <t>ActvSoccer_preset_name_43</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>全国联赛 第21/50轮</t>
+          <t>禁区混战二点</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SeasonCfg/21</t>
+          <t>SlicePresetCfg/43</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_22</t>
+          <t>ActvSoccer_preset_name_44</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>全国联赛 第22/50轮</t>
+          <t>左侧近端接应</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SeasonCfg/22</t>
+          <t>SlicePresetCfg/44</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_23</t>
+          <t>ActvSoccer_preset_name_45</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>全国联赛 第23/50轮</t>
+          <t>右侧近端接应</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SeasonCfg/23</t>
+          <t>SlicePresetCfg/45</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_24</t>
+          <t>ActvSoccer_preset_name_46</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>全国联赛 第24/50轮</t>
+          <t>左侧远端转移</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SeasonCfg/24</t>
+          <t>SlicePresetCfg/46</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_25</t>
+          <t>ActvSoccer_preset_name_47</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>全国联赛 第25/50轮</t>
+          <t>右侧远端转移</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SeasonCfg/25</t>
+          <t>SlicePresetCfg/47</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_26</t>
+          <t>ActvSoccer_preset_name_48</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>洲际资格赛 第26/50轮</t>
+          <t>左路快速反击</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SeasonCfg/26</t>
+          <t>SlicePresetCfg/48</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_27</t>
+          <t>ActvSoccer_preset_name_49</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>洲际资格赛 第27/50轮</t>
+          <t>右路快速反击</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SeasonCfg/27</t>
+          <t>SlicePresetCfg/49</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_28</t>
+          <t>ActvSoccer_preset_name_50</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>洲际资格赛 第28/50轮</t>
+          <t>左侧低球扑救</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SeasonCfg/28</t>
+          <t>SlicePresetCfg/50</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_29</t>
+          <t>ActvSoccer_growth_fame_title_1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>洲际资格赛 第29/50轮</t>
+          <t>业余球员</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SeasonCfg/29</t>
+          <t>FameGrowthLevelCfg/1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_30</t>
+          <t>ActvSoccer_growth_fame_title_2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>洲际资格赛 第30/50轮</t>
+          <t>新秀</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SeasonCfg/30</t>
+          <t>FameGrowthLevelCfg/2</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_31</t>
+          <t>ActvSoccer_growth_fame_title_3</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>洲际联赛 第31/50轮</t>
+          <t>专业球员</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SeasonCfg/31</t>
+          <t>FameGrowthLevelCfg/3</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_32</t>
+          <t>ActvSoccer_growth_fame_title_4</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>洲际联赛 第32/50轮</t>
+          <t>明星</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SeasonCfg/32</t>
+          <t>FameGrowthLevelCfg/4</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_33</t>
+          <t>ActvSoccer_growth_fame_title_5</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>洲际联赛 第33/50轮</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SeasonCfg/33</t>
+          <t>FameGrowthLevelCfg/5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_34</t>
+          <t>ActvSoccer_growth_fame_title_6</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>洲际联赛 第34/50轮</t>
+          <t>世界级</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SeasonCfg/34</t>
+          <t>FameGrowthLevelCfg/6</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_35</t>
+          <t>ActvSoccer_growth_fame_title_7</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>洲际联赛 第35/50轮</t>
+          <t>传奇</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SeasonCfg/35</t>
+          <t>FameGrowthLevelCfg/7</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_36</t>
+          <t>ActvSoccer_team_name_101</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>国际邀请赛 第36/50轮</t>
+          <t>红星联</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SeasonCfg/36</t>
+          <t>TeamCfg/101</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_37</t>
+          <t>ActvSoccer_team_name_102</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>国际邀请赛 第37/50轮</t>
+          <t>莱茵青年</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SeasonCfg/37</t>
+          <t>TeamCfg/102</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_38</t>
+          <t>ActvSoccer_team_name_103</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>国际邀请赛 第38/50轮</t>
+          <t>桑巴之星</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SeasonCfg/38</t>
+          <t>TeamCfg/103</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_39</t>
+          <t>ActvSoccer_team_name_104</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>国际邀请赛 第39/50轮</t>
+          <t>蓝白雄鹰</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SeasonCfg/39</t>
+          <t>TeamCfg/104</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_40</t>
+          <t>ActvSoccer_team_name_201</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>国际邀请赛 第40/50轮</t>
+          <t>海港FC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SeasonCfg/40</t>
+          <t>TeamCfg/201</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_41</t>
+          <t>ActvSoccer_team_name_202</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>世界精英赛 第41/50轮</t>
+          <t>东方之鹰</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SeasonCfg/41</t>
+          <t>TeamCfg/202</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_42</t>
+          <t>ActvSoccer_team_name_203</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>世界精英赛 第42/50轮</t>
+          <t>北欧狼</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SeasonCfg/42</t>
+          <t>TeamCfg/203</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_43</t>
+          <t>ActvSoccer_team_name_204</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>世界精英赛 第43/50轮</t>
+          <t>阿根廷神鹰</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SeasonCfg/43</t>
+          <t>TeamCfg/204</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_44</t>
+          <t>ActvSoccer_team_name_205</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>世界精英赛 第44/50轮</t>
+          <t>桑巴红魔</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SeasonCfg/44</t>
+          <t>TeamCfg/205</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_45</t>
+          <t>ActvSoccer_team_name_206</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>世界精英赛 第45/50轮</t>
+          <t>南美风暴</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SeasonCfg/45</t>
+          <t>TeamCfg/206</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_46</t>
+          <t>ActvSoccer_team_name_207</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第46/50轮</t>
+          <t>潘帕斯之翼</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SeasonCfg/46</t>
+          <t>TeamCfg/207</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_47</t>
+          <t>ActvSoccer_team_name_208</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第47/50轮</t>
+          <t>高卢雄鸡</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SeasonCfg/47</t>
+          <t>TeamCfg/208</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_48</t>
+          <t>ActvSoccer_team_name_3001</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第48/50轮</t>
+          <t>社区杯·联</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SeasonCfg/48</t>
+          <t>TeamCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_49</t>
+          <t>ActvSoccer_team_name_3002</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第49/50轮</t>
+          <t>社区杯·FC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SeasonCfg/49</t>
+          <t>TeamCfg/3002</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_50</t>
+          <t>ActvSoccer_team_name_3003</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第50/50轮</t>
+          <t>社区杯·竞技</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SeasonCfg/50</t>
+          <t>TeamCfg/3003</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_team_build</t>
+          <t>ActvSoccer_team_name_3004</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>组队期</t>
+          <t>社区杯·联合</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>TeamCfg/3004</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_1</t>
+          <t>ActvSoccer_team_name_3005</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>发起/加入组队、命名队名队标、审批</t>
+          <t>社区杯·勇士</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>TeamCfg/3005</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
+          <t>ActvSoccer_team_name_3006</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>海选</t>
+          <t>城市联赛·联</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>TeamCfg/3006</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
+          <t>ActvSoccer_team_name_3007</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1天内筛出64强</t>
+          <t>城市联赛·FC</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>TeamCfg/3007</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
+          <t>ActvSoccer_team_name_3008</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>正赛第1轮</t>
+          <t>城市联赛·竞技</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>TeamCfg/3008</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
+          <t>ActvSoccer_team_name_3009</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>8组各一轮(64强)</t>
+          <t>城市联赛·联合</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>TeamCfg/3009</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
+          <t>ActvSoccer_team_name_3010</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>正赛第2轮</t>
+          <t>城市联赛·勇士</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>TeamCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
+          <t>ActvSoccer_team_name_3011</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>8组各一轮(32强)</t>
+          <t>省级联赛·联</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>TeamCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
+          <t>ActvSoccer_team_name_3012</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>正赛第3轮</t>
+          <t>省级联赛·FC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>TeamCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
+          <t>ActvSoccer_team_name_3013</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>8组各一轮(16强)</t>
+          <t>省级联赛·竞技</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>TeamCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
+          <t>ActvSoccer_team_name_3014</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>正赛第4轮</t>
+          <t>省级联赛·联合</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>TeamCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
+          <t>ActvSoccer_team_name_3015</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>8组决出组冠军→8强</t>
+          <t>省级联赛·勇士</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>TeamCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
+          <t>ActvSoccer_team_name_3016</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>正赛第5轮</t>
+          <t>大区联赛·联</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>TeamCfg/3016</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
+          <t>ActvSoccer_team_name_3017</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>8强淘汰赛(4强)</t>
+          <t>大区联赛·FC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>TeamCfg/3017</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
+          <t>ActvSoccer_team_name_3018</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>决赛</t>
+          <t>大区联赛·竞技</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>TeamCfg/3018</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
+          <t>ActvSoccer_team_name_3019</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>冠亚军决赛</t>
+          <t>大区联赛·联合</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>TeamCfg/3019</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
+          <t>ActvSoccer_team_name_3020</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>展示期</t>
+          <t>大区联赛·勇士</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/9</t>
+          <t>TeamCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
+          <t>ActvSoccer_team_name_3021</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>全国联赛·联</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>TeamCfg/3021</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3022</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>全国联赛·FC</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>TeamCfg/3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3023</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>全国联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>TeamCfg/3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3024</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>全国联赛·联合</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>TeamCfg/3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3025</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>全国联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>TeamCfg/3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3026</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>洲际资格赛·联</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>TeamCfg/3026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3027</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>洲际资格赛·FC</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>TeamCfg/3027</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3028</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>洲际资格赛·竞技</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>TeamCfg/3028</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3029</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>洲际资格赛·联合</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>TeamCfg/3029</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3030</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>洲际资格赛·勇士</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>TeamCfg/3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3031</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>洲际联赛·联</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>TeamCfg/3031</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3032</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>洲际联赛·FC</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>TeamCfg/3032</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3033</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>洲际联赛·竞技</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>TeamCfg/3033</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3034</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>洲际联赛·联合</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TeamCfg/3034</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3035</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>洲际联赛·勇士</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TeamCfg/3035</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3036</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>国际邀请赛·联</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>TeamCfg/3036</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3037</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>国际邀请赛·FC</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TeamCfg/3037</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3038</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>国际邀请赛·竞技</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TeamCfg/3038</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3039</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>国际邀请赛·联合</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>TeamCfg/3039</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3040</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>国际邀请赛·勇士</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>TeamCfg/3040</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3041</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>世界精英赛·联</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TeamCfg/3041</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3042</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>世界精英赛·FC</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TeamCfg/3042</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3043</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>世界精英赛·竞技</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TeamCfg/3043</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3044</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>世界精英赛·联合</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>TeamCfg/3044</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3045</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>世界精英赛·勇士</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TeamCfg/3045</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3046</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·联</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TeamCfg/3046</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3047</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·FC</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TeamCfg/3047</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3048</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·竞技</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TeamCfg/3048</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3049</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·联合</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TeamCfg/3049</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ActvSoccer_team_name_3050</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>世界杯总决赛·勇士</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TeamCfg/3050</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_1</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>社区杯 第1/50轮</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SeasonCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_2</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>社区杯 第2/50轮</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SeasonCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_3</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>社区杯 第3/50轮</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SeasonCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_4</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>社区杯 第4/50轮</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SeasonCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_5</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>社区杯 第5/50轮</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SeasonCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_6</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>城市联赛 第6/50轮</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SeasonCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_7</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>城市联赛 第7/50轮</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SeasonCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_8</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>城市联赛 第8/50轮</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SeasonCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_9</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>城市联赛 第9/50轮</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SeasonCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_10</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>城市联赛 第10/50轮</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SeasonCfg/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_11</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>省级联赛 第11/50轮</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SeasonCfg/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_12</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>省级联赛 第12/50轮</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SeasonCfg/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_13</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>省级联赛 第13/50轮</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SeasonCfg/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_14</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>省级联赛 第14/50轮</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SeasonCfg/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_15</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>省级联赛 第15/50轮</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SeasonCfg/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_16</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>大区联赛 第16/50轮</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SeasonCfg/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_17</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>大区联赛 第17/50轮</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SeasonCfg/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>大区联赛 第18/50轮</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SeasonCfg/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>大区联赛 第19/50轮</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SeasonCfg/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_20</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>大区联赛 第20/50轮</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SeasonCfg/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_21</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>全国联赛 第21/50轮</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SeasonCfg/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_22</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>全国联赛 第22/50轮</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SeasonCfg/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_23</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>全国联赛 第23/50轮</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SeasonCfg/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_24</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>全国联赛 第24/50轮</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SeasonCfg/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_25</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>全国联赛 第25/50轮</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SeasonCfg/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第26/50轮</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SeasonCfg/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_27</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第27/50轮</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SeasonCfg/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_28</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第28/50轮</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SeasonCfg/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_29</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第29/50轮</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SeasonCfg/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_30</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>洲际资格赛 第30/50轮</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SeasonCfg/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_31</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>洲际联赛 第31/50轮</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SeasonCfg/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_32</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>洲际联赛 第32/50轮</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SeasonCfg/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_33</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>洲际联赛 第33/50轮</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SeasonCfg/33</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_34</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>洲际联赛 第34/50轮</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SeasonCfg/34</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_35</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>洲际联赛 第35/50轮</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SeasonCfg/35</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_36</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第36/50轮</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SeasonCfg/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_37</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第37/50轮</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SeasonCfg/37</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_38</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第38/50轮</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SeasonCfg/38</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_39</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第39/50轮</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SeasonCfg/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_40</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第40/50轮</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SeasonCfg/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_41</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>世界精英赛 第41/50轮</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SeasonCfg/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_42</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>世界精英赛 第42/50轮</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SeasonCfg/42</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_43</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>世界精英赛 第43/50轮</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SeasonCfg/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_44</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>世界精英赛 第44/50轮</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SeasonCfg/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_45</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>世界精英赛 第45/50轮</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SeasonCfg/45</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_46</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第46/50轮</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SeasonCfg/46</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_47</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第47/50轮</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SeasonCfg/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_48</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第48/50轮</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SeasonCfg/48</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_49</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第49/50轮</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SeasonCfg/49</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_50</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第50/50轮</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SeasonCfg/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_team_build</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>组队期</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_1</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>发起/加入组队、命名队名队标、审批</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_3</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>海选</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_3</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1天内筛出64强</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_4</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>正赛第1轮</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_4</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>8组各一轮(64强)</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_5</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>正赛第2轮</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_5</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>8组各一轮(32强)</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_6</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>正赛第3轮</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_6</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>8组各一轮(16强)</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_7</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>正赛第4轮</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_7</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>8组决出组冠军→8强</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_8</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>正赛第5轮</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_8</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>8强淘汰赛(4强)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_9</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>决赛</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_9</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>冠亚军决赛</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_10</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>展示期</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
           <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C303" t="inlineStr">
         <is>
           <t>KnockoutPhaseCfg/9</t>
         </is>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C303"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1001</t>
+          <t>ActvSoccer_guide_dialogue_1001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>试训入口</t>
+          <t>先完成一次试训，熟悉比赛中的射门操作。</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -710,4809 +710,3755 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1001</t>
+          <t>ActvSoccer_guide_dialogue_1010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>先完成一次试训，熟悉比赛中的射门操作。</t>
+          <t>按住球员脚下区域，画出你想踢出的路线。</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1001</t>
+          <t>GuideStepCfg/1010</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1010</t>
+          <t>ActvSoccer_guide_dialogue_1011</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>松手后，球会沿着轨迹飞出。</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1010</t>
+          <t>GuideStepCfg/1011</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1010</t>
+          <t>ActvSoccer_guide_dialogue_1012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>按住球员脚下区域，画出你想踢出的路线。</t>
+          <t>做得好！继续下一项训练。</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1010</t>
+          <t>GuideStepCfg/1012</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1010</t>
+          <t>ActvSoccer_guide_dialogue_1013</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>白色手指从球员脚下按住，沿推荐轨迹拖向白色目标框，轨迹线循环播放。</t>
+          <t>再试一次，把路线画向白色目标框。</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1010</t>
+          <t>GuideStepCfg/1013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1011</t>
+          <t>ActvSoccer_guide_dialogue_1020</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>任意球需要避开人墙。拖动来选择方向和力量。</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1011</t>
+          <t>GuideStepCfg/1020</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1011</t>
+          <t>ActvSoccer_guide_dialogue_1021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>松手后，球会沿着轨迹飞出。</t>
+          <t>力量控制在65%左右，更容易命中目标。</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1011</t>
+          <t>GuideStepCfg/1021</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1011</t>
+          <t>ActvSoccer_guide_dialogue_1022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>手指沿轨迹到达目标框后松开，展示释放射门。</t>
+          <t>很好，任意球训练完成。</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1011</t>
+          <t>GuideStepCfg/1022</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1012</t>
+          <t>ActvSoccer_guide_dialogue_1023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>力量太小了，再向后拖动一些。</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1012</t>
+          <t>GuideStepCfg/1023</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1012</t>
+          <t>ActvSoccer_guide_dialogue_1024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>做得好！继续下一项训练。</t>
+          <t>力量太大了，稍微收一点力。</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1012</t>
+          <t>GuideStepCfg/1024</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1013</t>
+          <t>ActvSoccer_guide_dialogue_1025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>角度偏离目标，再调整射门方向。</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1013</t>
+          <t>GuideStepCfg/1025</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1013</t>
+          <t>ActvSoccer_guide_dialogue_1030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>再试一次，把路线画向白色目标框。</t>
+          <t>试训中可以自由切换操作方式，选择你更顺手的模式。</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1013</t>
+          <t>GuideStepCfg/1030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1013</t>
+          <t>ActvSoccer_guide_dialogue_1031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>重复播放从球员脚下划向目标框的轨迹手势。</t>
+          <t>现在把球踢向高亮区域。</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1013</t>
+          <t>GuideStepCfg/1031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1020</t>
+          <t>ActvSoccer_guide_dialogue_1032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>点球训练完成。</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1020</t>
+          <t>GuideStepCfg/1032</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1020</t>
+          <t>ActvSoccer_guide_dialogue_1033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>任意球需要避开人墙。拖动来选择方向和力量。</t>
+          <t>再试一次，瞄准高亮区域射门。</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1020</t>
+          <t>GuideStepCfg/1033</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1020</t>
+          <t>ActvSoccer_guide_dialogue_1040</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>手指从球向后拖拽，出现弹弓方向线和力度百分比。</t>
+          <t>试训完成。球队给你发来了邀请，挑选一支作为职业生涯起点。</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1020</t>
+          <t>GuideStepCfg/1040</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1021</t>
+          <t>ActvSoccer_guide_dialogue_2001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>第一场比赛已经准备好了，先从基础比赛开始。</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1021</t>
+          <t>GuideStepCfg/2001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1021</t>
+          <t>ActvSoccer_guide_dialogue_2010</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>力量控制在65%左右，更容易命中目标。</t>
+          <t>这里可以看到本场比赛目标。</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1021</t>
+          <t>GuideStepCfg/2010</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1021</t>
+          <t>ActvSoccer_guide_dialogue_2011</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>手指拖动到推荐力度点，力度数值从49%动到65%附近。</t>
+          <t>点击开球，开始你的第一场比赛。</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1021</t>
+          <t>GuideStepCfg/2011</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1022</t>
+          <t>ActvSoccer_guide_dialogue_3001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>比赛即将开始。</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1022</t>
+          <t>GuideStepCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1022</t>
+          <t>ActvSoccer_guide_dialogue_3010</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>很好，任意球训练完成。</t>
+          <t>黄色光圈表示当前由你操作的球员。</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1022</t>
+          <t>GuideStepCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1023</t>
+          <t>ActvSoccer_guide_dialogue_3011</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>这个标志表示这个方向上有你的队友。</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1023</t>
+          <t>GuideStepCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1023</t>
+          <t>ActvSoccer_guide_dialogue_3012</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>力量太小了，再向后拖动一些。</t>
+          <t>在屏幕上半部分左右滑动，可以移动相机观察场上情况。</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1023</t>
+          <t>GuideStepCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1023</t>
+          <t>ActvSoccer_guide_dialogue_3013</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>重复播放向后拖拽至65%附近的力度手势。</t>
+          <t>现在把球踢向白色目标区域。</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1023</t>
+          <t>GuideStepCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1024</t>
+          <t>ActvSoccer_guide_dialogue_3014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>进攻完成，点击继续。</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1024</t>
+          <t>GuideStepCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1024</t>
+          <t>ActvSoccer_guide_dialogue_3015</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>力量太大了，稍微收一点力。</t>
+          <t>错过这次机会可能会影响比赛结果，可以使用回溯重试。</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1024</t>
+          <t>GuideStepCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1024</t>
+          <t>ActvSoccer_guide_dialogue_3020</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>重复播放力度回收到65%附近的手势。</t>
+          <t>有些机会需要先传给队友。把球传到队友脚下。</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1024</t>
+          <t>GuideStepCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1025</t>
+          <t>ActvSoccer_guide_dialogue_3021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>传球成功后，队友会完成射门，这会计为你的助攻。</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1025</t>
+          <t>GuideStepCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1025</t>
+          <t>ActvSoccer_guide_dialogue_3022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>角度偏离目标，再调整射门方向。</t>
+          <t>助攻完成，点击继续。</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1025</t>
+          <t>GuideStepCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1025</t>
+          <t>ActvSoccer_guide_dialogue_3023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>重复播放拖动方向线进入黄色允许角度范围的手势。</t>
+          <t>传球没有到位，可以回溯后再试一次。</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1025</t>
+          <t>GuideStepCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1030</t>
+          <t>ActvSoccer_guide_dialogue_3030</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>现在轮到你防守。看准射门方向，划线完成扑救。</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1030</t>
+          <t>GuideStepCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1030</t>
+          <t>ActvSoccer_guide_dialogue_3031</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>试训中可以自由切换操作方式，选择你更顺手的模式。</t>
+          <t>扑救完成，点击继续。</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1030</t>
+          <t>GuideStepCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1030</t>
+          <t>ActvSoccer_guide_dialogue_3032</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>点击手指点按模式切换按钮，按钮在划线/弹弓之间切换。</t>
+          <t>再试一次，沿着来球方向滑动。</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1030</t>
+          <t>GuideStepCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1031</t>
+          <t>ActvSoccer_guide_dialogue_3040</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>比赛结束，查看本场奖励。</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1031</t>
+          <t>GuideStepCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1031</t>
+          <t>ActvSoccer_guide_dialogue_3041</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>现在把球踢向高亮区域。</t>
+          <t>这里会展示本轮后的排名变化。</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1031</t>
+          <t>GuideStepCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1031</t>
+          <t>ActvSoccer_preset_name_1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>按玩家当前模式播放对应手势：划线轨迹或弹弓拖拽。</t>
+          <t>右路单刀</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1031</t>
+          <t>SlicePresetCfg/1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1032</t>
+          <t>ActvSoccer_preset_name_5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>左路单刀</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1032</t>
+          <t>SlicePresetCfg/5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1032</t>
+          <t>ActvSoccer_preset_name_6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>点球训练完成。</t>
+          <t>中路突破</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1032</t>
+          <t>SlicePresetCfg/6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1033</t>
+          <t>ActvSoccer_preset_name_16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>试训关卡</t>
+          <t>中路吊射</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1033</t>
+          <t>SlicePresetCfg/16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1033</t>
+          <t>ActvSoccer_preset_name_2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>再试一次，瞄准高亮区域射门。</t>
+          <t>中路任意球</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1033</t>
+          <t>SlicePresetCfg/2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1033</t>
+          <t>ActvSoccer_preset_name_7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>按当前操作模式重复播放点球射门手势。</t>
+          <t>左侧任意球</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1033</t>
+          <t>SlicePresetCfg/7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1040</t>
+          <t>ActvSoccer_preset_name_8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>试训完成</t>
+          <t>右侧任意球</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1040</t>
+          <t>SlicePresetCfg/8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1040</t>
+          <t>ActvSoccer_preset_name_17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>试训完成。球队给你发来了邀请，挑选一支作为职业生涯起点。</t>
+          <t>弧线任意球</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1040</t>
+          <t>SlicePresetCfg/17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1040</t>
+          <t>ActvSoccer_preset_name_3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>点击手指循环点按确认按钮。</t>
+          <t>标准点球</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1040</t>
+          <t>SlicePresetCfg/3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_2001</t>
+          <t>ActvSoccer_preset_name_9</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>主界面强引导</t>
+          <t>加压点球</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2001</t>
+          <t>SlicePresetCfg/9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2001</t>
+          <t>ActvSoccer_preset_name_10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>第一场比赛已经准备好了，先从基础比赛开始。</t>
+          <t>左角球</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2001</t>
+          <t>SlicePresetCfg/10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_2001</t>
+          <t>ActvSoccer_preset_name_11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>点击手指点按主界面下一场比赛按钮。</t>
+          <t>右角球</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2001</t>
+          <t>SlicePresetCfg/11</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_2010</t>
+          <t>ActvSoccer_preset_name_18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>战前页引导</t>
+          <t>后点包抄</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2010</t>
+          <t>SlicePresetCfg/18</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2010</t>
+          <t>ActvSoccer_preset_name_12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>这里可以看到本场比赛目标。</t>
+          <t>左界外球</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2010</t>
+          <t>SlicePresetCfg/12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_2011</t>
+          <t>ActvSoccer_preset_name_13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>战前页引导</t>
+          <t>右界外球</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2011</t>
+          <t>SlicePresetCfg/13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2011</t>
+          <t>ActvSoccer_preset_name_4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>点击开球，开始你的第一场比赛。</t>
+          <t>基础守门</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2011</t>
+          <t>SlicePresetCfg/4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_2011</t>
+          <t>ActvSoccer_preset_name_14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>点击手指点按黄色开球按钮。</t>
+          <t>大范围守门</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2011</t>
+          <t>SlicePresetCfg/14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3001</t>
+          <t>ActvSoccer_preset_name_15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>第一关入场</t>
+          <t>近距扑点</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3001</t>
+          <t>SlicePresetCfg/15</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3001</t>
+          <t>ActvSoccer_preset_name_19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>比赛即将开始。</t>
+          <t>右肋斜插</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3001</t>
+          <t>SlicePresetCfg/19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3010</t>
+          <t>ActvSoccer_preset_name_20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>第一关切片201</t>
+          <t>左肋斜插</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3010</t>
+          <t>SlicePresetCfg/20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3010</t>
+          <t>ActvSoccer_preset_name_21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>黄色光圈表示当前由你操作的球员。</t>
+          <t>禁区弧顶远射</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3010</t>
+          <t>SlicePresetCfg/21</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3011</t>
+          <t>ActvSoccer_preset_name_22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>第一关切片201</t>
+          <t>右路内切射门</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3011</t>
+          <t>SlicePresetCfg/22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3011</t>
+          <t>ActvSoccer_preset_name_23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>这个标志表示这个方向上有你的队友。</t>
+          <t>左路内切射门</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3011</t>
+          <t>SlicePresetCfg/23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3011</t>
+          <t>ActvSoccer_preset_name_24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>点击手指点按明白了按钮。</t>
+          <t>倒三角回做</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3011</t>
+          <t>SlicePresetCfg/24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3012</t>
+          <t>ActvSoccer_preset_name_25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>第一关切片201</t>
+          <t>门前抢点</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3012</t>
+          <t>SlicePresetCfg/25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3012</t>
+          <t>ActvSoccer_preset_name_26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>在屏幕上半部分左右滑动，可以移动相机观察场上情况。</t>
+          <t>禁区外吊射</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3012</t>
+          <t>SlicePresetCfg/26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3012</t>
+          <t>ActvSoccer_preset_name_27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>手指在上半屏左右滑动一次，循环播放。</t>
+          <t>二点补射</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3012</t>
+          <t>SlicePresetCfg/27</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3013</t>
+          <t>ActvSoccer_preset_name_28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>第一关切片201</t>
+          <t>横向摆脱射门</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3013</t>
+          <t>SlicePresetCfg/28</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3013</t>
+          <t>ActvSoccer_preset_name_29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>现在把球踢向白色目标区域。</t>
+          <t>近距中路任意球</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3013</t>
+          <t>SlicePresetCfg/29</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3013</t>
+          <t>ActvSoccer_preset_name_30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>按当前锁定前模式播放射门手势：划线或弹弓。</t>
+          <t>远距中路任意球</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3013</t>
+          <t>SlicePresetCfg/30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3014</t>
+          <t>ActvSoccer_preset_name_31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>第一关切片201</t>
+          <t>右侧绕墙低射</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3014</t>
+          <t>SlicePresetCfg/31</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3014</t>
+          <t>ActvSoccer_preset_name_32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>进攻完成，点击继续。</t>
+          <t>左侧绕墙低射</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3014</t>
+          <t>SlicePresetCfg/32</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3014</t>
+          <t>ActvSoccer_preset_name_33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>点击手指点按继续按钮。</t>
+          <t>传中任意球</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3014</t>
+          <t>SlicePresetCfg/33</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3015</t>
+          <t>ActvSoccer_preset_name_34</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>第一关切片201</t>
+          <t>左下角点球</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3015</t>
+          <t>SlicePresetCfg/34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3015</t>
+          <t>ActvSoccer_preset_name_35</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>错过这次机会可能会影响比赛结果，可以使用回溯重试。</t>
+          <t>右下角点球</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3015</t>
+          <t>SlicePresetCfg/35</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3015</t>
+          <t>ActvSoccer_preset_name_36</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>点击手指点按免费回溯按钮。</t>
+          <t>半高点球</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3015</t>
+          <t>SlicePresetCfg/36</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3020</t>
+          <t>ActvSoccer_preset_name_37</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>第一关切片202</t>
+          <t>左前点角球</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3020</t>
+          <t>SlicePresetCfg/37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3020</t>
+          <t>ActvSoccer_preset_name_38</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>有些机会需要先传给队友。把球传到队友脚下。</t>
+          <t>右前点角球</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3020</t>
+          <t>SlicePresetCfg/38</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3020</t>
+          <t>ActvSoccer_preset_name_39</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>手指从主角脚下拖向队友目标区域。</t>
+          <t>左后点高球</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3020</t>
+          <t>SlicePresetCfg/39</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3021</t>
+          <t>ActvSoccer_preset_name_40</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>第一关切片202</t>
+          <t>右后点高球</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3021</t>
+          <t>SlicePresetCfg/40</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3021</t>
+          <t>ActvSoccer_preset_name_41</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>传球成功后，队友会完成射门，这会计为你的助攻。</t>
+          <t>短角球配合</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3021</t>
+          <t>SlicePresetCfg/41</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3022</t>
+          <t>ActvSoccer_preset_name_42</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>第一关切片202</t>
+          <t>低平扫门前</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3022</t>
+          <t>SlicePresetCfg/42</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3022</t>
+          <t>ActvSoccer_preset_name_43</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>助攻完成，点击继续。</t>
+          <t>禁区混战二点</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3022</t>
+          <t>SlicePresetCfg/43</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3022</t>
+          <t>ActvSoccer_preset_name_44</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>点击手指点按继续按钮。</t>
+          <t>左侧近端接应</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3022</t>
+          <t>SlicePresetCfg/44</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3023</t>
+          <t>ActvSoccer_preset_name_45</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>第一关切片202</t>
+          <t>右侧近端接应</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3023</t>
+          <t>SlicePresetCfg/45</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3023</t>
+          <t>ActvSoccer_preset_name_46</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>传球没有到位，可以回溯后再试一次。</t>
+          <t>左侧远端转移</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3023</t>
+          <t>SlicePresetCfg/46</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3023</t>
+          <t>ActvSoccer_preset_name_47</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>点击手指点按回溯按钮；若玩家放弃则按失败继续。</t>
+          <t>右侧远端转移</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3023</t>
+          <t>SlicePresetCfg/47</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3030</t>
+          <t>ActvSoccer_preset_name_48</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>第一关切片203</t>
+          <t>左路快速反击</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3030</t>
+          <t>SlicePresetCfg/48</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3030</t>
+          <t>ActvSoccer_preset_name_49</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>现在轮到你防守。看准射门方向，划线完成扑救。</t>
+          <t>右路快速反击</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3030</t>
+          <t>SlicePresetCfg/49</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3030</t>
+          <t>ActvSoccer_preset_name_50</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>手指从门将位置滑向来球方向。</t>
+          <t>左侧低球扑救</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3030</t>
+          <t>SlicePresetCfg/50</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3031</t>
+          <t>ActvSoccer_growth_fame_title_1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>第一关切片203</t>
+          <t>业余球员</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3031</t>
+          <t>FameGrowthLevelCfg/1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3031</t>
+          <t>ActvSoccer_growth_fame_title_2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>扑救完成，点击继续。</t>
+          <t>新秀</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3031</t>
+          <t>FameGrowthLevelCfg/2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3031</t>
+          <t>ActvSoccer_growth_fame_title_3</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>点击手指点按继续按钮。</t>
+          <t>专业球员</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3031</t>
+          <t>FameGrowthLevelCfg/3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3032</t>
+          <t>ActvSoccer_growth_fame_title_4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>第一关切片203</t>
+          <t>明星</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3032</t>
+          <t>FameGrowthLevelCfg/4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3032</t>
+          <t>ActvSoccer_growth_fame_title_5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>再试一次，沿着来球方向滑动。</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3032</t>
+          <t>FameGrowthLevelCfg/5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3032</t>
+          <t>ActvSoccer_growth_fame_title_6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>重复播放门将滑向来球方向的手势；若玩家放弃则按失败继续。</t>
+          <t>世界级</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3032</t>
+          <t>FameGrowthLevelCfg/6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3040</t>
+          <t>ActvSoccer_growth_fame_title_7</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>第一关结算</t>
+          <t>传奇</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3040</t>
+          <t>FameGrowthLevelCfg/7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3040</t>
+          <t>ActvSoccer_team_name_101</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>比赛结束，查看本场奖励。</t>
+          <t>红星联</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3040</t>
+          <t>TeamCfg/101</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3040</t>
+          <t>ActvSoccer_team_name_102</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>点击手指点按结算确认按钮。</t>
+          <t>莱茵青年</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3040</t>
+          <t>TeamCfg/102</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3041</t>
+          <t>ActvSoccer_team_name_103</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>第一关结算</t>
+          <t>桑巴之星</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3041</t>
+          <t>TeamCfg/103</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3041</t>
+          <t>ActvSoccer_team_name_104</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>这里会展示本轮后的排名变化。</t>
+          <t>蓝白雄鹰</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3041</t>
+          <t>TeamCfg/104</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3041</t>
+          <t>ActvSoccer_team_name_201</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>点击手指点按排名结算确认按钮。</t>
+          <t>海港FC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3041</t>
+          <t>TeamCfg/201</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_1</t>
+          <t>ActvSoccer_team_name_202</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>右路单刀</t>
+          <t>东方之鹰</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1</t>
+          <t>TeamCfg/202</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_5</t>
+          <t>ActvSoccer_team_name_203</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>左路单刀</t>
+          <t>北欧狼</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5</t>
+          <t>TeamCfg/203</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_6</t>
+          <t>ActvSoccer_team_name_204</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>中路突破</t>
+          <t>阿根廷神鹰</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6</t>
+          <t>TeamCfg/204</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_16</t>
+          <t>ActvSoccer_team_name_205</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>中路吊射</t>
+          <t>桑巴红魔</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/16</t>
+          <t>TeamCfg/205</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_2</t>
+          <t>ActvSoccer_team_name_206</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>中路任意球</t>
+          <t>南美风暴</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2</t>
+          <t>TeamCfg/206</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_7</t>
+          <t>ActvSoccer_team_name_207</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>左侧任意球</t>
+          <t>潘帕斯之翼</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/7</t>
+          <t>TeamCfg/207</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_8</t>
+          <t>ActvSoccer_team_name_208</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>右侧任意球</t>
+          <t>高卢雄鸡</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/8</t>
+          <t>TeamCfg/208</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_17</t>
+          <t>ActvSoccer_team_name_3001</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>弧线任意球</t>
+          <t>社区杯·联</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/17</t>
+          <t>TeamCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_3</t>
+          <t>ActvSoccer_team_name_3002</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>标准点球</t>
+          <t>社区杯·FC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3</t>
+          <t>TeamCfg/3002</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_9</t>
+          <t>ActvSoccer_team_name_3003</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>加压点球</t>
+          <t>社区杯·竞技</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9</t>
+          <t>TeamCfg/3003</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_10</t>
+          <t>ActvSoccer_team_name_3004</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>左角球</t>
+          <t>社区杯·联合</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/10</t>
+          <t>TeamCfg/3004</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_11</t>
+          <t>ActvSoccer_team_name_3005</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>右角球</t>
+          <t>社区杯·勇士</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/11</t>
+          <t>TeamCfg/3005</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_18</t>
+          <t>ActvSoccer_team_name_3006</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>后点包抄</t>
+          <t>城市联赛·联</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/18</t>
+          <t>TeamCfg/3006</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_12</t>
+          <t>ActvSoccer_team_name_3007</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>左界外球</t>
+          <t>城市联赛·FC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/12</t>
+          <t>TeamCfg/3007</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_13</t>
+          <t>ActvSoccer_team_name_3008</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>右界外球</t>
+          <t>城市联赛·竞技</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/13</t>
+          <t>TeamCfg/3008</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_4</t>
+          <t>ActvSoccer_team_name_3009</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>基础守门</t>
+          <t>城市联赛·联合</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4</t>
+          <t>TeamCfg/3009</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_14</t>
+          <t>ActvSoccer_team_name_3010</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>大范围守门</t>
+          <t>城市联赛·勇士</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/14</t>
+          <t>TeamCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_15</t>
+          <t>ActvSoccer_team_name_3011</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>近距扑点</t>
+          <t>省级联赛·联</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/15</t>
+          <t>TeamCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_19</t>
+          <t>ActvSoccer_team_name_3012</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>右肋斜插</t>
+          <t>省级联赛·FC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/19</t>
+          <t>TeamCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_20</t>
+          <t>ActvSoccer_team_name_3013</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>左肋斜插</t>
+          <t>省级联赛·竞技</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/20</t>
+          <t>TeamCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_21</t>
+          <t>ActvSoccer_team_name_3014</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>禁区弧顶远射</t>
+          <t>省级联赛·联合</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/21</t>
+          <t>TeamCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_22</t>
+          <t>ActvSoccer_team_name_3015</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>右路内切射门</t>
+          <t>省级联赛·勇士</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/22</t>
+          <t>TeamCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_23</t>
+          <t>ActvSoccer_team_name_3016</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>左路内切射门</t>
+          <t>大区联赛·联</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/23</t>
+          <t>TeamCfg/3016</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_24</t>
+          <t>ActvSoccer_team_name_3017</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>倒三角回做</t>
+          <t>大区联赛·FC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/24</t>
+          <t>TeamCfg/3017</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_25</t>
+          <t>ActvSoccer_team_name_3018</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>门前抢点</t>
+          <t>大区联赛·竞技</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/25</t>
+          <t>TeamCfg/3018</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_26</t>
+          <t>ActvSoccer_team_name_3019</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>禁区外吊射</t>
+          <t>大区联赛·联合</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/26</t>
+          <t>TeamCfg/3019</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_27</t>
+          <t>ActvSoccer_team_name_3020</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>二点补射</t>
+          <t>大区联赛·勇士</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/27</t>
+          <t>TeamCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_28</t>
+          <t>ActvSoccer_team_name_3021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>横向摆脱射门</t>
+          <t>全国联赛·联</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/28</t>
+          <t>TeamCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_29</t>
+          <t>ActvSoccer_team_name_3022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>近距中路任意球</t>
+          <t>全国联赛·FC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/29</t>
+          <t>TeamCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_30</t>
+          <t>ActvSoccer_team_name_3023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>远距中路任意球</t>
+          <t>全国联赛·竞技</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/30</t>
+          <t>TeamCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_31</t>
+          <t>ActvSoccer_team_name_3024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>右侧绕墙低射</t>
+          <t>全国联赛·联合</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/31</t>
+          <t>TeamCfg/3024</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_32</t>
+          <t>ActvSoccer_team_name_3025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>左侧绕墙低射</t>
+          <t>全国联赛·勇士</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/32</t>
+          <t>TeamCfg/3025</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_33</t>
+          <t>ActvSoccer_team_name_3026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>传中任意球</t>
+          <t>洲际资格赛·联</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/33</t>
+          <t>TeamCfg/3026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_34</t>
+          <t>ActvSoccer_team_name_3027</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>左下角点球</t>
+          <t>洲际资格赛·FC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/34</t>
+          <t>TeamCfg/3027</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_35</t>
+          <t>ActvSoccer_team_name_3028</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>右下角点球</t>
+          <t>洲际资格赛·竞技</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/35</t>
+          <t>TeamCfg/3028</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_36</t>
+          <t>ActvSoccer_team_name_3029</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>半高点球</t>
+          <t>洲际资格赛·联合</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/36</t>
+          <t>TeamCfg/3029</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_37</t>
+          <t>ActvSoccer_team_name_3030</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>左前点角球</t>
+          <t>洲际资格赛·勇士</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/37</t>
+          <t>TeamCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_38</t>
+          <t>ActvSoccer_team_name_3031</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>右前点角球</t>
+          <t>洲际联赛·联</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/38</t>
+          <t>TeamCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_39</t>
+          <t>ActvSoccer_team_name_3032</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>左后点高球</t>
+          <t>洲际联赛·FC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/39</t>
+          <t>TeamCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_40</t>
+          <t>ActvSoccer_team_name_3033</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>右后点高球</t>
+          <t>洲际联赛·竞技</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/40</t>
+          <t>TeamCfg/3033</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_41</t>
+          <t>ActvSoccer_team_name_3034</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>短角球配合</t>
+          <t>洲际联赛·联合</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/41</t>
+          <t>TeamCfg/3034</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_42</t>
+          <t>ActvSoccer_team_name_3035</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>低平扫门前</t>
+          <t>洲际联赛·勇士</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/42</t>
+          <t>TeamCfg/3035</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_43</t>
+          <t>ActvSoccer_team_name_3036</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>禁区混战二点</t>
+          <t>国际邀请赛·联</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/43</t>
+          <t>TeamCfg/3036</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_44</t>
+          <t>ActvSoccer_team_name_3037</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>左侧近端接应</t>
+          <t>国际邀请赛·FC</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/44</t>
+          <t>TeamCfg/3037</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_45</t>
+          <t>ActvSoccer_team_name_3038</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>右侧近端接应</t>
+          <t>国际邀请赛·竞技</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/45</t>
+          <t>TeamCfg/3038</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_46</t>
+          <t>ActvSoccer_team_name_3039</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>左侧远端转移</t>
+          <t>国际邀请赛·联合</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/46</t>
+          <t>TeamCfg/3039</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_47</t>
+          <t>ActvSoccer_team_name_3040</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>右侧远端转移</t>
+          <t>国际邀请赛·勇士</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/47</t>
+          <t>TeamCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_48</t>
+          <t>ActvSoccer_team_name_3041</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>左路快速反击</t>
+          <t>世界精英赛·联</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/48</t>
+          <t>TeamCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_49</t>
+          <t>ActvSoccer_team_name_3042</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>右路快速反击</t>
+          <t>世界精英赛·FC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/49</t>
+          <t>TeamCfg/3042</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_50</t>
+          <t>ActvSoccer_team_name_3043</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>左侧低球扑救</t>
+          <t>世界精英赛·竞技</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/50</t>
+          <t>TeamCfg/3043</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_1</t>
+          <t>ActvSoccer_team_name_3044</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>业余球员</t>
+          <t>世界精英赛·联合</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/1</t>
+          <t>TeamCfg/3044</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_2</t>
+          <t>ActvSoccer_team_name_3045</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>新秀</t>
+          <t>世界精英赛·勇士</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/2</t>
+          <t>TeamCfg/3045</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_3</t>
+          <t>ActvSoccer_team_name_3046</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>专业球员</t>
+          <t>世界杯总决赛·联</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/3</t>
+          <t>TeamCfg/3046</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_4</t>
+          <t>ActvSoccer_team_name_3047</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>明星</t>
+          <t>世界杯总决赛·FC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/4</t>
+          <t>TeamCfg/3047</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_5</t>
+          <t>ActvSoccer_team_name_3048</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>大师</t>
+          <t>世界杯总决赛·竞技</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/5</t>
+          <t>TeamCfg/3048</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_6</t>
+          <t>ActvSoccer_team_name_3049</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>世界级</t>
+          <t>世界杯总决赛·联合</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/6</t>
+          <t>TeamCfg/3049</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_7</t>
+          <t>ActvSoccer_team_name_3050</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>传奇</t>
+          <t>世界杯总决赛·勇士</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/7</t>
+          <t>TeamCfg/3050</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_101</t>
+          <t>ActvSoccer_season_league_name_1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>红星联</t>
+          <t>社区杯 第1/50轮</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TeamCfg/101</t>
+          <t>SeasonCfg/1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_102</t>
+          <t>ActvSoccer_season_league_name_2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>莱茵青年</t>
+          <t>社区杯 第2/50轮</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TeamCfg/102</t>
+          <t>SeasonCfg/2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_103</t>
+          <t>ActvSoccer_season_league_name_3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>桑巴之星</t>
+          <t>社区杯 第3/50轮</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TeamCfg/103</t>
+          <t>SeasonCfg/3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_104</t>
+          <t>ActvSoccer_season_league_name_4</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>蓝白雄鹰</t>
+          <t>社区杯 第4/50轮</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TeamCfg/104</t>
+          <t>SeasonCfg/4</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_201</t>
+          <t>ActvSoccer_season_league_name_5</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>海港FC</t>
+          <t>社区杯 第5/50轮</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TeamCfg/201</t>
+          <t>SeasonCfg/5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_202</t>
+          <t>ActvSoccer_season_league_name_6</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>东方之鹰</t>
+          <t>城市联赛 第6/50轮</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TeamCfg/202</t>
+          <t>SeasonCfg/6</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_203</t>
+          <t>ActvSoccer_season_league_name_7</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>北欧狼</t>
+          <t>城市联赛 第7/50轮</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TeamCfg/203</t>
+          <t>SeasonCfg/7</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_204</t>
+          <t>ActvSoccer_season_league_name_8</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>阿根廷神鹰</t>
+          <t>城市联赛 第8/50轮</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TeamCfg/204</t>
+          <t>SeasonCfg/8</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_205</t>
+          <t>ActvSoccer_season_league_name_9</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>桑巴红魔</t>
+          <t>城市联赛 第9/50轮</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TeamCfg/205</t>
+          <t>SeasonCfg/9</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_206</t>
+          <t>ActvSoccer_season_league_name_10</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>南美风暴</t>
+          <t>城市联赛 第10/50轮</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TeamCfg/206</t>
+          <t>SeasonCfg/10</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_207</t>
+          <t>ActvSoccer_season_league_name_11</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>潘帕斯之翼</t>
+          <t>省级联赛 第11/50轮</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>TeamCfg/207</t>
+          <t>SeasonCfg/11</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_208</t>
+          <t>ActvSoccer_season_league_name_12</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>高卢雄鸡</t>
+          <t>省级联赛 第12/50轮</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TeamCfg/208</t>
+          <t>SeasonCfg/12</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3001</t>
+          <t>ActvSoccer_season_league_name_13</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>社区杯·联</t>
+          <t>省级联赛 第13/50轮</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TeamCfg/3001</t>
+          <t>SeasonCfg/13</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3002</t>
+          <t>ActvSoccer_season_league_name_14</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>社区杯·FC</t>
+          <t>省级联赛 第14/50轮</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>TeamCfg/3002</t>
+          <t>SeasonCfg/14</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3003</t>
+          <t>ActvSoccer_season_league_name_15</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>社区杯·竞技</t>
+          <t>省级联赛 第15/50轮</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TeamCfg/3003</t>
+          <t>SeasonCfg/15</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3004</t>
+          <t>ActvSoccer_season_league_name_16</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>社区杯·联合</t>
+          <t>大区联赛 第16/50轮</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TeamCfg/3004</t>
+          <t>SeasonCfg/16</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3005</t>
+          <t>ActvSoccer_season_league_name_17</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>社区杯·勇士</t>
+          <t>大区联赛 第17/50轮</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TeamCfg/3005</t>
+          <t>SeasonCfg/17</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3006</t>
+          <t>ActvSoccer_season_league_name_18</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>城市联赛·联</t>
+          <t>大区联赛 第18/50轮</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TeamCfg/3006</t>
+          <t>SeasonCfg/18</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3007</t>
+          <t>ActvSoccer_season_league_name_19</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>城市联赛·FC</t>
+          <t>大区联赛 第19/50轮</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TeamCfg/3007</t>
+          <t>SeasonCfg/19</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3008</t>
+          <t>ActvSoccer_season_league_name_20</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>城市联赛·竞技</t>
+          <t>大区联赛 第20/50轮</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TeamCfg/3008</t>
+          <t>SeasonCfg/20</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3009</t>
+          <t>ActvSoccer_season_league_name_21</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>城市联赛·联合</t>
+          <t>全国联赛 第21/50轮</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TeamCfg/3009</t>
+          <t>SeasonCfg/21</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3010</t>
+          <t>ActvSoccer_season_league_name_22</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>城市联赛·勇士</t>
+          <t>全国联赛 第22/50轮</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TeamCfg/3010</t>
+          <t>SeasonCfg/22</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3011</t>
+          <t>ActvSoccer_season_league_name_23</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>省级联赛·联</t>
+          <t>全国联赛 第23/50轮</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TeamCfg/3011</t>
+          <t>SeasonCfg/23</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3012</t>
+          <t>ActvSoccer_season_league_name_24</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>省级联赛·FC</t>
+          <t>全国联赛 第24/50轮</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TeamCfg/3012</t>
+          <t>SeasonCfg/24</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3013</t>
+          <t>ActvSoccer_season_league_name_25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>省级联赛·竞技</t>
+          <t>全国联赛 第25/50轮</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TeamCfg/3013</t>
+          <t>SeasonCfg/25</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3014</t>
+          <t>ActvSoccer_season_league_name_26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>省级联赛·联合</t>
+          <t>洲际资格赛 第26/50轮</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TeamCfg/3014</t>
+          <t>SeasonCfg/26</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3015</t>
+          <t>ActvSoccer_season_league_name_27</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>省级联赛·勇士</t>
+          <t>洲际资格赛 第27/50轮</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TeamCfg/3015</t>
+          <t>SeasonCfg/27</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3016</t>
+          <t>ActvSoccer_season_league_name_28</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>大区联赛·联</t>
+          <t>洲际资格赛 第28/50轮</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TeamCfg/3016</t>
+          <t>SeasonCfg/28</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3017</t>
+          <t>ActvSoccer_season_league_name_29</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>大区联赛·FC</t>
+          <t>洲际资格赛 第29/50轮</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TeamCfg/3017</t>
+          <t>SeasonCfg/29</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3018</t>
+          <t>ActvSoccer_season_league_name_30</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>大区联赛·竞技</t>
+          <t>洲际资格赛 第30/50轮</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TeamCfg/3018</t>
+          <t>SeasonCfg/30</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3019</t>
+          <t>ActvSoccer_season_league_name_31</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>大区联赛·联合</t>
+          <t>洲际联赛 第31/50轮</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TeamCfg/3019</t>
+          <t>SeasonCfg/31</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3020</t>
+          <t>ActvSoccer_season_league_name_32</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>大区联赛·勇士</t>
+          <t>洲际联赛 第32/50轮</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TeamCfg/3020</t>
+          <t>SeasonCfg/32</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3021</t>
+          <t>ActvSoccer_season_league_name_33</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>全国联赛·联</t>
+          <t>洲际联赛 第33/50轮</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>TeamCfg/3021</t>
+          <t>SeasonCfg/33</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3022</t>
+          <t>ActvSoccer_season_league_name_34</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>全国联赛·FC</t>
+          <t>洲际联赛 第34/50轮</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>TeamCfg/3022</t>
+          <t>SeasonCfg/34</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3023</t>
+          <t>ActvSoccer_season_league_name_35</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>全国联赛·竞技</t>
+          <t>洲际联赛 第35/50轮</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>TeamCfg/3023</t>
+          <t>SeasonCfg/35</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3024</t>
+          <t>ActvSoccer_season_league_name_36</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>全国联赛·联合</t>
+          <t>国际邀请赛 第36/50轮</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TeamCfg/3024</t>
+          <t>SeasonCfg/36</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3025</t>
+          <t>ActvSoccer_season_league_name_37</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>全国联赛·勇士</t>
+          <t>国际邀请赛 第37/50轮</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>TeamCfg/3025</t>
+          <t>SeasonCfg/37</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3026</t>
+          <t>ActvSoccer_season_league_name_38</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>洲际资格赛·联</t>
+          <t>国际邀请赛 第38/50轮</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TeamCfg/3026</t>
+          <t>SeasonCfg/38</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3027</t>
+          <t>ActvSoccer_season_league_name_39</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>洲际资格赛·FC</t>
+          <t>国际邀请赛 第39/50轮</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>TeamCfg/3027</t>
+          <t>SeasonCfg/39</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3028</t>
+          <t>ActvSoccer_season_league_name_40</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>洲际资格赛·竞技</t>
+          <t>国际邀请赛 第40/50轮</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TeamCfg/3028</t>
+          <t>SeasonCfg/40</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3029</t>
+          <t>ActvSoccer_season_league_name_41</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>洲际资格赛·联合</t>
+          <t>世界精英赛 第41/50轮</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TeamCfg/3029</t>
+          <t>SeasonCfg/41</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3030</t>
+          <t>ActvSoccer_season_league_name_42</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>洲际资格赛·勇士</t>
+          <t>世界精英赛 第42/50轮</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>TeamCfg/3030</t>
+          <t>SeasonCfg/42</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3031</t>
+          <t>ActvSoccer_season_league_name_43</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>洲际联赛·联</t>
+          <t>世界精英赛 第43/50轮</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TeamCfg/3031</t>
+          <t>SeasonCfg/43</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3032</t>
+          <t>ActvSoccer_season_league_name_44</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>洲际联赛·FC</t>
+          <t>世界精英赛 第44/50轮</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>TeamCfg/3032</t>
+          <t>SeasonCfg/44</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3033</t>
+          <t>ActvSoccer_season_league_name_45</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>洲际联赛·竞技</t>
+          <t>世界精英赛 第45/50轮</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TeamCfg/3033</t>
+          <t>SeasonCfg/45</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3034</t>
+          <t>ActvSoccer_season_league_name_46</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>洲际联赛·联合</t>
+          <t>世界杯总决赛 第46/50轮</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>TeamCfg/3034</t>
+          <t>SeasonCfg/46</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3035</t>
+          <t>ActvSoccer_season_league_name_47</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>洲际联赛·勇士</t>
+          <t>世界杯总决赛 第47/50轮</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>TeamCfg/3035</t>
+          <t>SeasonCfg/47</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3036</t>
+          <t>ActvSoccer_season_league_name_48</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>国际邀请赛·联</t>
+          <t>世界杯总决赛 第48/50轮</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TeamCfg/3036</t>
+          <t>SeasonCfg/48</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3037</t>
+          <t>ActvSoccer_season_league_name_49</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>国际邀请赛·FC</t>
+          <t>世界杯总决赛 第49/50轮</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TeamCfg/3037</t>
+          <t>SeasonCfg/49</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3038</t>
+          <t>ActvSoccer_season_league_name_50</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>国际邀请赛·竞技</t>
+          <t>世界杯总决赛 第50/50轮</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TeamCfg/3038</t>
+          <t>SeasonCfg/50</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3039</t>
+          <t>ActvSoccer_knockout_phase_name_team_build</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>国际邀请赛·联合</t>
+          <t>组队期</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TeamCfg/3039</t>
+          <t>KnockoutPhaseCfg/1</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3040</t>
+          <t>ActvSoccer_knockout_day_content_1</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>国际邀请赛·勇士</t>
+          <t>发起/加入组队、命名队名队标、审批</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>TeamCfg/3040</t>
+          <t>KnockoutPhaseCfg/1</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3041</t>
+          <t>ActvSoccer_knockout_phase_name_3</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>世界精英赛·联</t>
+          <t>海选</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>TeamCfg/3041</t>
+          <t>KnockoutPhaseCfg/2</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3042</t>
+          <t>ActvSoccer_knockout_day_content_3</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>世界精英赛·FC</t>
+          <t>1天内筛出64强</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>TeamCfg/3042</t>
+          <t>KnockoutPhaseCfg/2</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3043</t>
+          <t>ActvSoccer_knockout_phase_name_4</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>世界精英赛·竞技</t>
+          <t>正赛第1轮</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>TeamCfg/3043</t>
+          <t>KnockoutPhaseCfg/3</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3044</t>
+          <t>ActvSoccer_knockout_day_content_4</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>世界精英赛·联合</t>
+          <t>8组各一轮(64强)</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>TeamCfg/3044</t>
+          <t>KnockoutPhaseCfg/3</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3045</t>
+          <t>ActvSoccer_knockout_phase_name_5</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>世界精英赛·勇士</t>
+          <t>正赛第2轮</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TeamCfg/3045</t>
+          <t>KnockoutPhaseCfg/4</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3046</t>
+          <t>ActvSoccer_knockout_day_content_5</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联</t>
+          <t>8组各一轮(32强)</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>TeamCfg/3046</t>
+          <t>KnockoutPhaseCfg/4</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3047</t>
+          <t>ActvSoccer_knockout_phase_name_6</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>世界杯总决赛·FC</t>
+          <t>正赛第3轮</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TeamCfg/3047</t>
+          <t>KnockoutPhaseCfg/5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3048</t>
+          <t>ActvSoccer_knockout_day_content_6</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>世界杯总决赛·竞技</t>
+          <t>8组各一轮(16强)</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TeamCfg/3048</t>
+          <t>KnockoutPhaseCfg/5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3049</t>
+          <t>ActvSoccer_knockout_phase_name_7</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联合</t>
+          <t>正赛第4轮</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TeamCfg/3049</t>
+          <t>KnockoutPhaseCfg/6</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3050</t>
+          <t>ActvSoccer_knockout_day_content_7</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>世界杯总决赛·勇士</t>
+          <t>8组决出组冠军→8强</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TeamCfg/3050</t>
+          <t>KnockoutPhaseCfg/6</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_1</t>
+          <t>ActvSoccer_knockout_phase_name_8</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>社区杯 第1/50轮</t>
+          <t>正赛第5轮</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>SeasonCfg/1</t>
+          <t>KnockoutPhaseCfg/7</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_2</t>
+          <t>ActvSoccer_knockout_day_content_8</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>社区杯 第2/50轮</t>
+          <t>8强淘汰赛(4强)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SeasonCfg/2</t>
+          <t>KnockoutPhaseCfg/7</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_3</t>
+          <t>ActvSoccer_knockout_phase_name_9</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>社区杯 第3/50轮</t>
+          <t>决赛</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>SeasonCfg/3</t>
+          <t>KnockoutPhaseCfg/8</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_4</t>
+          <t>ActvSoccer_knockout_day_content_9</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>社区杯 第4/50轮</t>
+          <t>冠亚军决赛</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SeasonCfg/4</t>
+          <t>KnockoutPhaseCfg/8</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_5</t>
+          <t>ActvSoccer_knockout_phase_name_10</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>社区杯 第5/50轮</t>
+          <t>展示期</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SeasonCfg/5</t>
+          <t>KnockoutPhaseCfg/9</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_6</t>
+          <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>城市联赛 第6/50轮</t>
+          <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
-        <is>
-          <t>SeasonCfg/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_7</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>城市联赛 第7/50轮</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>SeasonCfg/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_8</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>城市联赛 第8/50轮</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>SeasonCfg/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_9</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>城市联赛 第9/50轮</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>SeasonCfg/9</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_10</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>城市联赛 第10/50轮</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>SeasonCfg/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_11</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>省级联赛 第11/50轮</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>SeasonCfg/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_12</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>省级联赛 第12/50轮</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>SeasonCfg/12</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_13</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>省级联赛 第13/50轮</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>SeasonCfg/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_14</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>省级联赛 第14/50轮</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>SeasonCfg/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_15</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>省级联赛 第15/50轮</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>SeasonCfg/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_16</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>大区联赛 第16/50轮</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>SeasonCfg/16</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_17</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>大区联赛 第17/50轮</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>SeasonCfg/17</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_18</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>大区联赛 第18/50轮</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>SeasonCfg/18</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_19</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>大区联赛 第19/50轮</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>SeasonCfg/19</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_20</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>大区联赛 第20/50轮</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>SeasonCfg/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_21</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>全国联赛 第21/50轮</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>SeasonCfg/21</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_22</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>全国联赛 第22/50轮</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>SeasonCfg/22</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_23</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>全国联赛 第23/50轮</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>SeasonCfg/23</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_24</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>全国联赛 第24/50轮</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>SeasonCfg/24</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_25</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>全国联赛 第25/50轮</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>SeasonCfg/25</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_26</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>洲际资格赛 第26/50轮</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>SeasonCfg/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_27</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>洲际资格赛 第27/50轮</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>SeasonCfg/27</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_28</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>洲际资格赛 第28/50轮</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>SeasonCfg/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_29</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>洲际资格赛 第29/50轮</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>SeasonCfg/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_30</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>洲际资格赛 第30/50轮</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>SeasonCfg/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_31</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>洲际联赛 第31/50轮</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>SeasonCfg/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_32</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>洲际联赛 第32/50轮</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>SeasonCfg/32</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_33</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>洲际联赛 第33/50轮</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>SeasonCfg/33</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_34</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>洲际联赛 第34/50轮</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>SeasonCfg/34</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_35</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>洲际联赛 第35/50轮</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>SeasonCfg/35</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_36</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第36/50轮</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>SeasonCfg/36</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_37</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第37/50轮</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>SeasonCfg/37</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_38</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第38/50轮</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>SeasonCfg/38</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_39</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第39/50轮</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>SeasonCfg/39</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_40</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第40/50轮</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>SeasonCfg/40</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_41</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>世界精英赛 第41/50轮</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>SeasonCfg/41</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_42</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>世界精英赛 第42/50轮</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>SeasonCfg/42</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_43</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>世界精英赛 第43/50轮</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>SeasonCfg/43</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_44</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>世界精英赛 第44/50轮</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>SeasonCfg/44</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_45</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>世界精英赛 第45/50轮</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>SeasonCfg/45</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_46</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第46/50轮</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>SeasonCfg/46</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_47</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第47/50轮</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>SeasonCfg/47</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_48</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第48/50轮</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>SeasonCfg/48</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_49</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第49/50轮</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>SeasonCfg/49</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_50</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第50/50轮</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>SeasonCfg/50</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_team_build</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>组队期</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_1</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>发起/加入组队、命名队名队标、审批</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>海选</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>1天内筛出64强</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>正赛第1轮</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>8组各一轮(64强)</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>正赛第2轮</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>8组各一轮(32强)</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>正赛第3轮</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>8组各一轮(16强)</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>正赛第4轮</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>8组决出组冠军→8强</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>正赛第5轮</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>8强淘汰赛(4强)</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>决赛</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>冠亚军决赛</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>展示期</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/9</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_10</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>冠军展示+兑换商店可用</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
         <is>
           <t>KnockoutPhaseCfg/9</t>
         </is>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C241"/>
+  <dimension ref="A1:C270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2138,2327 +2138,2820 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_1</t>
+          <t>ActvSoccer_preset_ref_9001</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>业余球员</t>
+          <t>弧顶正面推进</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/1</t>
+          <t>SlicePresetCfg/9001/ref:进攻1.png</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_2</t>
+          <t>ActvSoccer_preset_ref_9002</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>新秀</t>
+          <t>右肋雪地单刀</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/2</t>
+          <t>SlicePresetCfg/9002/ref:进攻2.png</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_3</t>
+          <t>ActvSoccer_preset_ref_9003</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>专业球员</t>
+          <t>左肋外侧推进</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/3</t>
+          <t>SlicePresetCfg/9003/ref:进攻3.png</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_4</t>
+          <t>ActvSoccer_preset_ref_9004</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>明星</t>
+          <t>禁区前穿人墙</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/4</t>
+          <t>SlicePresetCfg/9004/ref:进攻5.png</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_5</t>
+          <t>ActvSoccer_preset_ref_9005</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>大师</t>
+          <t>右侧倒地近射</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/5</t>
+          <t>SlicePresetCfg/9005/ref:进攻6.png</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_6</t>
+          <t>ActvSoccer_preset_ref_9006</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>世界级</t>
+          <t>右路三角压迫</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/6</t>
+          <t>SlicePresetCfg/9006/ref:进攻7.png</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_7</t>
+          <t>ActvSoccer_preset_ref_9007</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>传奇</t>
+          <t>左肋多人包围</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/7</t>
+          <t>SlicePresetCfg/9007/ref:进攻8.png</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_101</t>
+          <t>ActvSoccer_preset_ref_9008</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>红星联</t>
+          <t>弧顶密集防线</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TeamCfg/101</t>
+          <t>SlicePresetCfg/9008/ref:进攻9.png</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_102</t>
+          <t>ActvSoccer_preset_ref_9009</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>莱茵青年</t>
+          <t>左路远距推进</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TeamCfg/102</t>
+          <t>SlicePresetCfg/9009/ref:进攻10.png</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_103</t>
+          <t>ActvSoccer_preset_ref_9010</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>桑巴之星</t>
+          <t>中路远射</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TeamCfg/103</t>
+          <t>SlicePresetCfg/9010/ref:进攻11.png</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_104</t>
+          <t>ActvSoccer_preset_ref_9011</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>蓝白雄鹰</t>
+          <t>右路斜向禁区</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TeamCfg/104</t>
+          <t>SlicePresetCfg/9011/ref:进攻12.png</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_201</t>
+          <t>ActvSoccer_preset_ref_9012</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>海港FC</t>
+          <t>左路单线突破</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TeamCfg/201</t>
+          <t>SlicePresetCfg/9012/ref:进攻13.png</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_202</t>
+          <t>ActvSoccer_preset_ref_9013</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>东方之鹰</t>
+          <t>弧顶回做射门</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TeamCfg/202</t>
+          <t>SlicePresetCfg/9013/ref:进攻14.png</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_203</t>
+          <t>ActvSoccer_preset_ref_9014</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>北欧狼</t>
+          <t>中路直面对门</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TeamCfg/203</t>
+          <t>SlicePresetCfg/9014/ref:进攻15.png</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_204</t>
+          <t>ActvSoccer_preset_ref_9015</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>阿根廷神鹰</t>
+          <t>右禁区边窄角</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TeamCfg/204</t>
+          <t>SlicePresetCfg/9015/ref:进攻16.png</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_205</t>
+          <t>ActvSoccer_preset_ref_9016</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>桑巴红魔</t>
+          <t>正面一打四</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TeamCfg/205</t>
+          <t>SlicePresetCfg/9016/ref:进攻17.png</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_206</t>
+          <t>ActvSoccer_preset_ref_9017</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>南美风暴</t>
+          <t>弧顶混战</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TeamCfg/206</t>
+          <t>SlicePresetCfg/9017/ref:进攻18.png</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_207</t>
+          <t>ActvSoccer_preset_ref_9018</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>潘帕斯之翼</t>
+          <t>右肋夹防外弧</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TeamCfg/207</t>
+          <t>SlicePresetCfg/9018/ref:进攻19.png</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_208</t>
+          <t>ActvSoccer_preset_ref_9019</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>高卢雄鸡</t>
+          <t>禁区前二打二</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TeamCfg/208</t>
+          <t>SlicePresetCfg/9019/ref:进攻20.png</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3001</t>
+          <t>ActvSoccer_preset_ref_9020</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>社区杯·联</t>
+          <t>正中人墙任意球</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TeamCfg/3001</t>
+          <t>SlicePresetCfg/9020/ref:任意球1.png</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3002</t>
+          <t>ActvSoccer_preset_ref_9021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>社区杯·FC</t>
+          <t>左侧绕墙任意球</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TeamCfg/3002</t>
+          <t>SlicePresetCfg/9021/ref:任意球2.png</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3003</t>
+          <t>ActvSoccer_preset_ref_9022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>社区杯·竞技</t>
+          <t>中路无密墙任意球</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TeamCfg/3003</t>
+          <t>SlicePresetCfg/9022/ref:任意球3.png</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3004</t>
+          <t>ActvSoccer_preset_ref_9023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>社区杯·联合</t>
+          <t>右侧双人接应任意球</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TeamCfg/3004</t>
+          <t>SlicePresetCfg/9023/ref:任意球4.png</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3005</t>
+          <t>ActvSoccer_preset_ref_9024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>社区杯·勇士</t>
+          <t>近距正面任意球</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TeamCfg/3005</t>
+          <t>SlicePresetCfg/9024/ref:任意球5.png</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3006</t>
+          <t>ActvSoccer_preset_ref_9025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>城市联赛·联</t>
+          <t>标准点球</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TeamCfg/3006</t>
+          <t>SlicePresetCfg/9025/ref:点球.png</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3007</t>
+          <t>ActvSoccer_preset_ref_9026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>城市联赛·FC</t>
+          <t>左角球前点传中</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TeamCfg/3007</t>
+          <t>SlicePresetCfg/9026/ref:角球1.png</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3008</t>
+          <t>ActvSoccer_preset_ref_9027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>城市联赛·竞技</t>
+          <t>右角球禁区混战</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TeamCfg/3008</t>
+          <t>SlicePresetCfg/9027/ref:角球2.png</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3009</t>
+          <t>ActvSoccer_preset_ref_9028</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>城市联赛·联合</t>
+          <t>左侧界外球近端接应</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TeamCfg/3009</t>
+          <t>SlicePresetCfg/9028/ref:界外发球1.png</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3010</t>
+          <t>ActvSoccer_preset_ref_9029</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>城市联赛·勇士</t>
+          <t>正面守门扑救</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TeamCfg/3010</t>
+          <t>SlicePresetCfg/9029/ref:守门.png</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3011</t>
+          <t>ActvSoccer_growth_fame_title_1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>省级联赛·联</t>
+          <t>业余球员</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TeamCfg/3011</t>
+          <t>FameGrowthLevelCfg/1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3012</t>
+          <t>ActvSoccer_growth_fame_title_2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>省级联赛·FC</t>
+          <t>新秀</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TeamCfg/3012</t>
+          <t>FameGrowthLevelCfg/2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3013</t>
+          <t>ActvSoccer_growth_fame_title_3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>省级联赛·竞技</t>
+          <t>专业球员</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TeamCfg/3013</t>
+          <t>FameGrowthLevelCfg/3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3014</t>
+          <t>ActvSoccer_growth_fame_title_4</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>省级联赛·联合</t>
+          <t>明星</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TeamCfg/3014</t>
+          <t>FameGrowthLevelCfg/4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3015</t>
+          <t>ActvSoccer_growth_fame_title_5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>省级联赛·勇士</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TeamCfg/3015</t>
+          <t>FameGrowthLevelCfg/5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3016</t>
+          <t>ActvSoccer_growth_fame_title_6</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>大区联赛·联</t>
+          <t>世界级</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TeamCfg/3016</t>
+          <t>FameGrowthLevelCfg/6</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3017</t>
+          <t>ActvSoccer_growth_fame_title_7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>大区联赛·FC</t>
+          <t>传奇</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TeamCfg/3017</t>
+          <t>FameGrowthLevelCfg/7</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3018</t>
+          <t>ActvSoccer_team_name_101</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>大区联赛·竞技</t>
+          <t>红星联</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TeamCfg/3018</t>
+          <t>TeamCfg/101</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3019</t>
+          <t>ActvSoccer_team_name_102</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>大区联赛·联合</t>
+          <t>莱茵青年</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TeamCfg/3019</t>
+          <t>TeamCfg/102</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3020</t>
+          <t>ActvSoccer_team_name_103</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>大区联赛·勇士</t>
+          <t>桑巴之星</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TeamCfg/3020</t>
+          <t>TeamCfg/103</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3021</t>
+          <t>ActvSoccer_team_name_104</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>全国联赛·联</t>
+          <t>蓝白雄鹰</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TeamCfg/3021</t>
+          <t>TeamCfg/104</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3022</t>
+          <t>ActvSoccer_team_name_201</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>全国联赛·FC</t>
+          <t>海港FC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TeamCfg/3022</t>
+          <t>TeamCfg/201</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3023</t>
+          <t>ActvSoccer_team_name_202</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>全国联赛·竞技</t>
+          <t>东方之鹰</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TeamCfg/3023</t>
+          <t>TeamCfg/202</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3024</t>
+          <t>ActvSoccer_team_name_203</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>全国联赛·联合</t>
+          <t>北欧狼</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TeamCfg/3024</t>
+          <t>TeamCfg/203</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3025</t>
+          <t>ActvSoccer_team_name_204</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>全国联赛·勇士</t>
+          <t>阿根廷神鹰</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TeamCfg/3025</t>
+          <t>TeamCfg/204</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3026</t>
+          <t>ActvSoccer_team_name_205</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>洲际资格赛·联</t>
+          <t>桑巴红魔</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TeamCfg/3026</t>
+          <t>TeamCfg/205</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3027</t>
+          <t>ActvSoccer_team_name_206</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>洲际资格赛·FC</t>
+          <t>南美风暴</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TeamCfg/3027</t>
+          <t>TeamCfg/206</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3028</t>
+          <t>ActvSoccer_team_name_207</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>洲际资格赛·竞技</t>
+          <t>潘帕斯之翼</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TeamCfg/3028</t>
+          <t>TeamCfg/207</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3029</t>
+          <t>ActvSoccer_team_name_208</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>洲际资格赛·联合</t>
+          <t>高卢雄鸡</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TeamCfg/3029</t>
+          <t>TeamCfg/208</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3030</t>
+          <t>ActvSoccer_team_name_3001</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>洲际资格赛·勇士</t>
+          <t>社区杯·联</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TeamCfg/3030</t>
+          <t>TeamCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3031</t>
+          <t>ActvSoccer_team_name_3002</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>洲际联赛·联</t>
+          <t>社区杯·FC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TeamCfg/3031</t>
+          <t>TeamCfg/3002</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3032</t>
+          <t>ActvSoccer_team_name_3003</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>洲际联赛·FC</t>
+          <t>社区杯·竞技</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TeamCfg/3032</t>
+          <t>TeamCfg/3003</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3033</t>
+          <t>ActvSoccer_team_name_3004</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>洲际联赛·竞技</t>
+          <t>社区杯·联合</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TeamCfg/3033</t>
+          <t>TeamCfg/3004</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3034</t>
+          <t>ActvSoccer_team_name_3005</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>洲际联赛·联合</t>
+          <t>社区杯·勇士</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TeamCfg/3034</t>
+          <t>TeamCfg/3005</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3035</t>
+          <t>ActvSoccer_team_name_3006</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>洲际联赛·勇士</t>
+          <t>城市联赛·联</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TeamCfg/3035</t>
+          <t>TeamCfg/3006</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3036</t>
+          <t>ActvSoccer_team_name_3007</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>国际邀请赛·联</t>
+          <t>城市联赛·FC</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TeamCfg/3036</t>
+          <t>TeamCfg/3007</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3037</t>
+          <t>ActvSoccer_team_name_3008</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>国际邀请赛·FC</t>
+          <t>城市联赛·竞技</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TeamCfg/3037</t>
+          <t>TeamCfg/3008</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3038</t>
+          <t>ActvSoccer_team_name_3009</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>国际邀请赛·竞技</t>
+          <t>城市联赛·联合</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TeamCfg/3038</t>
+          <t>TeamCfg/3009</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3039</t>
+          <t>ActvSoccer_team_name_3010</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>国际邀请赛·联合</t>
+          <t>城市联赛·勇士</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TeamCfg/3039</t>
+          <t>TeamCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3040</t>
+          <t>ActvSoccer_team_name_3011</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>国际邀请赛·勇士</t>
+          <t>省级联赛·联</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TeamCfg/3040</t>
+          <t>TeamCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3041</t>
+          <t>ActvSoccer_team_name_3012</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>世界精英赛·联</t>
+          <t>省级联赛·FC</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TeamCfg/3041</t>
+          <t>TeamCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3042</t>
+          <t>ActvSoccer_team_name_3013</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>世界精英赛·FC</t>
+          <t>省级联赛·竞技</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TeamCfg/3042</t>
+          <t>TeamCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3043</t>
+          <t>ActvSoccer_team_name_3014</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>世界精英赛·竞技</t>
+          <t>省级联赛·联合</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TeamCfg/3043</t>
+          <t>TeamCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3044</t>
+          <t>ActvSoccer_team_name_3015</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>世界精英赛·联合</t>
+          <t>省级联赛·勇士</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TeamCfg/3044</t>
+          <t>TeamCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3045</t>
+          <t>ActvSoccer_team_name_3016</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>世界精英赛·勇士</t>
+          <t>大区联赛·联</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TeamCfg/3045</t>
+          <t>TeamCfg/3016</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3046</t>
+          <t>ActvSoccer_team_name_3017</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联</t>
+          <t>大区联赛·FC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TeamCfg/3046</t>
+          <t>TeamCfg/3017</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3047</t>
+          <t>ActvSoccer_team_name_3018</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>世界杯总决赛·FC</t>
+          <t>大区联赛·竞技</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TeamCfg/3047</t>
+          <t>TeamCfg/3018</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3048</t>
+          <t>ActvSoccer_team_name_3019</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>世界杯总决赛·竞技</t>
+          <t>大区联赛·联合</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TeamCfg/3048</t>
+          <t>TeamCfg/3019</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3049</t>
+          <t>ActvSoccer_team_name_3020</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联合</t>
+          <t>大区联赛·勇士</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TeamCfg/3049</t>
+          <t>TeamCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3050</t>
+          <t>ActvSoccer_team_name_3021</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>世界杯总决赛·勇士</t>
+          <t>全国联赛·联</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TeamCfg/3050</t>
+          <t>TeamCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_1</t>
+          <t>ActvSoccer_team_name_3022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>社区杯 第1/50轮</t>
+          <t>全国联赛·FC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SeasonCfg/1</t>
+          <t>TeamCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_2</t>
+          <t>ActvSoccer_team_name_3023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>社区杯 第2/50轮</t>
+          <t>全国联赛·竞技</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SeasonCfg/2</t>
+          <t>TeamCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_3</t>
+          <t>ActvSoccer_team_name_3024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>社区杯 第3/50轮</t>
+          <t>全国联赛·联合</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SeasonCfg/3</t>
+          <t>TeamCfg/3024</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_4</t>
+          <t>ActvSoccer_team_name_3025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>社区杯 第4/50轮</t>
+          <t>全国联赛·勇士</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SeasonCfg/4</t>
+          <t>TeamCfg/3025</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_5</t>
+          <t>ActvSoccer_team_name_3026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>社区杯 第5/50轮</t>
+          <t>洲际资格赛·联</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SeasonCfg/5</t>
+          <t>TeamCfg/3026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_6</t>
+          <t>ActvSoccer_team_name_3027</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>城市联赛 第6/50轮</t>
+          <t>洲际资格赛·FC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SeasonCfg/6</t>
+          <t>TeamCfg/3027</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_7</t>
+          <t>ActvSoccer_team_name_3028</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>城市联赛 第7/50轮</t>
+          <t>洲际资格赛·竞技</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SeasonCfg/7</t>
+          <t>TeamCfg/3028</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_8</t>
+          <t>ActvSoccer_team_name_3029</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>城市联赛 第8/50轮</t>
+          <t>洲际资格赛·联合</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SeasonCfg/8</t>
+          <t>TeamCfg/3029</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_9</t>
+          <t>ActvSoccer_team_name_3030</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>城市联赛 第9/50轮</t>
+          <t>洲际资格赛·勇士</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SeasonCfg/9</t>
+          <t>TeamCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_10</t>
+          <t>ActvSoccer_team_name_3031</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>城市联赛 第10/50轮</t>
+          <t>洲际联赛·联</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SeasonCfg/10</t>
+          <t>TeamCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_11</t>
+          <t>ActvSoccer_team_name_3032</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>省级联赛 第11/50轮</t>
+          <t>洲际联赛·FC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SeasonCfg/11</t>
+          <t>TeamCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_12</t>
+          <t>ActvSoccer_team_name_3033</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>省级联赛 第12/50轮</t>
+          <t>洲际联赛·竞技</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SeasonCfg/12</t>
+          <t>TeamCfg/3033</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_13</t>
+          <t>ActvSoccer_team_name_3034</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>省级联赛 第13/50轮</t>
+          <t>洲际联赛·联合</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SeasonCfg/13</t>
+          <t>TeamCfg/3034</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_14</t>
+          <t>ActvSoccer_team_name_3035</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>省级联赛 第14/50轮</t>
+          <t>洲际联赛·勇士</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SeasonCfg/14</t>
+          <t>TeamCfg/3035</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_15</t>
+          <t>ActvSoccer_team_name_3036</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>省级联赛 第15/50轮</t>
+          <t>国际邀请赛·联</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SeasonCfg/15</t>
+          <t>TeamCfg/3036</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_16</t>
+          <t>ActvSoccer_team_name_3037</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>大区联赛 第16/50轮</t>
+          <t>国际邀请赛·FC</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SeasonCfg/16</t>
+          <t>TeamCfg/3037</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_17</t>
+          <t>ActvSoccer_team_name_3038</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>大区联赛 第17/50轮</t>
+          <t>国际邀请赛·竞技</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SeasonCfg/17</t>
+          <t>TeamCfg/3038</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_18</t>
+          <t>ActvSoccer_team_name_3039</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>大区联赛 第18/50轮</t>
+          <t>国际邀请赛·联合</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SeasonCfg/18</t>
+          <t>TeamCfg/3039</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_19</t>
+          <t>ActvSoccer_team_name_3040</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>大区联赛 第19/50轮</t>
+          <t>国际邀请赛·勇士</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SeasonCfg/19</t>
+          <t>TeamCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_20</t>
+          <t>ActvSoccer_team_name_3041</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>大区联赛 第20/50轮</t>
+          <t>世界精英赛·联</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SeasonCfg/20</t>
+          <t>TeamCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_21</t>
+          <t>ActvSoccer_team_name_3042</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>全国联赛 第21/50轮</t>
+          <t>世界精英赛·FC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>SeasonCfg/21</t>
+          <t>TeamCfg/3042</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_22</t>
+          <t>ActvSoccer_team_name_3043</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>全国联赛 第22/50轮</t>
+          <t>世界精英赛·竞技</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>SeasonCfg/22</t>
+          <t>TeamCfg/3043</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_23</t>
+          <t>ActvSoccer_team_name_3044</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>全国联赛 第23/50轮</t>
+          <t>世界精英赛·联合</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SeasonCfg/23</t>
+          <t>TeamCfg/3044</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_24</t>
+          <t>ActvSoccer_team_name_3045</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>全国联赛 第24/50轮</t>
+          <t>世界精英赛·勇士</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SeasonCfg/24</t>
+          <t>TeamCfg/3045</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_25</t>
+          <t>ActvSoccer_team_name_3046</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>全国联赛 第25/50轮</t>
+          <t>世界杯总决赛·联</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SeasonCfg/25</t>
+          <t>TeamCfg/3046</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_26</t>
+          <t>ActvSoccer_team_name_3047</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>洲际资格赛 第26/50轮</t>
+          <t>世界杯总决赛·FC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SeasonCfg/26</t>
+          <t>TeamCfg/3047</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_27</t>
+          <t>ActvSoccer_team_name_3048</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>洲际资格赛 第27/50轮</t>
+          <t>世界杯总决赛·竞技</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SeasonCfg/27</t>
+          <t>TeamCfg/3048</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_28</t>
+          <t>ActvSoccer_team_name_3049</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>洲际资格赛 第28/50轮</t>
+          <t>世界杯总决赛·联合</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SeasonCfg/28</t>
+          <t>TeamCfg/3049</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_29</t>
+          <t>ActvSoccer_team_name_3050</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>洲际资格赛 第29/50轮</t>
+          <t>世界杯总决赛·勇士</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SeasonCfg/29</t>
+          <t>TeamCfg/3050</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_30</t>
+          <t>ActvSoccer_season_league_name_1</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>洲际资格赛 第30/50轮</t>
+          <t>社区杯 第1/50轮</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SeasonCfg/30</t>
+          <t>SeasonCfg/1</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_31</t>
+          <t>ActvSoccer_season_league_name_2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>洲际联赛 第31/50轮</t>
+          <t>社区杯 第2/50轮</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SeasonCfg/31</t>
+          <t>SeasonCfg/2</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_32</t>
+          <t>ActvSoccer_season_league_name_3</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>洲际联赛 第32/50轮</t>
+          <t>社区杯 第3/50轮</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SeasonCfg/32</t>
+          <t>SeasonCfg/3</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_33</t>
+          <t>ActvSoccer_season_league_name_4</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>洲际联赛 第33/50轮</t>
+          <t>社区杯 第4/50轮</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SeasonCfg/33</t>
+          <t>SeasonCfg/4</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_34</t>
+          <t>ActvSoccer_season_league_name_5</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>洲际联赛 第34/50轮</t>
+          <t>社区杯 第5/50轮</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SeasonCfg/34</t>
+          <t>SeasonCfg/5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_35</t>
+          <t>ActvSoccer_season_league_name_6</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>洲际联赛 第35/50轮</t>
+          <t>城市联赛 第6/50轮</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SeasonCfg/35</t>
+          <t>SeasonCfg/6</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_36</t>
+          <t>ActvSoccer_season_league_name_7</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>国际邀请赛 第36/50轮</t>
+          <t>城市联赛 第7/50轮</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SeasonCfg/36</t>
+          <t>SeasonCfg/7</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_37</t>
+          <t>ActvSoccer_season_league_name_8</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>国际邀请赛 第37/50轮</t>
+          <t>城市联赛 第8/50轮</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SeasonCfg/37</t>
+          <t>SeasonCfg/8</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_38</t>
+          <t>ActvSoccer_season_league_name_9</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>国际邀请赛 第38/50轮</t>
+          <t>城市联赛 第9/50轮</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SeasonCfg/38</t>
+          <t>SeasonCfg/9</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_39</t>
+          <t>ActvSoccer_season_league_name_10</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>国际邀请赛 第39/50轮</t>
+          <t>城市联赛 第10/50轮</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SeasonCfg/39</t>
+          <t>SeasonCfg/10</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_40</t>
+          <t>ActvSoccer_season_league_name_11</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>国际邀请赛 第40/50轮</t>
+          <t>省级联赛 第11/50轮</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SeasonCfg/40</t>
+          <t>SeasonCfg/11</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_41</t>
+          <t>ActvSoccer_season_league_name_12</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>世界精英赛 第41/50轮</t>
+          <t>省级联赛 第12/50轮</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SeasonCfg/41</t>
+          <t>SeasonCfg/12</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_42</t>
+          <t>ActvSoccer_season_league_name_13</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>世界精英赛 第42/50轮</t>
+          <t>省级联赛 第13/50轮</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SeasonCfg/42</t>
+          <t>SeasonCfg/13</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_43</t>
+          <t>ActvSoccer_season_league_name_14</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>世界精英赛 第43/50轮</t>
+          <t>省级联赛 第14/50轮</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SeasonCfg/43</t>
+          <t>SeasonCfg/14</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_44</t>
+          <t>ActvSoccer_season_league_name_15</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>世界精英赛 第44/50轮</t>
+          <t>省级联赛 第15/50轮</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SeasonCfg/44</t>
+          <t>SeasonCfg/15</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_45</t>
+          <t>ActvSoccer_season_league_name_16</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>世界精英赛 第45/50轮</t>
+          <t>大区联赛 第16/50轮</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SeasonCfg/45</t>
+          <t>SeasonCfg/16</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_46</t>
+          <t>ActvSoccer_season_league_name_17</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第46/50轮</t>
+          <t>大区联赛 第17/50轮</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SeasonCfg/46</t>
+          <t>SeasonCfg/17</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_47</t>
+          <t>ActvSoccer_season_league_name_18</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第47/50轮</t>
+          <t>大区联赛 第18/50轮</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SeasonCfg/47</t>
+          <t>SeasonCfg/18</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_48</t>
+          <t>ActvSoccer_season_league_name_19</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第48/50轮</t>
+          <t>大区联赛 第19/50轮</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SeasonCfg/48</t>
+          <t>SeasonCfg/19</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_49</t>
+          <t>ActvSoccer_season_league_name_20</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第49/50轮</t>
+          <t>大区联赛 第20/50轮</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SeasonCfg/49</t>
+          <t>SeasonCfg/20</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_50</t>
+          <t>ActvSoccer_season_league_name_21</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>世界杯总决赛 第50/50轮</t>
+          <t>全国联赛 第21/50轮</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SeasonCfg/50</t>
+          <t>SeasonCfg/21</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_team_build</t>
+          <t>ActvSoccer_season_league_name_22</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>组队期</t>
+          <t>全国联赛 第22/50轮</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>SeasonCfg/22</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_1</t>
+          <t>ActvSoccer_season_league_name_23</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>发起/加入组队、命名队名队标、审批</t>
+          <t>全国联赛 第23/50轮</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/1</t>
+          <t>SeasonCfg/23</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
+          <t>ActvSoccer_season_league_name_24</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>海选</t>
+          <t>全国联赛 第24/50轮</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>SeasonCfg/24</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
+          <t>ActvSoccer_season_league_name_25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>1天内筛出64强</t>
+          <t>全国联赛 第25/50轮</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/2</t>
+          <t>SeasonCfg/25</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
+          <t>ActvSoccer_season_league_name_26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>正赛第1轮</t>
+          <t>洲际资格赛 第26/50轮</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>SeasonCfg/26</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
+          <t>ActvSoccer_season_league_name_27</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>8组各一轮(64强)</t>
+          <t>洲际资格赛 第27/50轮</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/3</t>
+          <t>SeasonCfg/27</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
+          <t>ActvSoccer_season_league_name_28</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>正赛第2轮</t>
+          <t>洲际资格赛 第28/50轮</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>SeasonCfg/28</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
+          <t>ActvSoccer_season_league_name_29</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>8组各一轮(32强)</t>
+          <t>洲际资格赛 第29/50轮</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/4</t>
+          <t>SeasonCfg/29</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
+          <t>ActvSoccer_season_league_name_30</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>正赛第3轮</t>
+          <t>洲际资格赛 第30/50轮</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>SeasonCfg/30</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
+          <t>ActvSoccer_season_league_name_31</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>8组各一轮(16强)</t>
+          <t>洲际联赛 第31/50轮</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/5</t>
+          <t>SeasonCfg/31</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
+          <t>ActvSoccer_season_league_name_32</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>正赛第4轮</t>
+          <t>洲际联赛 第32/50轮</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>SeasonCfg/32</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
+          <t>ActvSoccer_season_league_name_33</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>8组决出组冠军→8强</t>
+          <t>洲际联赛 第33/50轮</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/6</t>
+          <t>SeasonCfg/33</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
+          <t>ActvSoccer_season_league_name_34</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>正赛第5轮</t>
+          <t>洲际联赛 第34/50轮</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>SeasonCfg/34</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
+          <t>ActvSoccer_season_league_name_35</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>8强淘汰赛(4强)</t>
+          <t>洲际联赛 第35/50轮</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/7</t>
+          <t>SeasonCfg/35</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
+          <t>ActvSoccer_season_league_name_36</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>决赛</t>
+          <t>国际邀请赛 第36/50轮</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>SeasonCfg/36</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
+          <t>ActvSoccer_season_league_name_37</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>冠亚军决赛</t>
+          <t>国际邀请赛 第37/50轮</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/8</t>
+          <t>SeasonCfg/37</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
+          <t>ActvSoccer_season_league_name_38</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>展示期</t>
+          <t>国际邀请赛 第38/50轮</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>KnockoutPhaseCfg/9</t>
+          <t>SeasonCfg/38</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
+          <t>ActvSoccer_season_league_name_39</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第39/50轮</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SeasonCfg/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_40</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>国际邀请赛 第40/50轮</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SeasonCfg/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_41</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>世界精英赛 第41/50轮</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SeasonCfg/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_42</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>世界精英赛 第42/50轮</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SeasonCfg/42</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_43</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>世界精英赛 第43/50轮</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SeasonCfg/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_44</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>世界精英赛 第44/50轮</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SeasonCfg/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_45</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>世界精英赛 第45/50轮</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SeasonCfg/45</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_46</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第46/50轮</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SeasonCfg/46</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_47</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第47/50轮</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SeasonCfg/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_48</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第48/50轮</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SeasonCfg/48</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_49</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第49/50轮</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SeasonCfg/49</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ActvSoccer_season_league_name_50</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>世界杯总决赛 第50/50轮</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SeasonCfg/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_team_build</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>组队期</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_1</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>发起/加入组队、命名队名队标、审批</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_3</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>海选</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_3</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1天内筛出64强</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_4</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>正赛第1轮</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_4</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>8组各一轮(64强)</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_5</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>正赛第2轮</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_5</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>8组各一轮(32强)</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_6</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>正赛第3轮</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_6</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>8组各一轮(16强)</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_7</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>正赛第4轮</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_7</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>8组决出组冠军→8强</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_8</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>正赛第5轮</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_8</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>8强淘汰赛(4强)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_9</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>决赛</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_day_content_9</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>冠亚军决赛</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ActvSoccer_knockout_phase_name_10</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>展示期</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>KnockoutPhaseCfg/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
           <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>KnockoutPhaseCfg/9</t>
         </is>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ActvSoccerLanguageCfg" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1</t>
+          <t>SlicePresetCfg/1001</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5</t>
+          <t>SlicePresetCfg/1002</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6</t>
+          <t>SlicePresetCfg/1003</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/16</t>
+          <t>SlicePresetCfg/1004</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2</t>
+          <t>SlicePresetCfg/3001</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/7</t>
+          <t>SlicePresetCfg/3002</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/8</t>
+          <t>SlicePresetCfg/3003</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/17</t>
+          <t>SlicePresetCfg/3004</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3</t>
+          <t>SlicePresetCfg/5001</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9</t>
+          <t>SlicePresetCfg/5002</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/10</t>
+          <t>SlicePresetCfg/2001</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/11</t>
+          <t>SlicePresetCfg/2002</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/18</t>
+          <t>SlicePresetCfg/2003</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/12</t>
+          <t>SlicePresetCfg/6001</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/13</t>
+          <t>SlicePresetCfg/6002</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4</t>
+          <t>SlicePresetCfg/4001</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/14</t>
+          <t>SlicePresetCfg/4002</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/15</t>
+          <t>SlicePresetCfg/4003</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/19</t>
+          <t>SlicePresetCfg/1005</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/20</t>
+          <t>SlicePresetCfg/1006</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/21</t>
+          <t>SlicePresetCfg/1007</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/22</t>
+          <t>SlicePresetCfg/1008</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/23</t>
+          <t>SlicePresetCfg/1009</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/24</t>
+          <t>SlicePresetCfg/1010</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/25</t>
+          <t>SlicePresetCfg/1011</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/26</t>
+          <t>SlicePresetCfg/1012</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/27</t>
+          <t>SlicePresetCfg/1013</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/28</t>
+          <t>SlicePresetCfg/1014</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/29</t>
+          <t>SlicePresetCfg/3005</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/30</t>
+          <t>SlicePresetCfg/3006</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/31</t>
+          <t>SlicePresetCfg/3007</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/32</t>
+          <t>SlicePresetCfg/3008</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/33</t>
+          <t>SlicePresetCfg/3009</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/34</t>
+          <t>SlicePresetCfg/5003</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/35</t>
+          <t>SlicePresetCfg/5004</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/36</t>
+          <t>SlicePresetCfg/5005</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/37</t>
+          <t>SlicePresetCfg/2004</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/38</t>
+          <t>SlicePresetCfg/2005</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/39</t>
+          <t>SlicePresetCfg/2006</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/40</t>
+          <t>SlicePresetCfg/2007</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/41</t>
+          <t>SlicePresetCfg/2008</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/42</t>
+          <t>SlicePresetCfg/2009</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/43</t>
+          <t>SlicePresetCfg/2010</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/44</t>
+          <t>SlicePresetCfg/6003</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/45</t>
+          <t>SlicePresetCfg/6004</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/46</t>
+          <t>SlicePresetCfg/6005</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/47</t>
+          <t>SlicePresetCfg/6006</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/48</t>
+          <t>SlicePresetCfg/6007</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/49</t>
+          <t>SlicePresetCfg/6008</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/50</t>
+          <t>SlicePresetCfg/4004</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9001/ref:进攻1.png</t>
+          <t>SlicePresetCfg/1015/ref:进攻1.png</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9002/ref:进攻2.png</t>
+          <t>SlicePresetCfg/1016/ref:进攻2.png</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9003/ref:进攻3.png</t>
+          <t>SlicePresetCfg/1017/ref:进攻3.png</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9004/ref:进攻5.png</t>
+          <t>SlicePresetCfg/1018/ref:进攻5.png</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9005/ref:进攻6.png</t>
+          <t>SlicePresetCfg/1019/ref:进攻6.png</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9006/ref:进攻7.png</t>
+          <t>SlicePresetCfg/1020/ref:进攻7.png</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9007/ref:进攻8.png</t>
+          <t>SlicePresetCfg/1021/ref:进攻8.png</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9008/ref:进攻9.png</t>
+          <t>SlicePresetCfg/1022/ref:进攻9.png</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9009/ref:进攻10.png</t>
+          <t>SlicePresetCfg/1023/ref:进攻10.png</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9010/ref:进攻11.png</t>
+          <t>SlicePresetCfg/1024/ref:进攻11.png</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9011/ref:进攻12.png</t>
+          <t>SlicePresetCfg/1025/ref:进攻12.png</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9012/ref:进攻13.png</t>
+          <t>SlicePresetCfg/1026/ref:进攻13.png</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9013/ref:进攻14.png</t>
+          <t>SlicePresetCfg/1027/ref:进攻14.png</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9014/ref:进攻15.png</t>
+          <t>SlicePresetCfg/1028/ref:进攻15.png</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9015/ref:进攻16.png</t>
+          <t>SlicePresetCfg/1029/ref:进攻16.png</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9016/ref:进攻17.png</t>
+          <t>SlicePresetCfg/1030/ref:进攻17.png</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9017/ref:进攻18.png</t>
+          <t>SlicePresetCfg/1031/ref:进攻18.png</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9018/ref:进攻19.png</t>
+          <t>SlicePresetCfg/1032/ref:进攻19.png</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9019/ref:进攻20.png</t>
+          <t>SlicePresetCfg/1033/ref:进攻20.png</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9020/ref:任意球1.png</t>
+          <t>SlicePresetCfg/3010/ref:任意球1.png</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9021/ref:任意球2.png</t>
+          <t>SlicePresetCfg/3011/ref:任意球2.png</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9022/ref:任意球3.png</t>
+          <t>SlicePresetCfg/3012/ref:任意球3.png</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9023/ref:任意球4.png</t>
+          <t>SlicePresetCfg/3013/ref:任意球4.png</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9024/ref:任意球5.png</t>
+          <t>SlicePresetCfg/3014/ref:任意球5.png</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9025/ref:点球.png</t>
+          <t>SlicePresetCfg/5006/ref:点球.png</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9026/ref:角球1.png</t>
+          <t>SlicePresetCfg/2011/ref:角球1.png</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9027/ref:角球2.png</t>
+          <t>SlicePresetCfg/2012/ref:角球2.png</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9028/ref:界外发球1.png</t>
+          <t>SlicePresetCfg/6009/ref:界外发球1.png</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/9029/ref:守门.png</t>
+          <t>SlicePresetCfg/4005/ref:守门.png</t>
         </is>
       </c>
     </row>

--- a/output/test-config/ActivitySoccerLanguage.xlsx
+++ b/output/test-config/ActivitySoccerLanguage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C270"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,4316 +642,3670 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ActvSoccer_tutorial_desc_1</t>
+          <t>ActvSoccer_preset_name_1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>进攻教学</t>
+          <t>右路单刀</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TutorialCfg/1</t>
+          <t>SlicePresetCfg/1001</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ActvSoccer_tutorial_desc_2</t>
+          <t>ActvSoccer_preset_name_5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>任意球教学</t>
+          <t>左路单刀</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TutorialCfg/2</t>
+          <t>SlicePresetCfg/1002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ActvSoccer_tutorial_desc_3</t>
+          <t>ActvSoccer_preset_name_6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>点球教学</t>
+          <t>中路突破</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TutorialCfg/3</t>
+          <t>SlicePresetCfg/1003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1001</t>
+          <t>ActvSoccer_preset_name_16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>先完成一次试训，熟悉比赛中的射门操作。</t>
+          <t>中路吊射</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1001</t>
+          <t>SlicePresetCfg/1004</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1010</t>
+          <t>ActvSoccer_preset_name_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>按住球员脚下区域，画出你想踢出的路线。</t>
+          <t>中路任意球</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1010</t>
+          <t>SlicePresetCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1011</t>
+          <t>ActvSoccer_preset_name_7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>松手后，球会沿着轨迹飞出。</t>
+          <t>左侧任意球</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1011</t>
+          <t>SlicePresetCfg/3002</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1012</t>
+          <t>ActvSoccer_preset_name_8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>做得好！继续下一项训练。</t>
+          <t>右侧任意球</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1012</t>
+          <t>SlicePresetCfg/3003</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1013</t>
+          <t>ActvSoccer_preset_name_17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>再试一次，把路线画向白色目标框。</t>
+          <t>弧线任意球</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1013</t>
+          <t>SlicePresetCfg/3004</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1020</t>
+          <t>ActvSoccer_preset_name_3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>任意球需要避开人墙。拖动来选择方向和力量。</t>
+          <t>标准点球</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1020</t>
+          <t>SlicePresetCfg/5001</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1021</t>
+          <t>ActvSoccer_preset_name_9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>力量控制在65%左右，更容易命中目标。</t>
+          <t>加压点球</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1021</t>
+          <t>SlicePresetCfg/5002</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1022</t>
+          <t>ActvSoccer_preset_name_10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>很好，任意球训练完成。</t>
+          <t>左角球</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1022</t>
+          <t>SlicePresetCfg/2001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1023</t>
+          <t>ActvSoccer_preset_name_11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>力量太小了，再向后拖动一些。</t>
+          <t>右角球</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1023</t>
+          <t>SlicePresetCfg/2002</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1024</t>
+          <t>ActvSoccer_preset_name_18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>力量太大了，稍微收一点力。</t>
+          <t>后点包抄</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1024</t>
+          <t>SlicePresetCfg/2003</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1025</t>
+          <t>ActvSoccer_preset_name_12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>角度偏离目标，再调整射门方向。</t>
+          <t>左界外球</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1025</t>
+          <t>SlicePresetCfg/6001</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1030</t>
+          <t>ActvSoccer_preset_name_13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>试训中可以自由切换操作方式，选择你更顺手的模式。</t>
+          <t>右界外球</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1030</t>
+          <t>SlicePresetCfg/6002</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1031</t>
+          <t>ActvSoccer_preset_name_4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>现在把球踢向高亮区域。</t>
+          <t>基础守门</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1031</t>
+          <t>SlicePresetCfg/4001</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1032</t>
+          <t>ActvSoccer_preset_name_14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>点球训练完成。</t>
+          <t>大范围守门</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1032</t>
+          <t>SlicePresetCfg/4002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1033</t>
+          <t>ActvSoccer_preset_name_15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>再试一次，瞄准高亮区域射门。</t>
+          <t>近距扑点</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1033</t>
+          <t>SlicePresetCfg/4003</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1040</t>
+          <t>ActvSoccer_preset_name_19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>试训完成。球队给你发来了邀请，挑选一支作为职业生涯起点。</t>
+          <t>右肋斜插</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GuideStepCfg/1040</t>
+          <t>SlicePresetCfg/1005</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2001</t>
+          <t>ActvSoccer_preset_name_20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>第一场比赛已经准备好了，先从基础比赛开始。</t>
+          <t>左肋斜插</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2001</t>
+          <t>SlicePresetCfg/1006</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2010</t>
+          <t>ActvSoccer_preset_name_21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>这里可以看到本场比赛目标。</t>
+          <t>禁区弧顶远射</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2010</t>
+          <t>SlicePresetCfg/1007</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2011</t>
+          <t>ActvSoccer_preset_name_22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>点击开球，开始你的第一场比赛。</t>
+          <t>右路内切射门</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GuideStepCfg/2011</t>
+          <t>SlicePresetCfg/1008</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3001</t>
+          <t>ActvSoccer_preset_name_23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>比赛即将开始。</t>
+          <t>左路内切射门</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3001</t>
+          <t>SlicePresetCfg/1009</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3010</t>
+          <t>ActvSoccer_preset_name_24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>黄色光圈表示当前由你操作的球员。</t>
+          <t>倒三角回做</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3010</t>
+          <t>SlicePresetCfg/1010</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3011</t>
+          <t>ActvSoccer_preset_name_25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>这个标志表示这个方向上有你的队友。</t>
+          <t>门前抢点</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3011</t>
+          <t>SlicePresetCfg/1011</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3012</t>
+          <t>ActvSoccer_preset_name_26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>在屏幕上半部分左右滑动，可以移动相机观察场上情况。</t>
+          <t>禁区外吊射</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3012</t>
+          <t>SlicePresetCfg/1012</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3013</t>
+          <t>ActvSoccer_preset_name_27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>现在把球踢向白色目标区域。</t>
+          <t>二点补射</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3013</t>
+          <t>SlicePresetCfg/1013</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3014</t>
+          <t>ActvSoccer_preset_name_28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>进攻完成，点击继续。</t>
+          <t>横向摆脱射门</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3014</t>
+          <t>SlicePresetCfg/1014</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3015</t>
+          <t>ActvSoccer_preset_name_29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>错过这次机会可能会影响比赛结果，可以使用回溯重试。</t>
+          <t>近距中路任意球</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3015</t>
+          <t>SlicePresetCfg/3005</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3020</t>
+          <t>ActvSoccer_preset_name_30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>有些机会需要先传给队友。把球传到队友脚下。</t>
+          <t>远距中路任意球</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3020</t>
+          <t>SlicePresetCfg/3006</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3021</t>
+          <t>ActvSoccer_preset_name_31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>传球成功后，队友会完成射门，这会计为你的助攻。</t>
+          <t>右侧绕墙低射</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3021</t>
+          <t>SlicePresetCfg/3007</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3022</t>
+          <t>ActvSoccer_preset_name_32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>助攻完成，点击继续。</t>
+          <t>左侧绕墙低射</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3022</t>
+          <t>SlicePresetCfg/3008</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3023</t>
+          <t>ActvSoccer_preset_name_33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>传球没有到位，可以回溯后再试一次。</t>
+          <t>传中任意球</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3023</t>
+          <t>SlicePresetCfg/3009</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3030</t>
+          <t>ActvSoccer_preset_name_34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>现在轮到你防守。看准射门方向，划线完成扑救。</t>
+          <t>左下角点球</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3030</t>
+          <t>SlicePresetCfg/5003</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3031</t>
+          <t>ActvSoccer_preset_name_35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>扑救完成，点击继续。</t>
+          <t>右下角点球</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3031</t>
+          <t>SlicePresetCfg/5004</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3032</t>
+          <t>ActvSoccer_preset_name_36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>再试一次，沿着来球方向滑动。</t>
+          <t>半高点球</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3032</t>
+          <t>SlicePresetCfg/5005</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3040</t>
+          <t>ActvSoccer_preset_name_37</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>比赛结束，查看本场奖励。</t>
+          <t>左前点角球</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3040</t>
+          <t>SlicePresetCfg/2004</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3041</t>
+          <t>ActvSoccer_preset_name_38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>这里会展示本轮后的排名变化。</t>
+          <t>右前点角球</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GuideStepCfg/3041</t>
+          <t>SlicePresetCfg/2005</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_1</t>
+          <t>ActvSoccer_preset_name_39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>右路单刀</t>
+          <t>左后点高球</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1001</t>
+          <t>SlicePresetCfg/2006</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_5</t>
+          <t>ActvSoccer_preset_name_40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>左路单刀</t>
+          <t>右后点高球</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1002</t>
+          <t>SlicePresetCfg/2007</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_6</t>
+          <t>ActvSoccer_preset_name_41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中路突破</t>
+          <t>短角球配合</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1003</t>
+          <t>SlicePresetCfg/2008</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_16</t>
+          <t>ActvSoccer_preset_name_42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中路吊射</t>
+          <t>低平扫门前</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1004</t>
+          <t>SlicePresetCfg/2009</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_2</t>
+          <t>ActvSoccer_preset_name_43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>中路任意球</t>
+          <t>禁区混战二点</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3001</t>
+          <t>SlicePresetCfg/2010</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_7</t>
+          <t>ActvSoccer_preset_name_44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>左侧任意球</t>
+          <t>左侧近端接应</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3002</t>
+          <t>SlicePresetCfg/6003</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_8</t>
+          <t>ActvSoccer_preset_name_45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>右侧任意球</t>
+          <t>右侧近端接应</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3003</t>
+          <t>SlicePresetCfg/6004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_17</t>
+          <t>ActvSoccer_preset_name_46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>弧线任意球</t>
+          <t>左侧远端转移</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3004</t>
+          <t>SlicePresetCfg/6005</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_3</t>
+          <t>ActvSoccer_preset_name_47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>标准点球</t>
+          <t>右侧远端转移</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5001</t>
+          <t>SlicePresetCfg/6006</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_9</t>
+          <t>ActvSoccer_preset_name_48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>加压点球</t>
+          <t>左路快速反击</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5002</t>
+          <t>SlicePresetCfg/6007</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_10</t>
+          <t>ActvSoccer_preset_name_49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>左角球</t>
+          <t>右路快速反击</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2001</t>
+          <t>SlicePresetCfg/6008</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_11</t>
+          <t>ActvSoccer_preset_name_50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>右角球</t>
+          <t>左侧低球扑救</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2002</t>
+          <t>SlicePresetCfg/4004</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_18</t>
+          <t>ActvSoccer_preset_ref_9001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>后点包抄</t>
+          <t>弧顶正面推进</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2003</t>
+          <t>SlicePresetCfg/1015/ref:进攻1.png</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_12</t>
+          <t>ActvSoccer_preset_ref_9002</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>左界外球</t>
+          <t>右肋雪地单刀</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6001</t>
+          <t>SlicePresetCfg/1016/ref:进攻2.png</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_13</t>
+          <t>ActvSoccer_preset_ref_9003</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>右界外球</t>
+          <t>左肋外侧推进</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6002</t>
+          <t>SlicePresetCfg/1017/ref:进攻3.png</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_4</t>
+          <t>ActvSoccer_preset_ref_9004</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>基础守门</t>
+          <t>禁区前穿人墙</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4001</t>
+          <t>SlicePresetCfg/1018/ref:进攻5.png</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_14</t>
+          <t>ActvSoccer_preset_ref_9005</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>大范围守门</t>
+          <t>右侧倒地近射</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4002</t>
+          <t>SlicePresetCfg/1019/ref:进攻6.png</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_15</t>
+          <t>ActvSoccer_preset_ref_9006</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>近距扑点</t>
+          <t>右路三角压迫</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4003</t>
+          <t>SlicePresetCfg/1020/ref:进攻7.png</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_19</t>
+          <t>ActvSoccer_preset_ref_9007</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>右肋斜插</t>
+          <t>左肋多人包围</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1005</t>
+          <t>SlicePresetCfg/1021/ref:进攻8.png</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_20</t>
+          <t>ActvSoccer_preset_ref_9008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>左肋斜插</t>
+          <t>弧顶密集防线</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1006</t>
+          <t>SlicePresetCfg/1022/ref:进攻9.png</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_21</t>
+          <t>ActvSoccer_preset_ref_9009</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>禁区弧顶远射</t>
+          <t>左路远距推进</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1007</t>
+          <t>SlicePresetCfg/1023/ref:进攻10.png</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_22</t>
+          <t>ActvSoccer_preset_ref_9010</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>右路内切射门</t>
+          <t>中路远射</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1008</t>
+          <t>SlicePresetCfg/1024/ref:进攻11.png</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_23</t>
+          <t>ActvSoccer_preset_ref_9011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>左路内切射门</t>
+          <t>右路斜向禁区</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1009</t>
+          <t>SlicePresetCfg/1025/ref:进攻12.png</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_24</t>
+          <t>ActvSoccer_preset_ref_9012</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>倒三角回做</t>
+          <t>左路单线突破</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1010</t>
+          <t>SlicePresetCfg/1026/ref:进攻13.png</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_25</t>
+          <t>ActvSoccer_preset_ref_9013</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>门前抢点</t>
+          <t>弧顶回做射门</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1011</t>
+          <t>SlicePresetCfg/1027/ref:进攻14.png</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_26</t>
+          <t>ActvSoccer_preset_ref_9014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>禁区外吊射</t>
+          <t>中路直面对门</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1012</t>
+          <t>SlicePresetCfg/1028/ref:进攻15.png</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_27</t>
+          <t>ActvSoccer_preset_ref_9015</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>二点补射</t>
+          <t>右禁区边窄角</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1013</t>
+          <t>SlicePresetCfg/1029/ref:进攻16.png</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_28</t>
+          <t>ActvSoccer_preset_ref_9016</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>横向摆脱射门</t>
+          <t>正面一打四</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1014</t>
+          <t>SlicePresetCfg/1030/ref:进攻17.png</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_29</t>
+          <t>ActvSoccer_preset_ref_9017</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>近距中路任意球</t>
+          <t>弧顶混战</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3005</t>
+          <t>SlicePresetCfg/1031/ref:进攻18.png</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_30</t>
+          <t>ActvSoccer_preset_ref_9018</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>远距中路任意球</t>
+          <t>右肋夹防外弧</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3006</t>
+          <t>SlicePresetCfg/1032/ref:进攻19.png</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_31</t>
+          <t>ActvSoccer_preset_ref_9019</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>右侧绕墙低射</t>
+          <t>禁区前二打二</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3007</t>
+          <t>SlicePresetCfg/1033/ref:进攻20.png</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_32</t>
+          <t>ActvSoccer_preset_ref_9020</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>左侧绕墙低射</t>
+          <t>正中人墙任意球</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3008</t>
+          <t>SlicePresetCfg/3010/ref:任意球1.png</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_33</t>
+          <t>ActvSoccer_preset_ref_9021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>传中任意球</t>
+          <t>左侧绕墙任意球</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3009</t>
+          <t>SlicePresetCfg/3011/ref:任意球2.png</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_34</t>
+          <t>ActvSoccer_preset_ref_9022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>左下角点球</t>
+          <t>中路无密墙任意球</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5003</t>
+          <t>SlicePresetCfg/3012/ref:任意球3.png</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_35</t>
+          <t>ActvSoccer_preset_ref_9023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>右下角点球</t>
+          <t>右侧双人接应任意球</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5004</t>
+          <t>SlicePresetCfg/3013/ref:任意球4.png</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_36</t>
+          <t>ActvSoccer_preset_ref_9024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>半高点球</t>
+          <t>近距正面任意球</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5005</t>
+          <t>SlicePresetCfg/3014/ref:任意球5.png</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_37</t>
+          <t>ActvSoccer_preset_ref_9025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>左前点角球</t>
+          <t>标准点球</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2004</t>
+          <t>SlicePresetCfg/5006/ref:点球.png</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_38</t>
+          <t>ActvSoccer_preset_ref_9026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>右前点角球</t>
+          <t>左角球前点传中</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2005</t>
+          <t>SlicePresetCfg/2011/ref:角球1.png</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_39</t>
+          <t>ActvSoccer_preset_ref_9027</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>左后点高球</t>
+          <t>右角球禁区混战</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2006</t>
+          <t>SlicePresetCfg/2012/ref:角球2.png</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_40</t>
+          <t>ActvSoccer_preset_ref_9028</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>右后点高球</t>
+          <t>左侧界外球近端接应</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2007</t>
+          <t>SlicePresetCfg/6009/ref:界外发球1.png</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_41</t>
+          <t>ActvSoccer_preset_ref_9029</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>短角球配合</t>
+          <t>正面守门扑救</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2008</t>
+          <t>SlicePresetCfg/4005/ref:守门.png</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_42</t>
+          <t>ActvSoccer_growth_fame_title_1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>低平扫门前</t>
+          <t>业余球员</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2009</t>
+          <t>FameGrowthLevelCfg/1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_43</t>
+          <t>ActvSoccer_growth_fame_title_2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>禁区混战二点</t>
+          <t>新秀</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2010</t>
+          <t>FameGrowthLevelCfg/2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_44</t>
+          <t>ActvSoccer_growth_fame_title_3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>左侧近端接应</t>
+          <t>专业球员</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6003</t>
+          <t>FameGrowthLevelCfg/3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_45</t>
+          <t>ActvSoccer_growth_fame_title_4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>右侧近端接应</t>
+          <t>明星</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6004</t>
+          <t>FameGrowthLevelCfg/4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_46</t>
+          <t>ActvSoccer_growth_fame_title_5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>左侧远端转移</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6005</t>
+          <t>FameGrowthLevelCfg/5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_47</t>
+          <t>ActvSoccer_growth_fame_title_6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>右侧远端转移</t>
+          <t>世界级</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6006</t>
+          <t>FameGrowthLevelCfg/6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_48</t>
+          <t>ActvSoccer_growth_fame_title_7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>左路快速反击</t>
+          <t>传奇</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6007</t>
+          <t>FameGrowthLevelCfg/7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_49</t>
+          <t>ActvSoccer_team_name_101</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>右路快速反击</t>
+          <t>红星联</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6008</t>
+          <t>TeamCfg/101</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_name_50</t>
+          <t>ActvSoccer_team_name_102</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>左侧低球扑救</t>
+          <t>莱茵青年</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4004</t>
+          <t>TeamCfg/102</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9001</t>
+          <t>ActvSoccer_team_name_103</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>弧顶正面推进</t>
+          <t>桑巴之星</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1015/ref:进攻1.png</t>
+          <t>TeamCfg/103</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9002</t>
+          <t>ActvSoccer_team_name_104</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>右肋雪地单刀</t>
+          <t>蓝白雄鹰</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1016/ref:进攻2.png</t>
+          <t>TeamCfg/104</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9003</t>
+          <t>ActvSoccer_team_name_201</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>左肋外侧推进</t>
+          <t>海港FC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1017/ref:进攻3.png</t>
+          <t>TeamCfg/201</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9004</t>
+          <t>ActvSoccer_team_name_202</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>禁区前穿人墙</t>
+          <t>东方之鹰</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1018/ref:进攻5.png</t>
+          <t>TeamCfg/202</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9005</t>
+          <t>ActvSoccer_team_name_203</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>右侧倒地近射</t>
+          <t>北欧狼</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1019/ref:进攻6.png</t>
+          <t>TeamCfg/203</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9006</t>
+          <t>ActvSoccer_team_name_204</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>右路三角压迫</t>
+          <t>阿根廷神鹰</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1020/ref:进攻7.png</t>
+          <t>TeamCfg/204</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9007</t>
+          <t>ActvSoccer_team_name_205</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>左肋多人包围</t>
+          <t>桑巴红魔</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1021/ref:进攻8.png</t>
+          <t>TeamCfg/205</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9008</t>
+          <t>ActvSoccer_team_name_206</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>弧顶密集防线</t>
+          <t>南美风暴</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1022/ref:进攻9.png</t>
+          <t>TeamCfg/206</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9009</t>
+          <t>ActvSoccer_team_name_207</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>左路远距推进</t>
+          <t>潘帕斯之翼</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1023/ref:进攻10.png</t>
+          <t>TeamCfg/207</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9010</t>
+          <t>ActvSoccer_team_name_208</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>中路远射</t>
+          <t>高卢雄鸡</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1024/ref:进攻11.png</t>
+          <t>TeamCfg/208</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9011</t>
+          <t>ActvSoccer_team_name_3001</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>右路斜向禁区</t>
+          <t>社区杯·联</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1025/ref:进攻12.png</t>
+          <t>TeamCfg/3001</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9012</t>
+          <t>ActvSoccer_team_name_3002</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>左路单线突破</t>
+          <t>社区杯·FC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1026/ref:进攻13.png</t>
+          <t>TeamCfg/3002</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9013</t>
+          <t>ActvSoccer_team_name_3003</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>弧顶回做射门</t>
+          <t>社区杯·竞技</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1027/ref:进攻14.png</t>
+          <t>TeamCfg/3003</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9014</t>
+          <t>ActvSoccer_team_name_3004</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>中路直面对门</t>
+          <t>社区杯·联合</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1028/ref:进攻15.png</t>
+          <t>TeamCfg/3004</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9015</t>
+          <t>ActvSoccer_team_name_3005</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>右禁区边窄角</t>
+          <t>社区杯·勇士</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1029/ref:进攻16.png</t>
+          <t>TeamCfg/3005</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9016</t>
+          <t>ActvSoccer_team_name_3006</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>正面一打四</t>
+          <t>城市联赛·联</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1030/ref:进攻17.png</t>
+          <t>TeamCfg/3006</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9017</t>
+          <t>ActvSoccer_team_name_3007</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>弧顶混战</t>
+          <t>城市联赛·FC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1031/ref:进攻18.png</t>
+          <t>TeamCfg/3007</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9018</t>
+          <t>ActvSoccer_team_name_3008</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>右肋夹防外弧</t>
+          <t>城市联赛·竞技</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1032/ref:进攻19.png</t>
+          <t>TeamCfg/3008</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9019</t>
+          <t>ActvSoccer_team_name_3009</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>禁区前二打二</t>
+          <t>城市联赛·联合</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/1033/ref:进攻20.png</t>
+          <t>TeamCfg/3009</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9020</t>
+          <t>ActvSoccer_team_name_3010</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>正中人墙任意球</t>
+          <t>城市联赛·勇士</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3010/ref:任意球1.png</t>
+          <t>TeamCfg/3010</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9021</t>
+          <t>ActvSoccer_team_name_3011</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>左侧绕墙任意球</t>
+          <t>省级联赛·联</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3011/ref:任意球2.png</t>
+          <t>TeamCfg/3011</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9022</t>
+          <t>ActvSoccer_team_name_3012</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>中路无密墙任意球</t>
+          <t>省级联赛·FC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3012/ref:任意球3.png</t>
+          <t>TeamCfg/3012</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9023</t>
+          <t>ActvSoccer_team_name_3013</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>右侧双人接应任意球</t>
+          <t>省级联赛·竞技</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3013/ref:任意球4.png</t>
+          <t>TeamCfg/3013</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9024</t>
+          <t>ActvSoccer_team_name_3014</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>近距正面任意球</t>
+          <t>省级联赛·联合</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/3014/ref:任意球5.png</t>
+          <t>TeamCfg/3014</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9025</t>
+          <t>ActvSoccer_team_name_3015</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>标准点球</t>
+          <t>省级联赛·勇士</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/5006/ref:点球.png</t>
+          <t>TeamCfg/3015</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9026</t>
+          <t>ActvSoccer_team_name_3016</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>左角球前点传中</t>
+          <t>大区联赛·联</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2011/ref:角球1.png</t>
+          <t>TeamCfg/3016</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9027</t>
+          <t>ActvSoccer_team_name_3017</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>右角球禁区混战</t>
+          <t>大区联赛·FC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/2012/ref:角球2.png</t>
+          <t>TeamCfg/3017</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9028</t>
+          <t>ActvSoccer_team_name_3018</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>左侧界外球近端接应</t>
+          <t>大区联赛·竞技</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/6009/ref:界外发球1.png</t>
+          <t>TeamCfg/3018</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ActvSoccer_preset_ref_9029</t>
+          <t>ActvSoccer_team_name_3019</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>正面守门扑救</t>
+          <t>大区联赛·联合</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SlicePresetCfg/4005/ref:守门.png</t>
+          <t>TeamCfg/3019</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_1</t>
+          <t>ActvSoccer_team_name_3020</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>业余球员</t>
+          <t>大区联赛·勇士</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/1</t>
+          <t>TeamCfg/3020</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_2</t>
+          <t>ActvSoccer_team_name_3021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>新秀</t>
+          <t>全国联赛·联</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/2</t>
+          <t>TeamCfg/3021</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_3</t>
+          <t>ActvSoccer_team_name_3022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>专业球员</t>
+          <t>全国联赛·FC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/3</t>
+          <t>TeamCfg/3022</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_4</t>
+          <t>ActvSoccer_team_name_3023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>明星</t>
+          <t>全国联赛·竞技</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/4</t>
+          <t>TeamCfg/3023</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_5</t>
+          <t>ActvSoccer_team_name_3024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>大师</t>
+          <t>全国联赛·联合</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/5</t>
+          <t>TeamCfg/3024</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_6</t>
+          <t>ActvSoccer_team_name_3025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>世界级</t>
+          <t>全国联赛·勇士</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/6</t>
+          <t>TeamCfg/3025</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ActvSoccer_growth_fame_title_7</t>
+          <t>ActvSoccer_team_name_3026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>传奇</t>
+          <t>洲际资格赛·联</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FameGrowthLevelCfg/7</t>
+          <t>TeamCfg/3026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_101</t>
+          <t>ActvSoccer_team_name_3027</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>红星联</t>
+          <t>洲际资格赛·FC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TeamCfg/101</t>
+          <t>TeamCfg/3027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_102</t>
+          <t>ActvSoccer_team_name_3028</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>莱茵青年</t>
+          <t>洲际资格赛·竞技</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TeamCfg/102</t>
+          <t>TeamCfg/3028</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_103</t>
+          <t>ActvSoccer_team_name_3029</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>桑巴之星</t>
+          <t>洲际资格赛·联合</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TeamCfg/103</t>
+          <t>TeamCfg/3029</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_104</t>
+          <t>ActvSoccer_team_name_3030</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>蓝白雄鹰</t>
+          <t>洲际资格赛·勇士</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TeamCfg/104</t>
+          <t>TeamCfg/3030</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_201</t>
+          <t>ActvSoccer_team_name_3031</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>海港FC</t>
+          <t>洲际联赛·联</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TeamCfg/201</t>
+          <t>TeamCfg/3031</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_202</t>
+          <t>ActvSoccer_team_name_3032</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>东方之鹰</t>
+          <t>洲际联赛·FC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TeamCfg/202</t>
+          <t>TeamCfg/3032</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_203</t>
+          <t>ActvSoccer_team_name_3033</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>北欧狼</t>
+          <t>洲际联赛·竞技</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TeamCfg/203</t>
+          <t>TeamCfg/3033</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_204</t>
+          <t>ActvSoccer_team_name_3034</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>阿根廷神鹰</t>
+          <t>洲际联赛·联合</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TeamCfg/204</t>
+          <t>TeamCfg/3034</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_205</t>
+          <t>ActvSoccer_team_name_3035</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>桑巴红魔</t>
+          <t>洲际联赛·勇士</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TeamCfg/205</t>
+          <t>TeamCfg/3035</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_206</t>
+          <t>ActvSoccer_team_name_3036</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>南美风暴</t>
+          <t>国际邀请赛·联</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TeamCfg/206</t>
+          <t>TeamCfg/3036</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_207</t>
+          <t>ActvSoccer_team_name_3037</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>潘帕斯之翼</t>
+          <t>国际邀请赛·FC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TeamCfg/207</t>
+          <t>TeamCfg/3037</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_208</t>
+          <t>ActvSoccer_team_name_3038</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>高卢雄鸡</t>
+          <t>国际邀请赛·竞技</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TeamCfg/208</t>
+          <t>TeamCfg/3038</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3001</t>
+          <t>ActvSoccer_team_name_3039</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>社区杯·联</t>
+          <t>国际邀请赛·联合</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TeamCfg/3001</t>
+          <t>TeamCfg/3039</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3002</t>
+          <t>ActvSoccer_team_name_3040</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>社区杯·FC</t>
+          <t>国际邀请赛·勇士</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TeamCfg/3002</t>
+          <t>TeamCfg/3040</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3003</t>
+          <t>ActvSoccer_team_name_3041</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>社区杯·竞技</t>
+          <t>世界精英赛·联</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TeamCfg/3003</t>
+          <t>TeamCfg/3041</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3004</t>
+          <t>ActvSoccer_team_name_3042</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>社区杯·联合</t>
+          <t>世界精英赛·FC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TeamCfg/3004</t>
+          <t>TeamCfg/3042</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3005</t>
+          <t>ActvSoccer_team_name_3043</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>社区杯·勇士</t>
+          <t>世界精英赛·竞技</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TeamCfg/3005</t>
+          <t>TeamCfg/3043</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3006</t>
+          <t>ActvSoccer_team_name_3044</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>城市联赛·联</t>
+          <t>世界精英赛·联合</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TeamCfg/3006</t>
+          <t>TeamCfg/3044</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3007</t>
+          <t>ActvSoccer_team_name_3045</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>城市联赛·FC</t>
+          <t>世界精英赛·勇士</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TeamCfg/3007</t>
+          <t>TeamCfg/3045</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3008</t>
+          <t>ActvSoccer_team_name_3046</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>城市联赛·竞技</t>
+          <t>世界杯总决赛·联</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TeamCfg/3008</t>
+          <t>TeamCfg/3046</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3009</t>
+          <t>ActvSoccer_team_name_3047</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>城市联赛·联合</t>
+          <t>世界杯总决赛·FC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TeamCfg/3009</t>
+          <t>TeamCfg/3047</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3010</t>
+          <t>ActvSoccer_team_name_3048</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>城市联赛·勇士</t>
+          <t>世界杯总决赛·竞技</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TeamCfg/3010</t>
+          <t>TeamCfg/3048</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3011</t>
+          <t>ActvSoccer_team_name_3049</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>省级联赛·联</t>
+          <t>世界杯总决赛·联合</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TeamCfg/3011</t>
+          <t>TeamCfg/3049</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3012</t>
+          <t>ActvSoccer_team_name_3050</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>省级联赛·FC</t>
+          <t>世界杯总决赛·勇士</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TeamCfg/3012</t>
+          <t>TeamCfg/3050</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3013</t>
+          <t>ActvSoccer_season_league_name_1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>省级联赛·竞技</t>
+          <t>社区杯 第1/50轮</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TeamCfg/3013</t>
+          <t>SeasonCfg/1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3014</t>
+          <t>ActvSoccer_season_league_name_2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>省级联赛·联合</t>
+          <t>社区杯 第2/50轮</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TeamCfg/3014</t>
+          <t>SeasonCfg/2</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3015</t>
+          <t>ActvSoccer_season_league_name_3</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>省级联赛·勇士</t>
+          <t>社区杯 第3/50轮</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TeamCfg/3015</t>
+          <t>SeasonCfg/3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3016</t>
+          <t>ActvSoccer_season_league_name_4</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>大区联赛·联</t>
+          <t>社区杯 第4/50轮</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TeamCfg/3016</t>
+          <t>SeasonCfg/4</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3017</t>
+          <t>ActvSoccer_season_league_name_5</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>大区联赛·FC</t>
+          <t>社区杯 第5/50轮</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TeamCfg/3017</t>
+          <t>SeasonCfg/5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3018</t>
+          <t>ActvSoccer_season_league_name_6</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>大区联赛·竞技</t>
+          <t>城市联赛 第6/50轮</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TeamCfg/3018</t>
+          <t>SeasonCfg/6</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3019</t>
+          <t>ActvSoccer_season_league_name_7</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>大区联赛·联合</t>
+          <t>城市联赛 第7/50轮</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TeamCfg/3019</t>
+          <t>SeasonCfg/7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3020</t>
+          <t>ActvSoccer_season_league_name_8</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>大区联赛·勇士</t>
+          <t>城市联赛 第8/50轮</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TeamCfg/3020</t>
+          <t>SeasonCfg/8</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3021</t>
+          <t>ActvSoccer_season_league_name_9</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>全国联赛·联</t>
+          <t>城市联赛 第9/50轮</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TeamCfg/3021</t>
+          <t>SeasonCfg/9</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3022</t>
+          <t>ActvSoccer_season_league_name_10</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>全国联赛·FC</t>
+          <t>城市联赛 第10/50轮</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TeamCfg/3022</t>
+          <t>SeasonCfg/10</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3023</t>
+          <t>ActvSoccer_season_league_name_11</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>全国联赛·竞技</t>
+          <t>省级联赛 第11/50轮</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TeamCfg/3023</t>
+          <t>SeasonCfg/11</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3024</t>
+          <t>ActvSoccer_season_league_name_12</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>全国联赛·联合</t>
+          <t>省级联赛 第12/50轮</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TeamCfg/3024</t>
+          <t>SeasonCfg/12</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3025</t>
+          <t>ActvSoccer_season_league_name_13</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>全国联赛·勇士</t>
+          <t>省级联赛 第13/50轮</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TeamCfg/3025</t>
+          <t>SeasonCfg/13</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3026</t>
+          <t>ActvSoccer_season_league_name_14</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>洲际资格赛·联</t>
+          <t>省级联赛 第14/50轮</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TeamCfg/3026</t>
+          <t>SeasonCfg/14</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3027</t>
+          <t>ActvSoccer_season_league_name_15</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>洲际资格赛·FC</t>
+          <t>省级联赛 第15/50轮</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TeamCfg/3027</t>
+          <t>SeasonCfg/15</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3028</t>
+          <t>ActvSoccer_season_league_name_16</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>洲际资格赛·竞技</t>
+          <t>大区联赛 第16/50轮</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TeamCfg/3028</t>
+          <t>SeasonCfg/16</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3029</t>
+          <t>ActvSoccer_season_league_name_17</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>洲际资格赛·联合</t>
+          <t>大区联赛 第17/50轮</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TeamCfg/3029</t>
+          <t>SeasonCfg/17</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3030</t>
+          <t>ActvSoccer_season_league_name_18</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>洲际资格赛·勇士</t>
+          <t>大区联赛 第18/50轮</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TeamCfg/3030</t>
+          <t>SeasonCfg/18</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3031</t>
+          <t>ActvSoccer_season_league_name_19</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>洲际联赛·联</t>
+          <t>大区联赛 第19/50轮</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TeamCfg/3031</t>
+          <t>SeasonCfg/19</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3032</t>
+          <t>ActvSoccer_season_league_name_20</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>洲际联赛·FC</t>
+          <t>大区联赛 第20/50轮</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>TeamCfg/3032</t>
+          <t>SeasonCfg/20</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3033</t>
+          <t>ActvSoccer_season_league_name_21</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>洲际联赛·竞技</t>
+          <t>全国联赛 第21/50轮</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TeamCfg/3033</t>
+          <t>SeasonCfg/21</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3034</t>
+          <t>ActvSoccer_season_league_name_22</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>洲际联赛·联合</t>
+          <t>全国联赛 第22/50轮</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TeamCfg/3034</t>
+          <t>SeasonCfg/22</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3035</t>
+          <t>ActvSoccer_season_league_name_23</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>洲际联赛·勇士</t>
+          <t>全国联赛 第23/50轮</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>TeamCfg/3035</t>
+          <t>SeasonCfg/23</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3036</t>
+          <t>ActvSoccer_season_league_name_24</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>国际邀请赛·联</t>
+          <t>全国联赛 第24/50轮</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TeamCfg/3036</t>
+          <t>SeasonCfg/24</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3037</t>
+          <t>ActvSoccer_season_league_name_25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>国际邀请赛·FC</t>
+          <t>全国联赛 第25/50轮</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TeamCfg/3037</t>
+          <t>SeasonCfg/25</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3038</t>
+          <t>ActvSoccer_season_league_name_26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>国际邀请赛·竞技</t>
+          <t>洲际资格赛 第26/50轮</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TeamCfg/3038</t>
+          <t>SeasonCfg/26</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3039</t>
+          <t>ActvSoccer_season_league_name_27</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>国际邀请赛·联合</t>
+          <t>洲际资格赛 第27/50轮</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TeamCfg/3039</t>
+          <t>SeasonCfg/27</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3040</t>
+          <t>ActvSoccer_season_league_name_28</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>国际邀请赛·勇士</t>
+          <t>洲际资格赛 第28/50轮</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TeamCfg/3040</t>
+          <t>SeasonCfg/28</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3041</t>
+          <t>ActvSoccer_season_league_name_29</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>世界精英赛·联</t>
+          <t>洲际资格赛 第29/50轮</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TeamCfg/3041</t>
+          <t>SeasonCfg/29</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3042</t>
+          <t>ActvSoccer_season_league_name_30</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>世界精英赛·FC</t>
+          <t>洲际资格赛 第30/50轮</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TeamCfg/3042</t>
+          <t>SeasonCfg/30</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3043</t>
+          <t>ActvSoccer_season_league_name_31</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>世界精英赛·竞技</t>
+          <t>洲际联赛 第31/50轮</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TeamCfg/3043</t>
+          <t>SeasonCfg/31</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3044</t>
+          <t>ActvSoccer_season_league_name_32</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>世界精英赛·联合</t>
+          <t>洲际联赛 第32/50轮</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TeamCfg/3044</t>
+          <t>SeasonCfg/32</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3045</t>
+          <t>ActvSoccer_season_league_name_33</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>世界精英赛·勇士</t>
+          <t>洲际联赛 第33/50轮</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TeamCfg/3045</t>
+          <t>SeasonCfg/33</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3046</t>
+          <t>ActvSoccer_season_league_name_34</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联</t>
+          <t>洲际联赛 第34/50轮</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TeamCfg/3046</t>
+          <t>SeasonCfg/34</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3047</t>
+          <t>ActvSoccer_season_league_name_35</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>世界杯总决赛·FC</t>
+          <t>洲际联赛 第35/50轮</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TeamCfg/3047</t>
+          <t>SeasonCfg/35</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3048</t>
+          <t>ActvSoccer_season_league_name_36</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>世界杯总决赛·竞技</t>
+          <t>国际邀请赛 第36/50轮</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TeamCfg/3048</t>
+          <t>SeasonCfg/36</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3049</t>
+          <t>ActvSoccer_season_league_name_37</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>世界杯总决赛·联合</t>
+          <t>国际邀请赛 第37/50轮</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TeamCfg/3049</t>
+          <t>SeasonCfg/37</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ActvSoccer_team_name_3050</t>
+          <t>ActvSoccer_season_league_name_38</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>世界杯总决赛·勇士</t>
+          <t>国际邀请赛 第38/50轮</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TeamCfg/3050</t>
+          <t>SeasonCfg/38</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_1</t>
+          <t>ActvSoccer_season_league_name_39</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>社区杯 第1/50轮</t>
+          <t>国际邀请赛 第39/50轮</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SeasonCfg/1</t>
+          <t>SeasonCfg/39</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_2</t>
+          <t>ActvSoccer_season_league_name_40</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>社区杯 第2/50轮</t>
+          <t>国际邀请赛 第40/50轮</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SeasonCfg/2</t>
+          <t>SeasonCfg/40</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_3</t>
+          <t>ActvSoccer_season_league_name_41</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>社区杯 第3/50轮</t>
+          <t>世界精英赛 第41/50轮</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SeasonCfg/3</t>
+          <t>SeasonCfg/41</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_4</t>
+          <t>ActvSoccer_season_league_name_42</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>社区杯 第4/50轮</t>
+          <t>世界精英赛 第42/50轮</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SeasonCfg/4</t>
+          <t>SeasonCfg/42</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_5</t>
+          <t>ActvSoccer_season_league_name_43</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>社区杯 第5/50轮</t>
+          <t>世界精英赛 第43/50轮</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SeasonCfg/5</t>
+          <t>SeasonCfg/43</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_6</t>
+          <t>ActvSoccer_season_league_name_44</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>城市联赛 第6/50轮</t>
+          <t>世界精英赛 第44/50轮</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SeasonCfg/6</t>
+          <t>SeasonCfg/44</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_7</t>
+          <t>ActvSoccer_season_league_name_45</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>城市联赛 第7/50轮</t>
+          <t>世界精英赛 第45/50轮</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SeasonCfg/7</t>
+          <t>SeasonCfg/45</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_8</t>
+          <t>ActvSoccer_season_league_name_46</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>城市联赛 第8/50轮</t>
+          <t>世界杯总决赛 第46/50轮</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SeasonCfg/8</t>
+          <t>SeasonCfg/46</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_9</t>
+          <t>ActvSoccer_season_league_name_47</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>城市联赛 第9/50轮</t>
+          <t>世界杯总决赛 第47/50轮</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SeasonCfg/9</t>
+          <t>SeasonCfg/47</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_10</t>
+          <t>ActvSoccer_season_league_name_48</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>城市联赛 第10/50轮</t>
+          <t>世界杯总决赛 第48/50轮</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SeasonCfg/10</t>
+          <t>SeasonCfg/48</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_11</t>
+          <t>ActvSoccer_season_league_name_49</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>省级联赛 第11/50轮</t>
+          <t>世界杯总决赛 第49/50轮</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SeasonCfg/11</t>
+          <t>SeasonCfg/49</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_12</t>
+          <t>ActvSoccer_season_league_name_50</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>省级联赛 第12/50轮</t>
+          <t>世界杯总决赛 第50/50轮</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SeasonCfg/12</t>
+          <t>SeasonCfg/50</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_13</t>
+          <t>ActvSoccer_knockout_phase_name_team_build</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>省级联赛 第13/50轮</t>
+          <t>组队期</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SeasonCfg/13</t>
+          <t>KnockoutPhaseCfg/1</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_14</t>
+          <t>ActvSoccer_knockout_day_content_1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>省级联赛 第14/50轮</t>
+          <t>发起/加入组队、命名队名队标、审批</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SeasonCfg/14</t>
+          <t>KnockoutPhaseCfg/1</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_15</t>
+          <t>ActvSoccer_knockout_phase_name_3</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>省级联赛 第15/50轮</t>
+          <t>海选</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SeasonCfg/15</t>
+          <t>KnockoutPhaseCfg/2</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_16</t>
+          <t>ActvSoccer_knockout_day_content_3</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>大区联赛 第16/50轮</t>
+          <t>1天内筛出64强</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SeasonCfg/16</t>
+          <t>KnockoutPhaseCfg/2</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_17</t>
+          <t>ActvSoccer_knockout_phase_name_4</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>大区联赛 第17/50轮</t>
+          <t>正赛第1轮</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SeasonCfg/17</t>
+          <t>KnockoutPhaseCfg/3</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_18</t>
+          <t>ActvSoccer_knockout_day_content_4</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>大区联赛 第18/50轮</t>
+          <t>8组各一轮(64强)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SeasonCfg/18</t>
+          <t>KnockoutPhaseCfg/3</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_19</t>
+          <t>ActvSoccer_knockout_phase_name_5</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>大区联赛 第19/50轮</t>
+          <t>正赛第2轮</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SeasonCfg/19</t>
+          <t>KnockoutPhaseCfg/4</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_20</t>
+          <t>ActvSoccer_knockout_day_content_5</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>大区联赛 第20/50轮</t>
+          <t>8组各一轮(32强)</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SeasonCfg/20</t>
+          <t>KnockoutPhaseCfg/4</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_21</t>
+          <t>ActvSoccer_knockout_phase_name_6</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>全国联赛 第21/50轮</t>
+          <t>正赛第3轮</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SeasonCfg/21</t>
+          <t>KnockoutPhaseCfg/5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_22</t>
+          <t>ActvSoccer_knockout_day_content_6</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>全国联赛 第22/50轮</t>
+          <t>8组各一轮(16强)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>SeasonCfg/22</t>
+          <t>KnockoutPhaseCfg/5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_23</t>
+          <t>ActvSoccer_knockout_phase_name_7</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>全国联赛 第23/50轮</t>
+          <t>正赛第4轮</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SeasonCfg/23</t>
+          <t>KnockoutPhaseCfg/6</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_24</t>
+          <t>ActvSoccer_knockout_day_content_7</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>全国联赛 第24/50轮</t>
+          <t>8组决出组冠军→8强</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SeasonCfg/24</t>
+          <t>KnockoutPhaseCfg/6</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_25</t>
+          <t>ActvSoccer_knockout_phase_name_8</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>全国联赛 第25/50轮</t>
+          <t>正赛第5轮</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SeasonCfg/25</t>
+          <t>KnockoutPhaseCfg/7</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_26</t>
+          <t>ActvSoccer_knockout_day_content_8</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>洲际资格赛 第26/50轮</t>
+          <t>8强淘汰赛(4强)</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SeasonCfg/26</t>
+          <t>KnockoutPhaseCfg/7</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_27</t>
+          <t>ActvSoccer_knockout_phase_name_9</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>洲际资格赛 第27/50轮</t>
+          <t>决赛</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SeasonCfg/27</t>
+          <t>KnockoutPhaseCfg/8</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_28</t>
+          <t>ActvSoccer_knockout_day_content_9</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>洲际资格赛 第28/50轮</t>
+          <t>冠亚军决赛</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SeasonCfg/28</t>
+          <t>KnockoutPhaseCfg/8</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_29</t>
+          <t>ActvSoccer_knockout_phase_name_10</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>洲际资格赛 第29/50轮</t>
+          <t>展示期</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SeasonCfg/29</t>
+          <t>KnockoutPhaseCfg/9</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ActvSoccer_season_league_name_30</t>
+          <t>ActvSoccer_knockout_day_content_10</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>洲际资格赛 第30/50轮</t>
+          <t>冠军展示+兑换商店可用</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
-        <is>
-          <t>SeasonCfg/30</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_31</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>洲际联赛 第31/50轮</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>SeasonCfg/31</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_32</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>洲际联赛 第32/50轮</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>SeasonCfg/32</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_33</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>洲际联赛 第33/50轮</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>SeasonCfg/33</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_34</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>洲际联赛 第34/50轮</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>SeasonCfg/34</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_35</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>洲际联赛 第35/50轮</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>SeasonCfg/35</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_36</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第36/50轮</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>SeasonCfg/36</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_37</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第37/50轮</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>SeasonCfg/37</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_38</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第38/50轮</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>SeasonCfg/38</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_39</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第39/50轮</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>SeasonCfg/39</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_40</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>国际邀请赛 第40/50轮</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>SeasonCfg/40</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_41</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>世界精英赛 第41/50轮</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>SeasonCfg/41</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_42</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>世界精英赛 第42/50轮</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>SeasonCfg/42</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_43</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>世界精英赛 第43/50轮</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>SeasonCfg/43</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_44</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>世界精英赛 第44/50轮</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>SeasonCfg/44</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_45</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>世界精英赛 第45/50轮</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>SeasonCfg/45</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_46</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第46/50轮</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>SeasonCfg/46</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_47</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第47/50轮</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>SeasonCfg/47</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_48</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第48/50轮</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>SeasonCfg/48</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_49</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第49/50轮</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>SeasonCfg/49</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>ActvSoccer_season_league_name_50</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>世界杯总决赛 第50/50轮</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>SeasonCfg/50</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_team_build</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>组队期</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_1</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>发起/加入组队、命名队名队标、审批</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_3</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>海选</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_3</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>1天内筛出64强</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/2</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_4</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>正赛第1轮</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_4</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>8组各一轮(64强)</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_5</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>正赛第2轮</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_5</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>8组各一轮(32强)</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/4</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_6</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>正赛第3轮</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_6</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>8组各一轮(16强)</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_7</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>正赛第4轮</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_7</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>8组决出组冠军→8强</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_8</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>正赛第5轮</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_8</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>8强淘汰赛(4强)</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_9</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>决赛</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_9</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>冠亚军决赛</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_phase_name_10</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>展示期</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>KnockoutPhaseCfg/9</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>ActvSoccer_knockout_day_content_10</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>冠军展示+兑换商店可用</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
         <is>
           <t>KnockoutPhaseCfg/9</t>
         </is>
